--- a/Prediction_Excel_Sheets/Predictions_With_Sentiment_LAll_H1.xlsx
+++ b/Prediction_Excel_Sheets/Predictions_With_Sentiment_LAll_H1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C689"/>
+  <dimension ref="A1:C663"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,7570 +447,7284 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>172.7889251708984</v>
+        <v>168.513916</v>
       </c>
       <c r="B2" t="n">
-        <v>170.4594268798828</v>
+        <v>171.68158</v>
       </c>
       <c r="C2" t="n">
-        <v>2.329498291015625</v>
+        <v>-3.167664000000002</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>172.8975067138672</v>
+        <v>168.817947</v>
       </c>
       <c r="B3" t="n">
-        <v>172.7889251708984</v>
+        <v>168.513916</v>
       </c>
       <c r="C3" t="n">
-        <v>0.10858154296875</v>
+        <v>0.304031000000009</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>171.9498901367188</v>
+        <v>166.80748</v>
       </c>
       <c r="B4" t="n">
-        <v>172.8975067138672</v>
+        <v>168.817947</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.9476165771484375</v>
+        <v>-2.010467000000006</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>169.343994140625</v>
+        <v>162.551224</v>
       </c>
       <c r="B5" t="n">
-        <v>171.9498901367188</v>
+        <v>166.80748</v>
       </c>
       <c r="C5" t="n">
-        <v>-2.60589599609375</v>
+        <v>-4.256256000000008</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>169.620361328125</v>
+        <v>164.424362</v>
       </c>
       <c r="B6" t="n">
-        <v>169.343994140625</v>
+        <v>162.551224</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2763671874999716</v>
+        <v>1.873138000000012</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>170.7555236816406</v>
+        <v>167.111465</v>
       </c>
       <c r="B7" t="n">
-        <v>169.620361328125</v>
+        <v>164.424362</v>
       </c>
       <c r="C7" t="n">
-        <v>1.135162353515653</v>
+        <v>2.687103000000008</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>173.1640014648437</v>
+        <v>162.100098</v>
       </c>
       <c r="B8" t="n">
-        <v>170.7555236816406</v>
+        <v>167.111465</v>
       </c>
       <c r="C8" t="n">
-        <v>2.408477783203097</v>
+        <v>-5.011367000000007</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>175.0098419189453</v>
+        <v>161.884399</v>
       </c>
       <c r="B9" t="n">
-        <v>173.1640014648437</v>
+        <v>162.100098</v>
       </c>
       <c r="C9" t="n">
-        <v>1.845840454101591</v>
+        <v>-0.2156990000000008</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>174.9605102539062</v>
+        <v>164.169357</v>
       </c>
       <c r="B10" t="n">
-        <v>175.0098419189453</v>
+        <v>161.884399</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.0493316650390625</v>
+        <v>2.284957999999989</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>177.7637939453125</v>
+        <v>164.002686</v>
       </c>
       <c r="B11" t="n">
-        <v>174.9605102539062</v>
+        <v>164.169357</v>
       </c>
       <c r="C11" t="n">
-        <v>2.80328369140625</v>
+        <v>-0.1666709999999796</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>178.6126861572266</v>
+        <v>163.208328</v>
       </c>
       <c r="B12" t="n">
-        <v>177.7637939453125</v>
+        <v>164.002686</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8488922119140625</v>
+        <v>-0.7943580000000168</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>177.2603912353516</v>
+        <v>158.667664</v>
       </c>
       <c r="B13" t="n">
-        <v>178.6126861572266</v>
+        <v>163.208328</v>
       </c>
       <c r="C13" t="n">
-        <v>-1.352294921875</v>
+        <v>-4.540663999999992</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>176.8951721191406</v>
+        <v>159.736633</v>
       </c>
       <c r="B14" t="n">
-        <v>177.2603912353516</v>
+        <v>158.667664</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.3652191162109375</v>
+        <v>1.06896900000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>175.5231323242188</v>
+        <v>153.773972</v>
       </c>
       <c r="B15" t="n">
-        <v>176.8951721191406</v>
+        <v>159.736633</v>
       </c>
       <c r="C15" t="n">
-        <v>-1.372039794921875</v>
+        <v>-5.962661000000026</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>178.2376251220703</v>
+        <v>153.548401</v>
       </c>
       <c r="B16" t="n">
-        <v>175.5231323242188</v>
+        <v>153.773972</v>
       </c>
       <c r="C16" t="n">
-        <v>2.714492797851562</v>
+        <v>-0.2255709999999738</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>178.62255859375</v>
+        <v>160.481934</v>
       </c>
       <c r="B17" t="n">
-        <v>178.2376251220703</v>
+        <v>153.548401</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3849334716796875</v>
+        <v>6.933532999999983</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>181.416030883789</v>
+        <v>154.607559</v>
       </c>
       <c r="B18" t="n">
-        <v>178.62255859375</v>
+        <v>160.481934</v>
       </c>
       <c r="C18" t="n">
-        <v>2.793472290039034</v>
+        <v>-5.874374999999986</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>180.9421997070312</v>
+        <v>154.911575</v>
       </c>
       <c r="B19" t="n">
-        <v>181.416030883789</v>
+        <v>154.607559</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.4738311767577841</v>
+        <v>0.3040159999999901</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>181.573959350586</v>
+        <v>156.402237</v>
       </c>
       <c r="B20" t="n">
-        <v>180.9421997070312</v>
+        <v>154.911575</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6317596435547443</v>
+        <v>1.490662000000015</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>183.6073150634766</v>
+        <v>162.81604</v>
       </c>
       <c r="B21" t="n">
-        <v>181.573959350586</v>
+        <v>156.402237</v>
       </c>
       <c r="C21" t="n">
-        <v>2.033355712890568</v>
+        <v>6.413802999999973</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>182.5314025878907</v>
+        <v>153.744583</v>
       </c>
       <c r="B22" t="n">
-        <v>183.6073150634766</v>
+        <v>162.81604</v>
       </c>
       <c r="C22" t="n">
-        <v>-1.075912475585909</v>
+        <v>-9.071456999999981</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>182.6202545166016</v>
+        <v>154.471329</v>
       </c>
       <c r="B23" t="n">
-        <v>182.5314025878907</v>
+        <v>153.744583</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0888519287109375</v>
+        <v>0.7267459999999915</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>181.5838470458984</v>
+        <v>149.344543</v>
       </c>
       <c r="B24" t="n">
-        <v>182.6202545166016</v>
+        <v>154.471329</v>
       </c>
       <c r="C24" t="n">
-        <v>-1.036407470703153</v>
+        <v>-5.12678600000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>184.5845642089844</v>
+        <v>151.750793</v>
       </c>
       <c r="B25" t="n">
-        <v>181.5838470458984</v>
+        <v>149.344543</v>
       </c>
       <c r="C25" t="n">
-        <v>3.000717163085966</v>
+        <v>2.40625</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>184.2686614990234</v>
+        <v>143.883865</v>
       </c>
       <c r="B26" t="n">
-        <v>184.5845642089844</v>
+        <v>151.750793</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.3159027099609659</v>
+        <v>-7.866928000000001</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>182.8769073486328</v>
+        <v>140.014191</v>
       </c>
       <c r="B27" t="n">
-        <v>184.2686614990234</v>
+        <v>143.883865</v>
       </c>
       <c r="C27" t="n">
-        <v>-1.391754150390653</v>
+        <v>-3.869673999999975</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>185.630874633789</v>
+        <v>144.482925</v>
       </c>
       <c r="B28" t="n">
-        <v>182.8769073486328</v>
+        <v>140.014191</v>
       </c>
       <c r="C28" t="n">
-        <v>2.75396728515625</v>
+        <v>4.468733999999984</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>186.8054962158203</v>
+        <v>142.940994</v>
       </c>
       <c r="B29" t="n">
-        <v>185.630874633789</v>
+        <v>144.482925</v>
       </c>
       <c r="C29" t="n">
-        <v>1.174621582031278</v>
+        <v>-1.541931000000005</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>187.1410675048828</v>
+        <v>146.574905</v>
       </c>
       <c r="B30" t="n">
-        <v>186.8054962158203</v>
+        <v>142.940994</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3355712890625</v>
+        <v>3.633911000000012</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>191.4645538330078</v>
+        <v>138.305252</v>
       </c>
       <c r="B31" t="n">
-        <v>187.1410675048828</v>
+        <v>146.574905</v>
       </c>
       <c r="C31" t="n">
-        <v>4.323486328124972</v>
+        <v>-8.269653000000005</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>189.9740447998047</v>
+        <v>134.897232</v>
       </c>
       <c r="B32" t="n">
-        <v>191.4645538330078</v>
+        <v>138.305252</v>
       </c>
       <c r="C32" t="n">
-        <v>-1.490509033203097</v>
+        <v>-3.408019999999993</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>188.8586120605469</v>
+        <v>135.132965</v>
       </c>
       <c r="B33" t="n">
-        <v>189.9740447998047</v>
+        <v>134.897232</v>
       </c>
       <c r="C33" t="n">
-        <v>-1.115432739257812</v>
+        <v>0.2357330000000104</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>189.3324279785156</v>
+        <v>140.554367</v>
       </c>
       <c r="B34" t="n">
-        <v>188.8586120605469</v>
+        <v>135.132965</v>
       </c>
       <c r="C34" t="n">
-        <v>0.4738159179687216</v>
+        <v>5.421402</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>188.2170104980469</v>
+        <v>137.853485</v>
       </c>
       <c r="B35" t="n">
-        <v>189.3324279785156</v>
+        <v>140.554367</v>
       </c>
       <c r="C35" t="n">
-        <v>-1.115417480468722</v>
+        <v>-2.700882000000007</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>186.1737670898437</v>
+        <v>138.010651</v>
       </c>
       <c r="B36" t="n">
-        <v>188.2170104980469</v>
+        <v>137.853485</v>
       </c>
       <c r="C36" t="n">
-        <v>-2.043243408203182</v>
+        <v>0.1571659999999895</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>185.650619506836</v>
+        <v>141.212448</v>
       </c>
       <c r="B37" t="n">
-        <v>186.1737670898437</v>
+        <v>138.010651</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.5231475830076704</v>
+        <v>3.201796999999999</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>187.3187713623047</v>
+        <v>146.967758</v>
       </c>
       <c r="B38" t="n">
-        <v>185.650619506836</v>
+        <v>141.212448</v>
       </c>
       <c r="C38" t="n">
-        <v>1.668151855468665</v>
+        <v>5.755310000000009</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>188.0788269042969</v>
+        <v>146.182068</v>
       </c>
       <c r="B39" t="n">
-        <v>187.3187713623047</v>
+        <v>146.967758</v>
       </c>
       <c r="C39" t="n">
-        <v>0.7600555419921875</v>
+        <v>-0.7856900000000167</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>188.2268829345703</v>
+        <v>146.054398</v>
       </c>
       <c r="B40" t="n">
-        <v>188.0788269042969</v>
+        <v>146.182068</v>
       </c>
       <c r="C40" t="n">
-        <v>0.1480560302734375</v>
+        <v>-0.1276699999999948</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>191.4842834472656</v>
+        <v>148.509735</v>
       </c>
       <c r="B41" t="n">
-        <v>188.2268829345703</v>
+        <v>146.054398</v>
       </c>
       <c r="C41" t="n">
-        <v>3.257400512695312</v>
+        <v>2.455337000000014</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>191.2276153564453</v>
+        <v>142.783844</v>
       </c>
       <c r="B42" t="n">
-        <v>191.4842834472656</v>
+        <v>148.509735</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.2566680908203125</v>
+        <v>-5.725891000000018</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>192.5799255371093</v>
+        <v>143.530243</v>
       </c>
       <c r="B43" t="n">
-        <v>191.2276153564453</v>
+        <v>142.783844</v>
       </c>
       <c r="C43" t="n">
-        <v>1.352310180664006</v>
+        <v>0.7463990000000251</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>190.6353912353516</v>
+        <v>146.054398</v>
       </c>
       <c r="B44" t="n">
-        <v>192.5799255371093</v>
+        <v>143.530243</v>
       </c>
       <c r="C44" t="n">
-        <v>-1.944534301757727</v>
+        <v>2.524154999999979</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>189.4607391357422</v>
+        <v>145.317764</v>
       </c>
       <c r="B45" t="n">
-        <v>190.6353912353516</v>
+        <v>146.054398</v>
       </c>
       <c r="C45" t="n">
-        <v>-1.174652099609403</v>
+        <v>-0.7366339999999809</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>190.2602996826172</v>
+        <v>140.092773</v>
       </c>
       <c r="B46" t="n">
-        <v>189.4607391357422</v>
+        <v>145.317764</v>
       </c>
       <c r="C46" t="n">
-        <v>0.7995605468749716</v>
+        <v>-5.224991000000017</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>191.1190490722656</v>
+        <v>134.681183</v>
       </c>
       <c r="B47" t="n">
-        <v>190.2602996826172</v>
+        <v>140.092773</v>
       </c>
       <c r="C47" t="n">
-        <v>0.8587493896484375</v>
+        <v>-5.41158999999999</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>191.9877014160156</v>
+        <v>129.524918</v>
       </c>
       <c r="B48" t="n">
-        <v>191.1190490722656</v>
+        <v>134.681183</v>
       </c>
       <c r="C48" t="n">
-        <v>0.86865234375</v>
+        <v>-5.156264999999991</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>190.7242126464844</v>
+        <v>130.389221</v>
       </c>
       <c r="B49" t="n">
-        <v>191.9877014160156</v>
+        <v>129.524918</v>
       </c>
       <c r="C49" t="n">
-        <v>-1.263488769531193</v>
+        <v>0.8643029999999783</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>193.3004913330078</v>
+        <v>133.01152</v>
       </c>
       <c r="B50" t="n">
-        <v>190.7242126464844</v>
+        <v>130.389221</v>
       </c>
       <c r="C50" t="n">
-        <v>2.576278686523409</v>
+        <v>2.622298999999998</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>193.9125061035156</v>
+        <v>127.737381</v>
       </c>
       <c r="B51" t="n">
-        <v>193.3004913330078</v>
+        <v>133.01152</v>
       </c>
       <c r="C51" t="n">
-        <v>0.6120147705077841</v>
+        <v>-5.274138999999991</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>193.0833129882812</v>
+        <v>129.210632</v>
       </c>
       <c r="B52" t="n">
-        <v>193.9125061035156</v>
+        <v>127.737381</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.8291931152343466</v>
+        <v>1.473251000000005</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>190.0924682617188</v>
+        <v>133.443649</v>
       </c>
       <c r="B53" t="n">
-        <v>193.0833129882812</v>
+        <v>129.210632</v>
       </c>
       <c r="C53" t="n">
-        <v>-2.9908447265625</v>
+        <v>4.23301699999999</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>188.700698852539</v>
+        <v>132.932968</v>
       </c>
       <c r="B54" t="n">
-        <v>190.0924682617188</v>
+        <v>133.443649</v>
       </c>
       <c r="C54" t="n">
-        <v>-1.391769409179716</v>
+        <v>-0.5106810000000053</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>179.6392669677734</v>
+        <v>135.800797</v>
       </c>
       <c r="B55" t="n">
-        <v>188.700698852539</v>
+        <v>132.932968</v>
       </c>
       <c r="C55" t="n">
-        <v>-9.061431884765597</v>
+        <v>2.867829</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>176.5398406982422</v>
+        <v>139.130234</v>
       </c>
       <c r="B56" t="n">
-        <v>179.6392669677734</v>
+        <v>135.800797</v>
       </c>
       <c r="C56" t="n">
-        <v>-3.09942626953125</v>
+        <v>3.329437000000013</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>177.4775695800781</v>
+        <v>139.130234</v>
       </c>
       <c r="B57" t="n">
-        <v>176.5398406982422</v>
+        <v>139.130234</v>
       </c>
       <c r="C57" t="n">
-        <v>0.9377288818359375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>175.8883361816406</v>
+        <v>134.985596</v>
       </c>
       <c r="B58" t="n">
-        <v>177.4775695800781</v>
+        <v>139.130234</v>
       </c>
       <c r="C58" t="n">
-        <v>-1.5892333984375</v>
+        <v>-4.144638000000015</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>175.6711883544922</v>
+        <v>136.743668</v>
       </c>
       <c r="B59" t="n">
-        <v>175.8883361816406</v>
+        <v>134.985596</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.2171478271484375</v>
+        <v>1.758072000000027</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>175.730484008789</v>
+        <v>134.278503</v>
       </c>
       <c r="B60" t="n">
-        <v>175.6711883544922</v>
+        <v>136.743668</v>
       </c>
       <c r="C60" t="n">
-        <v>0.05929565429684658</v>
+        <v>-2.465165000000013</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>177.3811798095703</v>
+        <v>136.449005</v>
       </c>
       <c r="B61" t="n">
-        <v>175.730484008789</v>
+        <v>134.278503</v>
       </c>
       <c r="C61" t="n">
-        <v>1.650695800781278</v>
+        <v>2.170501999999999</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>175.3944396972656</v>
+        <v>139.032043</v>
       </c>
       <c r="B62" t="n">
-        <v>177.3811798095703</v>
+        <v>136.449005</v>
       </c>
       <c r="C62" t="n">
-        <v>-1.986740112304688</v>
+        <v>2.583037999999988</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>174.5246734619141</v>
+        <v>140.367783</v>
       </c>
       <c r="B63" t="n">
-        <v>175.3944396972656</v>
+        <v>139.032043</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.8697662353515625</v>
+        <v>1.335740000000015</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>171.9844207763672</v>
+        <v>143.736526</v>
       </c>
       <c r="B64" t="n">
-        <v>174.5246734619141</v>
+        <v>140.367783</v>
       </c>
       <c r="C64" t="n">
-        <v>-2.540252685546847</v>
+        <v>3.368742999999995</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>172.4687194824219</v>
+        <v>144.414169</v>
       </c>
       <c r="B65" t="n">
-        <v>171.9844207763672</v>
+        <v>143.736526</v>
       </c>
       <c r="C65" t="n">
-        <v>0.4842987060546591</v>
+        <v>0.6776429999999891</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>173.8030853271484</v>
+        <v>142.282944</v>
       </c>
       <c r="B66" t="n">
-        <v>172.4687194824219</v>
+        <v>144.414169</v>
       </c>
       <c r="C66" t="n">
-        <v>1.334365844726562</v>
+        <v>-2.131225000000001</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>175.1769714355469</v>
+        <v>143.255249</v>
       </c>
       <c r="B67" t="n">
-        <v>173.8030853271484</v>
+        <v>142.282944</v>
       </c>
       <c r="C67" t="n">
-        <v>1.373886108398438</v>
+        <v>0.9723050000000057</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>179.0219268798828</v>
+        <v>142.891876</v>
       </c>
       <c r="B68" t="n">
-        <v>175.1769714355469</v>
+        <v>143.255249</v>
       </c>
       <c r="C68" t="n">
-        <v>3.844955444335938</v>
+        <v>-0.3633729999999957</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>174.3368530273438</v>
+        <v>145.818649</v>
       </c>
       <c r="B69" t="n">
-        <v>179.0219268798828</v>
+        <v>142.891876</v>
       </c>
       <c r="C69" t="n">
-        <v>-4.685073852539062</v>
+        <v>2.926772999999997</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>176.5410003662109</v>
+        <v>147.488297</v>
       </c>
       <c r="B70" t="n">
-        <v>174.3368530273438</v>
+        <v>145.818649</v>
       </c>
       <c r="C70" t="n">
-        <v>2.204147338867159</v>
+        <v>1.669647999999995</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>178.1027069091797</v>
+        <v>144.443695</v>
       </c>
       <c r="B71" t="n">
-        <v>176.5410003662109</v>
+        <v>147.488297</v>
       </c>
       <c r="C71" t="n">
-        <v>1.561706542968778</v>
+        <v>-3.044601999999998</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>181.9871673583984</v>
+        <v>148.303452</v>
       </c>
       <c r="B72" t="n">
-        <v>178.1027069091797</v>
+        <v>144.443695</v>
       </c>
       <c r="C72" t="n">
-        <v>3.88446044921875</v>
+        <v>3.859757000000002</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>185.4762725830078</v>
+        <v>150.307037</v>
       </c>
       <c r="B73" t="n">
-        <v>181.9871673583984</v>
+        <v>148.303452</v>
       </c>
       <c r="C73" t="n">
-        <v>3.489105224609375</v>
+        <v>2.003585000000015</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>185.6937408447265</v>
+        <v>152.575836</v>
       </c>
       <c r="B74" t="n">
-        <v>185.4762725830078</v>
+        <v>150.307037</v>
       </c>
       <c r="C74" t="n">
-        <v>0.2174682617187216</v>
+        <v>2.268799000000001</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>187.2653198242188</v>
+        <v>151.338272</v>
       </c>
       <c r="B75" t="n">
-        <v>185.6937408447265</v>
+        <v>152.575836</v>
       </c>
       <c r="C75" t="n">
-        <v>1.571578979492216</v>
+        <v>-1.23756400000002</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>187.5025329589844</v>
+        <v>150.218658</v>
       </c>
       <c r="B76" t="n">
-        <v>187.2653198242188</v>
+        <v>151.338272</v>
       </c>
       <c r="C76" t="n">
-        <v>0.2372131347656534</v>
+        <v>-1.119613999999984</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>180.7911834716797</v>
+        <v>148.892761</v>
       </c>
       <c r="B77" t="n">
-        <v>187.5025329589844</v>
+        <v>150.218658</v>
       </c>
       <c r="C77" t="n">
-        <v>-6.711349487304688</v>
+        <v>-1.325896999999998</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>175.503173828125</v>
+        <v>153.990067</v>
       </c>
       <c r="B78" t="n">
-        <v>180.7911834716797</v>
+        <v>148.892761</v>
       </c>
       <c r="C78" t="n">
-        <v>-5.288009643554744</v>
+        <v>5.097306000000003</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>176.115982055664</v>
+        <v>154.5401</v>
       </c>
       <c r="B79" t="n">
-        <v>175.503173828125</v>
+        <v>153.990067</v>
       </c>
       <c r="C79" t="n">
-        <v>0.6128082275390625</v>
+        <v>0.5500329999999849</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>177.2823181152344</v>
+        <v>159.607941</v>
       </c>
       <c r="B80" t="n">
-        <v>176.115982055664</v>
+        <v>154.5401</v>
       </c>
       <c r="C80" t="n">
-        <v>1.166336059570341</v>
+        <v>5.067841000000016</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>174.2577667236328</v>
+        <v>158.625778</v>
       </c>
       <c r="B81" t="n">
-        <v>177.2823181152344</v>
+        <v>159.607941</v>
       </c>
       <c r="C81" t="n">
-        <v>-3.024551391601562</v>
+        <v>-0.9821630000000141</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>172.1919555664062</v>
+        <v>157.152573</v>
       </c>
       <c r="B82" t="n">
-        <v>174.2577667236328</v>
+        <v>158.625778</v>
       </c>
       <c r="C82" t="n">
-        <v>-2.065811157226562</v>
+        <v>-1.473205000000007</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>173.7042541503906</v>
+        <v>163.163315</v>
       </c>
       <c r="B83" t="n">
-        <v>172.1919555664062</v>
+        <v>157.152573</v>
       </c>
       <c r="C83" t="n">
-        <v>1.512298583984375</v>
+        <v>6.010742000000022</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>172.9827117919922</v>
+        <v>162.849014</v>
       </c>
       <c r="B84" t="n">
-        <v>173.7042541503906</v>
+        <v>163.163315</v>
       </c>
       <c r="C84" t="n">
-        <v>-0.7215423583984375</v>
+        <v>-0.3143010000000004</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>175.9084014892578</v>
+        <v>162.622803</v>
       </c>
       <c r="B85" t="n">
-        <v>172.9827117919922</v>
+        <v>162.849014</v>
       </c>
       <c r="C85" t="n">
-        <v>2.925689697265625</v>
+        <v>-0.2262110000000064</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>176.9956817626953</v>
+        <v>162.150711</v>
       </c>
       <c r="B86" t="n">
-        <v>175.9084014892578</v>
+        <v>162.622803</v>
       </c>
       <c r="C86" t="n">
-        <v>1.0872802734375</v>
+        <v>-0.4720920000000035</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>173.4571533203125</v>
+        <v>162.19989</v>
       </c>
       <c r="B87" t="n">
-        <v>176.9956817626953</v>
+        <v>162.150711</v>
       </c>
       <c r="C87" t="n">
-        <v>-3.538528442382812</v>
+        <v>0.04917900000000941</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>171.9152069091797</v>
+        <v>166.448654</v>
       </c>
       <c r="B88" t="n">
-        <v>173.4571533203125</v>
+        <v>162.19989</v>
       </c>
       <c r="C88" t="n">
-        <v>-1.541946411132812</v>
+        <v>4.248763999999994</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>172.7652130126953</v>
+        <v>165.711014</v>
       </c>
       <c r="B89" t="n">
-        <v>171.9152069091797</v>
+        <v>166.448654</v>
       </c>
       <c r="C89" t="n">
-        <v>0.850006103515625</v>
+        <v>-0.737639999999999</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>174.0403289794922</v>
+        <v>169.261475</v>
       </c>
       <c r="B90" t="n">
-        <v>172.7652130126953</v>
+        <v>165.711014</v>
       </c>
       <c r="C90" t="n">
-        <v>1.275115966796875</v>
+        <v>3.550460999999984</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>169.9680328369141</v>
+        <v>170.333496</v>
       </c>
       <c r="B91" t="n">
-        <v>174.0403289794922</v>
+        <v>169.261475</v>
       </c>
       <c r="C91" t="n">
-        <v>-4.072296142578125</v>
+        <v>1.072021000000007</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>168.4557647705078</v>
+        <v>170.176102</v>
       </c>
       <c r="B92" t="n">
-        <v>169.9680328369141</v>
+        <v>170.333496</v>
       </c>
       <c r="C92" t="n">
-        <v>-1.51226806640625</v>
+        <v>-0.1573940000000107</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>168.7127532958984</v>
+        <v>171.671066</v>
       </c>
       <c r="B93" t="n">
-        <v>168.4557647705078</v>
+        <v>170.176102</v>
       </c>
       <c r="C93" t="n">
-        <v>0.2569885253905966</v>
+        <v>1.49496400000001</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>169.2267456054688</v>
+        <v>171.277634</v>
       </c>
       <c r="B94" t="n">
-        <v>168.7127532958984</v>
+        <v>171.671066</v>
       </c>
       <c r="C94" t="n">
-        <v>0.5139923095703409</v>
+        <v>-0.39343199999999</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>171.7372894287109</v>
+        <v>168.691025</v>
       </c>
       <c r="B95" t="n">
-        <v>169.2267456054688</v>
+        <v>171.277634</v>
       </c>
       <c r="C95" t="n">
-        <v>2.510543823242188</v>
+        <v>-2.58660900000001</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>170.4029388427734</v>
+        <v>164.806168</v>
       </c>
       <c r="B96" t="n">
-        <v>171.7372894287109</v>
+        <v>168.691025</v>
       </c>
       <c r="C96" t="n">
-        <v>-1.3343505859375</v>
+        <v>-3.884856999999982</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>171.6483764648438</v>
+        <v>164.471771</v>
       </c>
       <c r="B97" t="n">
-        <v>170.4029388427734</v>
+        <v>164.806168</v>
       </c>
       <c r="C97" t="n">
-        <v>1.245437622070312</v>
+        <v>-0.334397000000024</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>172.8838653564453</v>
+        <v>164.76683</v>
       </c>
       <c r="B98" t="n">
-        <v>171.6483764648438</v>
+        <v>164.471771</v>
       </c>
       <c r="C98" t="n">
-        <v>1.235488891601562</v>
+        <v>0.2950590000000091</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>175.4339752197266</v>
+        <v>167.225616</v>
       </c>
       <c r="B99" t="n">
-        <v>172.8838653564453</v>
+        <v>164.76683</v>
       </c>
       <c r="C99" t="n">
-        <v>2.55010986328125</v>
+        <v>2.458786000000003</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>176.9166107177734</v>
+        <v>160.921326</v>
       </c>
       <c r="B100" t="n">
-        <v>175.4339752197266</v>
+        <v>167.225616</v>
       </c>
       <c r="C100" t="n">
-        <v>1.482635498046875</v>
+        <v>-6.304290000000009</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>176.3235778808594</v>
+        <v>158.718262</v>
       </c>
       <c r="B101" t="n">
-        <v>176.9166107177734</v>
+        <v>160.921326</v>
       </c>
       <c r="C101" t="n">
-        <v>-0.5930328369140625</v>
+        <v>-2.203063999999983</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>177.7172241210938</v>
+        <v>156.289017</v>
       </c>
       <c r="B102" t="n">
-        <v>176.3235778808594</v>
+        <v>158.718262</v>
       </c>
       <c r="C102" t="n">
-        <v>1.393646240234375</v>
+        <v>-2.429245000000009</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>178.61669921875</v>
+        <v>154.626907</v>
       </c>
       <c r="B103" t="n">
-        <v>177.7172241210938</v>
+        <v>156.289017</v>
       </c>
       <c r="C103" t="n">
-        <v>0.89947509765625</v>
+        <v>-1.662110000000013</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>176.7782440185547</v>
+        <v>155.354691</v>
       </c>
       <c r="B104" t="n">
-        <v>178.61669921875</v>
+        <v>154.626907</v>
       </c>
       <c r="C104" t="n">
-        <v>-1.838455200195312</v>
+        <v>0.727784000000014</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>176.6497192382812</v>
+        <v>153.240128</v>
       </c>
       <c r="B105" t="n">
-        <v>176.7782440185547</v>
+        <v>155.354691</v>
       </c>
       <c r="C105" t="n">
-        <v>-0.1285247802734375</v>
+        <v>-2.114563000000004</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>175.097900390625</v>
+        <v>151.981232</v>
       </c>
       <c r="B106" t="n">
-        <v>176.6497192382812</v>
+        <v>153.240128</v>
       </c>
       <c r="C106" t="n">
-        <v>-1.55181884765625</v>
+        <v>-1.258895999999993</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>173.8030853271484</v>
+        <v>153.38768</v>
       </c>
       <c r="B107" t="n">
-        <v>175.097900390625</v>
+        <v>151.981232</v>
       </c>
       <c r="C107" t="n">
-        <v>-1.294815063476562</v>
+        <v>1.406447999999983</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>173.427490234375</v>
+        <v>151.912415</v>
       </c>
       <c r="B108" t="n">
-        <v>173.8030853271484</v>
+        <v>153.38768</v>
       </c>
       <c r="C108" t="n">
-        <v>-0.3755950927734375</v>
+        <v>-1.475264999999979</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>170.8773803710938</v>
+        <v>154.774414</v>
       </c>
       <c r="B109" t="n">
-        <v>173.427490234375</v>
+        <v>151.912415</v>
       </c>
       <c r="C109" t="n">
-        <v>-2.55010986328125</v>
+        <v>2.861998999999997</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>170.9959869384766</v>
+        <v>160.734451</v>
       </c>
       <c r="B110" t="n">
-        <v>170.8773803710938</v>
+        <v>154.774414</v>
       </c>
       <c r="C110" t="n">
-        <v>0.1186065673828125</v>
+        <v>5.960037</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>171.4308929443359</v>
+        <v>151.302628</v>
       </c>
       <c r="B111" t="n">
-        <v>170.9959869384766</v>
+        <v>160.734451</v>
       </c>
       <c r="C111" t="n">
-        <v>0.434906005859375</v>
+        <v>-9.431823000000009</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>169.1180267333984</v>
+        <v>152.748383</v>
       </c>
       <c r="B112" t="n">
-        <v>171.4308929443359</v>
+        <v>151.302628</v>
       </c>
       <c r="C112" t="n">
-        <v>-2.3128662109375</v>
+        <v>1.445754999999991</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>164.9567718505859</v>
+        <v>149.856857</v>
       </c>
       <c r="B113" t="n">
-        <v>169.1180267333984</v>
+        <v>152.748383</v>
       </c>
       <c r="C113" t="n">
-        <v>-4.1612548828125</v>
+        <v>-2.891525999999999</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>166.2713623046875</v>
+        <v>148.214462</v>
       </c>
       <c r="B114" t="n">
-        <v>164.9567718505859</v>
+        <v>149.856857</v>
       </c>
       <c r="C114" t="n">
-        <v>1.314590454101562</v>
+        <v>-1.642394999999993</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>168.3173675537109</v>
+        <v>151.932083</v>
       </c>
       <c r="B115" t="n">
-        <v>166.2713623046875</v>
+        <v>148.214462</v>
       </c>
       <c r="C115" t="n">
-        <v>2.046005249023438</v>
+        <v>3.717621000000008</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>168.7918395996094</v>
+        <v>154.31218</v>
       </c>
       <c r="B116" t="n">
-        <v>168.3173675537109</v>
+        <v>151.932083</v>
       </c>
       <c r="C116" t="n">
-        <v>0.4744720458984375</v>
+        <v>2.380097000000006</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>171.9547424316406</v>
+        <v>151.184631</v>
       </c>
       <c r="B117" t="n">
-        <v>168.7918395996094</v>
+        <v>154.31218</v>
       </c>
       <c r="C117" t="n">
-        <v>3.16290283203125</v>
+        <v>-3.127549000000016</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>175.5130615234375</v>
+        <v>150.220795</v>
       </c>
       <c r="B118" t="n">
-        <v>171.9547424316406</v>
+        <v>151.184631</v>
       </c>
       <c r="C118" t="n">
-        <v>3.558319091796875</v>
+        <v>-0.9638359999999864</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>174.6037139892578</v>
+        <v>147.948868</v>
       </c>
       <c r="B119" t="n">
-        <v>175.5130615234375</v>
+        <v>150.220795</v>
       </c>
       <c r="C119" t="n">
-        <v>-0.9093475341796875</v>
+        <v>-2.271927000000005</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>177.1538391113281</v>
+        <v>148.283264</v>
       </c>
       <c r="B120" t="n">
-        <v>174.6037139892578</v>
+        <v>147.948868</v>
       </c>
       <c r="C120" t="n">
-        <v>2.550125122070312</v>
+        <v>0.3343959999999981</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>179.7138214111328</v>
+        <v>149.256943</v>
       </c>
       <c r="B121" t="n">
-        <v>177.1538391113281</v>
+        <v>148.283264</v>
       </c>
       <c r="C121" t="n">
-        <v>2.559982299804688</v>
+        <v>0.9736790000000042</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>180.7714233398437</v>
+        <v>147.368622</v>
       </c>
       <c r="B122" t="n">
-        <v>179.7138214111328</v>
+        <v>149.256943</v>
       </c>
       <c r="C122" t="n">
-        <v>1.057601928710881</v>
+        <v>-1.888321000000019</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>180.2969818115234</v>
+        <v>140.130005</v>
       </c>
       <c r="B123" t="n">
-        <v>180.7714233398437</v>
+        <v>147.368622</v>
       </c>
       <c r="C123" t="n">
-        <v>-0.4744415283202557</v>
+        <v>-7.238616999999977</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>184.4834747314453</v>
+        <v>135.920593</v>
       </c>
       <c r="B124" t="n">
-        <v>180.2969818115234</v>
+        <v>140.130005</v>
       </c>
       <c r="C124" t="n">
-        <v>4.186492919921875</v>
+        <v>-4.209412000000015</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>182.8999633789062</v>
+        <v>140.10051</v>
       </c>
       <c r="B125" t="n">
-        <v>184.4834747314453</v>
+        <v>135.920593</v>
       </c>
       <c r="C125" t="n">
-        <v>-1.583511352539062</v>
+        <v>4.179917000000017</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>185.5128326416016</v>
+        <v>143.690308</v>
       </c>
       <c r="B126" t="n">
-        <v>182.8999633789062</v>
+        <v>140.10051</v>
       </c>
       <c r="C126" t="n">
-        <v>2.612869262695341</v>
+        <v>3.589797999999973</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>186.0769348144532</v>
+        <v>143.985352</v>
       </c>
       <c r="B127" t="n">
-        <v>185.5128326416016</v>
+        <v>143.690308</v>
       </c>
       <c r="C127" t="n">
-        <v>0.5641021728515625</v>
+        <v>0.2950440000000185</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>187.7594451904297</v>
+        <v>143.031372</v>
       </c>
       <c r="B128" t="n">
-        <v>186.0769348144532</v>
+        <v>143.985352</v>
       </c>
       <c r="C128" t="n">
-        <v>1.682510375976534</v>
+        <v>-0.9539800000000014</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>187.7397003173828</v>
+        <v>137.779404</v>
       </c>
       <c r="B129" t="n">
-        <v>187.7594451904297</v>
+        <v>143.031372</v>
       </c>
       <c r="C129" t="n">
-        <v>-0.019744873046875</v>
+        <v>-5.251968000000005</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>189.4815826416016</v>
+        <v>138.103973</v>
       </c>
       <c r="B130" t="n">
-        <v>187.7397003173828</v>
+        <v>137.779404</v>
       </c>
       <c r="C130" t="n">
-        <v>1.741882324218778</v>
+        <v>0.3245689999999968</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>188.6798858642578</v>
+        <v>136.687729</v>
       </c>
       <c r="B131" t="n">
-        <v>189.4815826416016</v>
+        <v>138.103973</v>
       </c>
       <c r="C131" t="n">
-        <v>-0.8016967773437784</v>
+        <v>-1.416244000000006</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>189.3429870605469</v>
+        <v>136.058273</v>
       </c>
       <c r="B132" t="n">
-        <v>188.6798858642578</v>
+        <v>136.687729</v>
       </c>
       <c r="C132" t="n">
-        <v>0.6631011962890625</v>
+        <v>-0.6294559999999763</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>188.0168151855469</v>
+        <v>140.631592</v>
       </c>
       <c r="B133" t="n">
-        <v>189.3429870605469</v>
+        <v>136.058273</v>
       </c>
       <c r="C133" t="n">
-        <v>-1.326171875</v>
+        <v>4.573318999999998</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>187.8386383056641</v>
+        <v>136.097626</v>
       </c>
       <c r="B134" t="n">
-        <v>188.0168151855469</v>
+        <v>140.631592</v>
       </c>
       <c r="C134" t="n">
-        <v>-0.1781768798827841</v>
+        <v>-4.533966000000021</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>188.4423522949219</v>
+        <v>140.061172</v>
       </c>
       <c r="B135" t="n">
-        <v>187.8386383056641</v>
+        <v>136.097626</v>
       </c>
       <c r="C135" t="n">
-        <v>0.6037139892578125</v>
+        <v>3.963546000000008</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>187.4229583740234</v>
+        <v>141.379044</v>
       </c>
       <c r="B136" t="n">
-        <v>188.4423522949219</v>
+        <v>140.061172</v>
       </c>
       <c r="C136" t="n">
-        <v>-1.019393920898466</v>
+        <v>1.317871999999994</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>187.9969940185547</v>
+        <v>141.487244</v>
       </c>
       <c r="B137" t="n">
-        <v>187.4229583740234</v>
+        <v>141.379044</v>
       </c>
       <c r="C137" t="n">
-        <v>0.57403564453125</v>
+        <v>0.1082000000000107</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>189.2737274169922</v>
+        <v>141.024963</v>
       </c>
       <c r="B138" t="n">
-        <v>187.9969940185547</v>
+        <v>141.487244</v>
       </c>
       <c r="C138" t="n">
-        <v>1.2767333984375</v>
+        <v>-0.4622809999999902</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>187.4823455810547</v>
+        <v>144.840973</v>
       </c>
       <c r="B139" t="n">
-        <v>189.2737274169922</v>
+        <v>141.024963</v>
       </c>
       <c r="C139" t="n">
-        <v>-1.7913818359375</v>
+        <v>3.816009999999977</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>191.4313201904297</v>
+        <v>146.985046</v>
       </c>
       <c r="B140" t="n">
-        <v>187.4823455810547</v>
+        <v>144.840973</v>
       </c>
       <c r="C140" t="n">
-        <v>3.948974609375</v>
+        <v>2.14407300000002</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>190.3426361083984</v>
+        <v>149.827362</v>
       </c>
       <c r="B141" t="n">
-        <v>191.4313201904297</v>
+        <v>146.985046</v>
       </c>
       <c r="C141" t="n">
-        <v>-1.08868408203125</v>
+        <v>2.842315999999983</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>192.2725830078125</v>
+        <v>146.886688</v>
       </c>
       <c r="B142" t="n">
-        <v>190.3426361083984</v>
+        <v>149.827362</v>
       </c>
       <c r="C142" t="n">
-        <v>1.929946899414062</v>
+        <v>-2.940674000000001</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>193.6977844238281</v>
+        <v>142.411743</v>
       </c>
       <c r="B143" t="n">
-        <v>192.2725830078125</v>
+        <v>146.886688</v>
       </c>
       <c r="C143" t="n">
-        <v>1.425201416015568</v>
+        <v>-4.474944999999991</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>191.1937713623047</v>
+        <v>153.171356</v>
       </c>
       <c r="B144" t="n">
-        <v>193.6977844238281</v>
+        <v>142.411743</v>
       </c>
       <c r="C144" t="n">
-        <v>-2.504013061523381</v>
+        <v>10.759613</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>192.7080688476563</v>
+        <v>150.810867</v>
       </c>
       <c r="B145" t="n">
-        <v>191.1937713623047</v>
+        <v>153.171356</v>
       </c>
       <c r="C145" t="n">
-        <v>1.514297485351591</v>
+        <v>-2.360489000000001</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>195.9246520996093</v>
+        <v>148.165237</v>
       </c>
       <c r="B146" t="n">
-        <v>192.7080688476563</v>
+        <v>150.810867</v>
       </c>
       <c r="C146" t="n">
-        <v>3.21658325195304</v>
+        <v>-2.645630000000011</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>196.0731048583984</v>
+        <v>142.637955</v>
       </c>
       <c r="B147" t="n">
-        <v>195.9246520996093</v>
+        <v>148.165237</v>
       </c>
       <c r="C147" t="n">
-        <v>0.1484527587891193</v>
+        <v>-5.527281999999985</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>195.5386657714844</v>
+        <v>136.589401</v>
       </c>
       <c r="B148" t="n">
-        <v>196.0731048583984</v>
+        <v>142.637955</v>
       </c>
       <c r="C148" t="n">
-        <v>-0.5344390869140341</v>
+        <v>-6.048553999999996</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>193.8759307861328</v>
+        <v>136.323395</v>
       </c>
       <c r="B149" t="n">
-        <v>195.5386657714844</v>
+        <v>136.589401</v>
       </c>
       <c r="C149" t="n">
-        <v>-1.662734985351591</v>
+        <v>-0.2660060000000044</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>194.9151306152344</v>
+        <v>136.855331</v>
       </c>
       <c r="B150" t="n">
-        <v>193.8759307861328</v>
+        <v>136.323395</v>
       </c>
       <c r="C150" t="n">
-        <v>1.039199829101591</v>
+        <v>0.5319360000000017</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>192.8268280029297</v>
+        <v>137.426758</v>
       </c>
       <c r="B151" t="n">
-        <v>194.9151306152344</v>
+        <v>136.855331</v>
       </c>
       <c r="C151" t="n">
-        <v>-2.088302612304716</v>
+        <v>0.5714269999999999</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>192.6783447265625</v>
+        <v>132.865585</v>
       </c>
       <c r="B152" t="n">
-        <v>192.8268280029297</v>
+        <v>137.426758</v>
       </c>
       <c r="C152" t="n">
-        <v>-0.1484832763671875</v>
+        <v>-4.561172999999997</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>191.6094512939453</v>
+        <v>144.68721</v>
       </c>
       <c r="B153" t="n">
-        <v>192.6783447265625</v>
+        <v>132.865585</v>
       </c>
       <c r="C153" t="n">
-        <v>-1.068893432617188</v>
+        <v>11.82162499999998</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>191.0651092529297</v>
+        <v>147.475128</v>
       </c>
       <c r="B154" t="n">
-        <v>191.6094512939453</v>
+        <v>144.68721</v>
       </c>
       <c r="C154" t="n">
-        <v>-0.544342041015625</v>
+        <v>2.787918000000019</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>191.1640930175781</v>
+        <v>146.076279</v>
       </c>
       <c r="B155" t="n">
-        <v>191.0651092529297</v>
+        <v>147.475128</v>
       </c>
       <c r="C155" t="n">
-        <v>0.09898376464838066</v>
+        <v>-1.398849000000013</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>191.5896911621093</v>
+        <v>147.810104</v>
       </c>
       <c r="B156" t="n">
-        <v>191.1640930175781</v>
+        <v>146.076279</v>
       </c>
       <c r="C156" t="n">
-        <v>0.42559814453125</v>
+        <v>1.733824999999996</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>190.5504608154297</v>
+        <v>146.578644</v>
       </c>
       <c r="B157" t="n">
-        <v>191.5896911621093</v>
+        <v>147.810104</v>
       </c>
       <c r="C157" t="n">
-        <v>-1.039230346679631</v>
+        <v>-1.231459999999998</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>183.7313079833984</v>
+        <v>148.47998</v>
       </c>
       <c r="B158" t="n">
-        <v>190.5504608154297</v>
+        <v>146.578644</v>
       </c>
       <c r="C158" t="n">
-        <v>-6.81915283203125</v>
+        <v>1.901336000000015</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>182.3555908203125</v>
+        <v>149.041534</v>
       </c>
       <c r="B159" t="n">
-        <v>183.7313079833984</v>
+        <v>148.47998</v>
       </c>
       <c r="C159" t="n">
-        <v>-1.375717163085938</v>
+        <v>0.561554000000001</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>180.0396728515625</v>
+        <v>145.810242</v>
       </c>
       <c r="B160" t="n">
-        <v>182.3555908203125</v>
+        <v>149.041534</v>
       </c>
       <c r="C160" t="n">
-        <v>-2.31591796875</v>
+        <v>-3.231292000000025</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>179.317138671875</v>
+        <v>147.947998</v>
       </c>
       <c r="B161" t="n">
-        <v>180.0396728515625</v>
+        <v>145.810242</v>
       </c>
       <c r="C161" t="n">
-        <v>-0.7225341796875</v>
+        <v>2.137756000000024</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>183.6521301269531</v>
+        <v>148.824768</v>
       </c>
       <c r="B162" t="n">
-        <v>179.317138671875</v>
+        <v>147.947998</v>
       </c>
       <c r="C162" t="n">
-        <v>4.334991455078125</v>
+        <v>0.8767699999999934</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>183.2364349365234</v>
+        <v>145.908798</v>
       </c>
       <c r="B163" t="n">
-        <v>183.6521301269531</v>
+        <v>148.824768</v>
       </c>
       <c r="C163" t="n">
-        <v>-0.4156951904296875</v>
+        <v>-2.915970000000016</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>184.2756805419922</v>
+        <v>142.076614</v>
       </c>
       <c r="B164" t="n">
-        <v>183.2364349365234</v>
+        <v>145.908798</v>
       </c>
       <c r="C164" t="n">
-        <v>1.03924560546875</v>
+        <v>-3.832183999999984</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>183.6818237304688</v>
+        <v>139.07193</v>
       </c>
       <c r="B165" t="n">
-        <v>184.2756805419922</v>
+        <v>142.076614</v>
       </c>
       <c r="C165" t="n">
-        <v>-0.5938568115234375</v>
+        <v>-3.004683999999997</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>184.0084381103516</v>
+        <v>145.830002</v>
       </c>
       <c r="B166" t="n">
-        <v>183.6818237304688</v>
+        <v>139.07193</v>
       </c>
       <c r="C166" t="n">
-        <v>0.3266143798828409</v>
+        <v>6.758071999999999</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>181.7419891357422</v>
+        <v>146.105835</v>
       </c>
       <c r="B167" t="n">
-        <v>184.0084381103516</v>
+        <v>145.830002</v>
       </c>
       <c r="C167" t="n">
-        <v>-2.266448974609432</v>
+        <v>0.2758330000000058</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>180.8017425537109</v>
+        <v>145.613235</v>
       </c>
       <c r="B168" t="n">
-        <v>181.7419891357422</v>
+        <v>146.105835</v>
       </c>
       <c r="C168" t="n">
-        <v>-0.94024658203125</v>
+        <v>-0.4926000000000101</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>186.6905670166016</v>
+        <v>144.450775</v>
       </c>
       <c r="B169" t="n">
-        <v>180.8017425537109</v>
+        <v>145.613235</v>
       </c>
       <c r="C169" t="n">
-        <v>5.888824462890682</v>
+        <v>-1.16246000000001</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>189.5904388427734</v>
+        <v>140.786087</v>
       </c>
       <c r="B170" t="n">
-        <v>186.6905670166016</v>
+        <v>144.450775</v>
       </c>
       <c r="C170" t="n">
-        <v>2.899871826171847</v>
+        <v>-3.664687999999984</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>191.896484375</v>
+        <v>138.845352</v>
       </c>
       <c r="B171" t="n">
-        <v>189.5904388427734</v>
+        <v>140.786087</v>
       </c>
       <c r="C171" t="n">
-        <v>2.306045532226562</v>
+        <v>-1.940735000000018</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>193.1732177734375</v>
+        <v>140.529892</v>
       </c>
       <c r="B172" t="n">
-        <v>191.896484375</v>
+        <v>138.845352</v>
       </c>
       <c r="C172" t="n">
-        <v>1.2767333984375</v>
+        <v>1.684539999999998</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>192.5001983642578</v>
+        <v>140.047195</v>
       </c>
       <c r="B173" t="n">
-        <v>193.1732177734375</v>
+        <v>140.529892</v>
       </c>
       <c r="C173" t="n">
-        <v>-0.6730194091796875</v>
+        <v>-0.4826970000000017</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>192.173583984375</v>
+        <v>142.34259</v>
       </c>
       <c r="B174" t="n">
-        <v>192.5001983642578</v>
+        <v>140.047195</v>
       </c>
       <c r="C174" t="n">
-        <v>-0.3266143798828125</v>
+        <v>2.295395000000013</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>190.4415893554688</v>
+        <v>143.308014</v>
       </c>
       <c r="B175" t="n">
-        <v>192.173583984375</v>
+        <v>142.34259</v>
       </c>
       <c r="C175" t="n">
-        <v>-1.73199462890625</v>
+        <v>0.9654239999999845</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>189.7586975097656</v>
+        <v>141.081604</v>
       </c>
       <c r="B176" t="n">
-        <v>190.4415893554688</v>
+        <v>143.308014</v>
       </c>
       <c r="C176" t="n">
-        <v>-0.6828918457031818</v>
+        <v>-2.226409999999987</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>186.1066589355469</v>
+        <v>134.471329</v>
       </c>
       <c r="B177" t="n">
-        <v>189.7586975097656</v>
+        <v>141.081604</v>
       </c>
       <c r="C177" t="n">
-        <v>-3.652038574218693</v>
+        <v>-6.610275000000001</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>182.5040588378907</v>
+        <v>132.51088</v>
       </c>
       <c r="B178" t="n">
-        <v>186.1066589355469</v>
+        <v>134.471329</v>
       </c>
       <c r="C178" t="n">
-        <v>-3.602600097656222</v>
+        <v>-1.960449000000011</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>184.9387359619141</v>
+        <v>130.402695</v>
       </c>
       <c r="B179" t="n">
-        <v>182.5040588378907</v>
+        <v>132.51088</v>
       </c>
       <c r="C179" t="n">
-        <v>2.434677124023438</v>
+        <v>-2.108184999999992</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>183.9391632080078</v>
+        <v>130.333755</v>
       </c>
       <c r="B180" t="n">
-        <v>184.9387359619141</v>
+        <v>130.402695</v>
       </c>
       <c r="C180" t="n">
-        <v>-0.9995727539062784</v>
+        <v>-0.06893999999999778</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>185.7503051757812</v>
+        <v>133.43692</v>
       </c>
       <c r="B181" t="n">
-        <v>183.9391632080078</v>
+        <v>130.333755</v>
       </c>
       <c r="C181" t="n">
-        <v>1.811141967773438</v>
+        <v>3.10316499999999</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>187.3536682128907</v>
+        <v>130.264755</v>
       </c>
       <c r="B182" t="n">
-        <v>185.7503051757812</v>
+        <v>133.43692</v>
       </c>
       <c r="C182" t="n">
-        <v>1.603363037109403</v>
+        <v>-3.172164999999978</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>187.4625549316407</v>
+        <v>129.900299</v>
       </c>
       <c r="B183" t="n">
-        <v>187.3536682128907</v>
+        <v>130.264755</v>
       </c>
       <c r="C183" t="n">
-        <v>0.10888671875</v>
+        <v>-0.3644560000000183</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>186.3837585449219</v>
+        <v>128.097488</v>
       </c>
       <c r="B184" t="n">
-        <v>187.4625549316407</v>
+        <v>129.900299</v>
       </c>
       <c r="C184" t="n">
-        <v>-1.07879638671875</v>
+        <v>-1.802810999999991</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>187.1468048095703</v>
+        <v>124.166794</v>
       </c>
       <c r="B185" t="n">
-        <v>186.3837585449219</v>
+        <v>128.097488</v>
       </c>
       <c r="C185" t="n">
-        <v>0.7630462646484091</v>
+        <v>-3.930694000000017</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>185.462158203125</v>
+        <v>127.683731</v>
       </c>
       <c r="B186" t="n">
-        <v>187.1468048095703</v>
+        <v>124.166794</v>
       </c>
       <c r="C186" t="n">
-        <v>-1.684646606445312</v>
+        <v>3.516937000000013</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>183.3711547851562</v>
+        <v>127.998978</v>
       </c>
       <c r="B187" t="n">
-        <v>185.462158203125</v>
+        <v>127.683731</v>
       </c>
       <c r="C187" t="n">
-        <v>-2.091003417968778</v>
+        <v>0.3152469999999994</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>182.4891815185547</v>
+        <v>123.211205</v>
       </c>
       <c r="B188" t="n">
-        <v>183.3711547851562</v>
+        <v>127.998978</v>
       </c>
       <c r="C188" t="n">
-        <v>-0.8819732666015341</v>
+        <v>-4.787773000000001</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>182.2018127441406</v>
+        <v>124.482033</v>
       </c>
       <c r="B189" t="n">
-        <v>182.4891815185547</v>
+        <v>123.211205</v>
       </c>
       <c r="C189" t="n">
-        <v>-0.2873687744140625</v>
+        <v>1.270828000000009</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>180.665771484375</v>
+        <v>123.161949</v>
       </c>
       <c r="B190" t="n">
-        <v>182.2018127441406</v>
+        <v>124.482033</v>
       </c>
       <c r="C190" t="n">
-        <v>-1.536041259765625</v>
+        <v>-1.320083999999994</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>179.9225616455078</v>
+        <v>127.693565</v>
       </c>
       <c r="B191" t="n">
-        <v>180.665771484375</v>
+        <v>123.161949</v>
       </c>
       <c r="C191" t="n">
-        <v>-0.7432098388671875</v>
+        <v>4.531616</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>180.6756744384766</v>
+        <v>128.215729</v>
       </c>
       <c r="B192" t="n">
-        <v>179.9225616455078</v>
+        <v>127.693565</v>
       </c>
       <c r="C192" t="n">
-        <v>0.75311279296875</v>
+        <v>0.5221640000000036</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>182.7072296142578</v>
+        <v>128.787125</v>
       </c>
       <c r="B193" t="n">
-        <v>180.6756744384766</v>
+        <v>128.215729</v>
       </c>
       <c r="C193" t="n">
-        <v>2.031555175781278</v>
+        <v>0.5713959999999929</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>180.8739013671875</v>
+        <v>131.506104</v>
       </c>
       <c r="B194" t="n">
-        <v>182.7072296142578</v>
+        <v>128.787125</v>
       </c>
       <c r="C194" t="n">
-        <v>-1.833328247070312</v>
+        <v>2.71897899999999</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>179.5261688232422</v>
+        <v>131.427261</v>
       </c>
       <c r="B195" t="n">
-        <v>180.8739013671875</v>
+        <v>131.506104</v>
       </c>
       <c r="C195" t="n">
-        <v>-1.347732543945341</v>
+        <v>-0.07884300000000621</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>180.98291015625</v>
+        <v>132.757187</v>
       </c>
       <c r="B196" t="n">
-        <v>179.5261688232422</v>
+        <v>131.427261</v>
       </c>
       <c r="C196" t="n">
-        <v>1.456741333007841</v>
+        <v>1.329926</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>179.7838134765625</v>
+        <v>133.919662</v>
       </c>
       <c r="B197" t="n">
-        <v>180.98291015625</v>
+        <v>132.757187</v>
       </c>
       <c r="C197" t="n">
-        <v>-1.199096679687528</v>
+        <v>1.162475000000001</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>179.1198577880859</v>
+        <v>133.200516</v>
       </c>
       <c r="B198" t="n">
-        <v>179.7838134765625</v>
+        <v>133.919662</v>
       </c>
       <c r="C198" t="n">
-        <v>-0.6639556884765625</v>
+        <v>-0.719145999999995</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>178.0396881103515</v>
+        <v>133.259613</v>
       </c>
       <c r="B199" t="n">
-        <v>179.1198577880859</v>
+        <v>133.200516</v>
       </c>
       <c r="C199" t="n">
-        <v>-1.080169677734403</v>
+        <v>0.05909700000000839</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>173.5208282470703</v>
+        <v>135.820969</v>
       </c>
       <c r="B200" t="n">
-        <v>178.0396881103515</v>
+        <v>133.259613</v>
       </c>
       <c r="C200" t="n">
-        <v>-4.518859863281222</v>
+        <v>2.561355999999989</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>168.5857086181641</v>
+        <v>139.012802</v>
       </c>
       <c r="B201" t="n">
-        <v>173.5208282470703</v>
+        <v>135.820969</v>
       </c>
       <c r="C201" t="n">
-        <v>-4.93511962890625</v>
+        <v>3.191833000000003</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>167.5947418212891</v>
+        <v>140.411743</v>
       </c>
       <c r="B202" t="n">
-        <v>168.5857086181641</v>
+        <v>139.012802</v>
       </c>
       <c r="C202" t="n">
-        <v>-0.990966796875</v>
+        <v>1.398941000000008</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>167.4758148193359</v>
+        <v>139.751663</v>
       </c>
       <c r="B203" t="n">
-        <v>167.5947418212891</v>
+        <v>140.411743</v>
       </c>
       <c r="C203" t="n">
-        <v>-0.118927001953125</v>
+        <v>-0.6600799999999936</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>169.1902313232422</v>
+        <v>141.82048</v>
       </c>
       <c r="B204" t="n">
-        <v>167.4758148193359</v>
+        <v>139.751663</v>
       </c>
       <c r="C204" t="n">
-        <v>1.71441650390625</v>
+        <v>2.068816999999996</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>171.1920013427734</v>
+        <v>143.761185</v>
       </c>
       <c r="B205" t="n">
-        <v>169.1902313232422</v>
+        <v>141.82048</v>
       </c>
       <c r="C205" t="n">
-        <v>2.00177001953125</v>
+        <v>1.940705000000008</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>171.6676788330078</v>
+        <v>140.874725</v>
       </c>
       <c r="B206" t="n">
-        <v>171.1920013427734</v>
+        <v>143.761185</v>
       </c>
       <c r="C206" t="n">
-        <v>0.475677490234375</v>
+        <v>-2.88646</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>169.5866241455078</v>
+        <v>142.145554</v>
       </c>
       <c r="B207" t="n">
-        <v>171.6676788330078</v>
+        <v>140.874725</v>
       </c>
       <c r="C207" t="n">
-        <v>-2.0810546875</v>
+        <v>1.270828999999992</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>171.4397583007812</v>
+        <v>143.268646</v>
       </c>
       <c r="B208" t="n">
-        <v>169.5866241455078</v>
+        <v>142.145554</v>
       </c>
       <c r="C208" t="n">
-        <v>1.853134155273438</v>
+        <v>1.123091999999986</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>171.0631713867188</v>
+        <v>148.578491</v>
       </c>
       <c r="B209" t="n">
-        <v>171.4397583007812</v>
+        <v>143.268646</v>
       </c>
       <c r="C209" t="n">
-        <v>-0.3765869140625</v>
+        <v>5.309845000000024</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>172.1532592773438</v>
+        <v>152.203827</v>
       </c>
       <c r="B210" t="n">
-        <v>171.0631713867188</v>
+        <v>148.578491</v>
       </c>
       <c r="C210" t="n">
-        <v>1.090087890625028</v>
+        <v>3.625335999999976</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>174.4919891357422</v>
+        <v>149.47496</v>
       </c>
       <c r="B211" t="n">
-        <v>172.1532592773438</v>
+        <v>152.203827</v>
       </c>
       <c r="C211" t="n">
-        <v>2.338729858398409</v>
+        <v>-2.72886699999998</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>177.0586242675781</v>
+        <v>152.351547</v>
       </c>
       <c r="B212" t="n">
-        <v>174.4919891357422</v>
+        <v>149.47496</v>
       </c>
       <c r="C212" t="n">
-        <v>2.566635131835938</v>
+        <v>2.876587000000001</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>169.8244323730469</v>
+        <v>149.662155</v>
       </c>
       <c r="B213" t="n">
-        <v>177.0586242675781</v>
+        <v>152.351547</v>
       </c>
       <c r="C213" t="n">
-        <v>-7.23419189453125</v>
+        <v>-2.689391999999998</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>170.7262573242188</v>
+        <v>148.627777</v>
       </c>
       <c r="B214" t="n">
-        <v>169.8244323730469</v>
+        <v>149.662155</v>
       </c>
       <c r="C214" t="n">
-        <v>0.901824951171875</v>
+        <v>-1.034378000000004</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>169.3091430664062</v>
+        <v>148.992798</v>
       </c>
       <c r="B215" t="n">
-        <v>170.7262573242188</v>
+        <v>148.627777</v>
       </c>
       <c r="C215" t="n">
-        <v>-1.4171142578125</v>
+        <v>0.3650209999999845</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>168.179443359375</v>
+        <v>151.794891</v>
       </c>
       <c r="B216" t="n">
-        <v>169.3091430664062</v>
+        <v>148.992798</v>
       </c>
       <c r="C216" t="n">
-        <v>-1.12969970703125</v>
+        <v>2.802093000000013</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>171.7469482421875</v>
+        <v>151.153549</v>
       </c>
       <c r="B217" t="n">
-        <v>168.179443359375</v>
+        <v>151.794891</v>
       </c>
       <c r="C217" t="n">
-        <v>3.5675048828125</v>
+        <v>-0.6413420000000087</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>169.9334411621094</v>
+        <v>153.255112</v>
       </c>
       <c r="B218" t="n">
-        <v>171.7469482421875</v>
+        <v>151.153549</v>
       </c>
       <c r="C218" t="n">
-        <v>-1.813507080078125</v>
+        <v>2.101562999999999</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>168.4965362548828</v>
+        <v>151.656754</v>
       </c>
       <c r="B219" t="n">
-        <v>169.9334411621094</v>
+        <v>153.255112</v>
       </c>
       <c r="C219" t="n">
-        <v>-1.436904907226562</v>
+        <v>-1.59835799999999</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>167.3172607421875</v>
+        <v>150.512253</v>
       </c>
       <c r="B220" t="n">
-        <v>168.4965362548828</v>
+        <v>151.656754</v>
       </c>
       <c r="C220" t="n">
-        <v>-1.179275512695312</v>
+        <v>-1.14450100000002</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>168.1199493408203</v>
+        <v>146.496597</v>
       </c>
       <c r="B221" t="n">
-        <v>167.3172607421875</v>
+        <v>150.512253</v>
       </c>
       <c r="C221" t="n">
-        <v>0.8026885986328125</v>
+        <v>-4.015655999999979</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>167.2974548339844</v>
+        <v>146.920914</v>
       </c>
       <c r="B222" t="n">
-        <v>168.1199493408203</v>
+        <v>146.496597</v>
       </c>
       <c r="C222" t="n">
-        <v>-0.8224945068359375</v>
+        <v>0.4243170000000021</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>168.0506134033203</v>
+        <v>147.404343</v>
       </c>
       <c r="B223" t="n">
-        <v>167.2974548339844</v>
+        <v>146.920914</v>
       </c>
       <c r="C223" t="n">
-        <v>0.7531585693359659</v>
+        <v>0.483429000000001</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>166.9308013916016</v>
+        <v>144.750275</v>
       </c>
       <c r="B224" t="n">
-        <v>168.0506134033203</v>
+        <v>147.404343</v>
       </c>
       <c r="C224" t="n">
-        <v>-1.119812011718778</v>
+        <v>-2.654068000000024</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>168.1397857666016</v>
+        <v>145.944077</v>
       </c>
       <c r="B225" t="n">
-        <v>166.9308013916016</v>
+        <v>144.750275</v>
       </c>
       <c r="C225" t="n">
-        <v>1.208984375000028</v>
+        <v>1.193802000000005</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>166.266845703125</v>
+        <v>145.440903</v>
       </c>
       <c r="B226" t="n">
-        <v>168.1397857666016</v>
+        <v>145.944077</v>
       </c>
       <c r="C226" t="n">
-        <v>-1.872940063476591</v>
+        <v>-0.5031740000000013</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>173.4613342285156</v>
+        <v>143.368988</v>
       </c>
       <c r="B227" t="n">
-        <v>166.266845703125</v>
+        <v>145.440903</v>
       </c>
       <c r="C227" t="n">
-        <v>7.194488525390625</v>
+        <v>-2.07191499999999</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>174.9577331542969</v>
+        <v>143.960922</v>
       </c>
       <c r="B228" t="n">
-        <v>173.4613342285156</v>
+        <v>143.368988</v>
       </c>
       <c r="C228" t="n">
-        <v>1.49639892578125</v>
+        <v>0.5919340000000091</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>171.132568359375</v>
+        <v>149.012573</v>
       </c>
       <c r="B229" t="n">
-        <v>174.9577331542969</v>
+        <v>143.960922</v>
       </c>
       <c r="C229" t="n">
-        <v>-3.825164794921875</v>
+        <v>5.051650999999993</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>167.8524169921875</v>
+        <v>151.775162</v>
       </c>
       <c r="B230" t="n">
-        <v>171.132568359375</v>
+        <v>149.012573</v>
       </c>
       <c r="C230" t="n">
-        <v>-3.2801513671875</v>
+        <v>2.762588999999991</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>166.48486328125</v>
+        <v>149.574951</v>
       </c>
       <c r="B231" t="n">
-        <v>167.8524169921875</v>
+        <v>151.775162</v>
       </c>
       <c r="C231" t="n">
-        <v>-1.3675537109375</v>
+        <v>-2.200210999999996</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>165.5334777832031</v>
+        <v>150.827972</v>
       </c>
       <c r="B232" t="n">
-        <v>166.48486328125</v>
+        <v>149.574951</v>
       </c>
       <c r="C232" t="n">
-        <v>-0.951385498046875</v>
+        <v>1.25302099999999</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>163.5119018554688</v>
+        <v>148.57843</v>
       </c>
       <c r="B233" t="n">
-        <v>165.5334777832031</v>
+        <v>150.827972</v>
       </c>
       <c r="C233" t="n">
-        <v>-2.021575927734375</v>
+        <v>-2.249541999999991</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>164.3443145751953</v>
+        <v>146.516357</v>
       </c>
       <c r="B234" t="n">
-        <v>163.5119018554688</v>
+        <v>148.57843</v>
       </c>
       <c r="C234" t="n">
-        <v>0.8324127197265625</v>
+        <v>-2.062072999999998</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>165.3947601318359</v>
+        <v>148.460037</v>
       </c>
       <c r="B235" t="n">
-        <v>164.3443145751953</v>
+        <v>146.516357</v>
       </c>
       <c r="C235" t="n">
-        <v>1.050445556640625</v>
+        <v>1.943680000000001</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>167.4956512451172</v>
+        <v>150.551697</v>
       </c>
       <c r="B236" t="n">
-        <v>165.3947601318359</v>
+        <v>148.460037</v>
       </c>
       <c r="C236" t="n">
-        <v>2.10089111328125</v>
+        <v>2.09165999999999</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>168.3578033447266</v>
+        <v>150.946365</v>
       </c>
       <c r="B237" t="n">
-        <v>167.4956512451172</v>
+        <v>150.551697</v>
       </c>
       <c r="C237" t="n">
-        <v>0.8621520996094034</v>
+        <v>0.3946679999999958</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>167.7731323242188</v>
+        <v>153.768188</v>
       </c>
       <c r="B238" t="n">
-        <v>168.3578033447266</v>
+        <v>150.946365</v>
       </c>
       <c r="C238" t="n">
-        <v>-0.5846710205078409</v>
+        <v>2.821823000000023</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>171.9352416992188</v>
+        <v>152.929535</v>
       </c>
       <c r="B239" t="n">
-        <v>167.7731323242188</v>
+        <v>153.768188</v>
       </c>
       <c r="C239" t="n">
-        <v>4.162109375000028</v>
+        <v>-0.8386530000000221</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>168.7938385009765</v>
+        <v>155.297485</v>
       </c>
       <c r="B240" t="n">
-        <v>171.9352416992188</v>
+        <v>152.929535</v>
       </c>
       <c r="C240" t="n">
-        <v>-3.141403198242244</v>
+        <v>2.367950000000008</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>167.7731323242188</v>
+        <v>157.152374</v>
       </c>
       <c r="B241" t="n">
-        <v>168.7938385009765</v>
+        <v>155.297485</v>
       </c>
       <c r="C241" t="n">
-        <v>-1.020706176757784</v>
+        <v>1.854889000000014</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>171.469482421875</v>
+        <v>155.721741</v>
       </c>
       <c r="B242" t="n">
-        <v>167.7731323242188</v>
+        <v>157.152374</v>
       </c>
       <c r="C242" t="n">
-        <v>3.69635009765625</v>
+        <v>-1.430633</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>181.7261505126953</v>
+        <v>156.807022</v>
       </c>
       <c r="B243" t="n">
-        <v>171.469482421875</v>
+        <v>155.721741</v>
       </c>
       <c r="C243" t="n">
-        <v>10.25666809082031</v>
+        <v>1.085280999999981</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>180.0711822509766</v>
+        <v>158.109406</v>
       </c>
       <c r="B244" t="n">
-        <v>181.7261505126953</v>
+        <v>156.807022</v>
       </c>
       <c r="C244" t="n">
-        <v>-1.65496826171875</v>
+        <v>1.302384000000018</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>180.7549591064453</v>
+        <v>156.16571</v>
       </c>
       <c r="B245" t="n">
-        <v>180.0711822509766</v>
+        <v>158.109406</v>
       </c>
       <c r="C245" t="n">
-        <v>0.68377685546875</v>
+        <v>-1.943696000000017</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>181.0919036865234</v>
+        <v>155.544128</v>
       </c>
       <c r="B246" t="n">
-        <v>180.7549591064453</v>
+        <v>156.16571</v>
       </c>
       <c r="C246" t="n">
-        <v>0.336944580078125</v>
+        <v>-0.6215819999999894</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>182.9053955078125</v>
+        <v>158.622467</v>
       </c>
       <c r="B247" t="n">
-        <v>181.0919036865234</v>
+        <v>155.544128</v>
       </c>
       <c r="C247" t="n">
-        <v>1.813491821289062</v>
+        <v>3.078339</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>181.6451721191407</v>
+        <v>160.191208</v>
       </c>
       <c r="B248" t="n">
-        <v>182.9053955078125</v>
+        <v>158.622467</v>
       </c>
       <c r="C248" t="n">
-        <v>-1.260223388671847</v>
+        <v>1.568740999999989</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>184.850341796875</v>
+        <v>162.697266</v>
       </c>
       <c r="B249" t="n">
-        <v>181.6451721191407</v>
+        <v>160.191208</v>
       </c>
       <c r="C249" t="n">
-        <v>3.205169677734347</v>
+        <v>2.506058000000024</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>185.9915161132812</v>
+        <v>163.950317</v>
       </c>
       <c r="B250" t="n">
-        <v>184.850341796875</v>
+        <v>162.697266</v>
       </c>
       <c r="C250" t="n">
-        <v>1.14117431640625</v>
+        <v>1.253050999999999</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>188.2639617919922</v>
+        <v>163.417526</v>
       </c>
       <c r="B251" t="n">
-        <v>185.9915161132812</v>
+        <v>163.950317</v>
       </c>
       <c r="C251" t="n">
-        <v>2.272445678710938</v>
+        <v>-0.5327910000000031</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>188.383041381836</v>
+        <v>161.572495</v>
       </c>
       <c r="B252" t="n">
-        <v>188.2639617919922</v>
+        <v>163.417526</v>
       </c>
       <c r="C252" t="n">
-        <v>0.1190795898438068</v>
+        <v>-1.845031000000006</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>188.4128112792969</v>
+        <v>162.460495</v>
       </c>
       <c r="B253" t="n">
-        <v>188.383041381836</v>
+        <v>161.572495</v>
       </c>
       <c r="C253" t="n">
-        <v>0.02976989746088066</v>
+        <v>0.8880000000000052</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>189.5738525390625</v>
+        <v>159.865601</v>
       </c>
       <c r="B254" t="n">
-        <v>188.4128112792969</v>
+        <v>162.460495</v>
       </c>
       <c r="C254" t="n">
-        <v>1.161041259765625</v>
+        <v>-2.594894000000011</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>190.8737945556641</v>
+        <v>158.652054</v>
       </c>
       <c r="B255" t="n">
-        <v>189.5738525390625</v>
+        <v>159.865601</v>
       </c>
       <c r="C255" t="n">
-        <v>1.299942016601591</v>
+        <v>-1.213547000000005</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>189.4348907470703</v>
+        <v>157.961395</v>
       </c>
       <c r="B256" t="n">
-        <v>190.8737945556641</v>
+        <v>158.652054</v>
       </c>
       <c r="C256" t="n">
-        <v>-1.438903808593778</v>
+        <v>-0.6906589999999824</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>185.4457702636719</v>
+        <v>163.348465</v>
       </c>
       <c r="B257" t="n">
-        <v>189.4348907470703</v>
+        <v>157.961395</v>
       </c>
       <c r="C257" t="n">
-        <v>-3.989120483398438</v>
+        <v>5.387069999999994</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>188.52197265625</v>
+        <v>163.003128</v>
       </c>
       <c r="B258" t="n">
-        <v>185.4457702636719</v>
+        <v>163.348465</v>
       </c>
       <c r="C258" t="n">
-        <v>3.076202392578125</v>
+        <v>-0.3453370000000007</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>188.5318908691407</v>
+        <v>163.022858</v>
       </c>
       <c r="B259" t="n">
-        <v>188.52197265625</v>
+        <v>163.003128</v>
       </c>
       <c r="C259" t="n">
-        <v>0.009918212890653422</v>
+        <v>0.0197300000000098</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>188.8295745849609</v>
+        <v>164.246323</v>
       </c>
       <c r="B260" t="n">
-        <v>188.5318908691407</v>
+        <v>163.022858</v>
       </c>
       <c r="C260" t="n">
-        <v>0.2976837158202841</v>
+        <v>1.223464999999976</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>189.8219299316407</v>
+        <v>165.390839</v>
       </c>
       <c r="B261" t="n">
-        <v>188.8295745849609</v>
+        <v>164.246323</v>
       </c>
       <c r="C261" t="n">
-        <v>0.9923553466797159</v>
+        <v>1.14451600000001</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>190.7745513916016</v>
+        <v>164.423904</v>
       </c>
       <c r="B262" t="n">
-        <v>189.8219299316407</v>
+        <v>165.390839</v>
       </c>
       <c r="C262" t="n">
-        <v>0.9526214599609091</v>
+        <v>-0.9669350000000065</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>192.5408935546875</v>
+        <v>162.815674</v>
       </c>
       <c r="B263" t="n">
-        <v>190.7745513916016</v>
+        <v>164.423904</v>
       </c>
       <c r="C263" t="n">
-        <v>1.766342163085938</v>
+        <v>-1.608229999999992</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>192.8584289550781</v>
+        <v>163.121582</v>
       </c>
       <c r="B264" t="n">
-        <v>192.5408935546875</v>
+        <v>162.815674</v>
       </c>
       <c r="C264" t="n">
-        <v>0.3175354003905682</v>
+        <v>0.3059079999999881</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>194.3667602539062</v>
+        <v>161.582382</v>
       </c>
       <c r="B265" t="n">
-        <v>192.8584289550781</v>
+        <v>163.121582</v>
       </c>
       <c r="C265" t="n">
-        <v>1.508331298828182</v>
+        <v>-1.539199999999994</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>192.9874267578125</v>
+        <v>161.572495</v>
       </c>
       <c r="B266" t="n">
-        <v>194.3667602539062</v>
+        <v>161.582382</v>
       </c>
       <c r="C266" t="n">
-        <v>-1.37933349609375</v>
+        <v>-0.009886999999991986</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>195.3789520263672</v>
+        <v>166.160385</v>
       </c>
       <c r="B267" t="n">
-        <v>192.9874267578125</v>
+        <v>161.572495</v>
       </c>
       <c r="C267" t="n">
-        <v>2.391525268554688</v>
+        <v>4.587889999999987</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>191.6378631591797</v>
+        <v>167.413422</v>
       </c>
       <c r="B268" t="n">
-        <v>195.3789520263672</v>
+        <v>166.160385</v>
       </c>
       <c r="C268" t="n">
-        <v>-3.7410888671875</v>
+        <v>1.253037000000006</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>205.5601806640625</v>
+        <v>167.324646</v>
       </c>
       <c r="B269" t="n">
-        <v>191.6378631591797</v>
+        <v>167.413422</v>
       </c>
       <c r="C269" t="n">
-        <v>13.92231750488281</v>
+        <v>-0.08877599999999575</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>211.4347686767578</v>
+        <v>166.288651</v>
       </c>
       <c r="B270" t="n">
-        <v>205.5601806640625</v>
+        <v>167.324646</v>
       </c>
       <c r="C270" t="n">
-        <v>5.874588012695312</v>
+        <v>-1.035995000000014</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>212.5957946777344</v>
+        <v>165.213196</v>
       </c>
       <c r="B271" t="n">
-        <v>211.4347686767578</v>
+        <v>166.288651</v>
       </c>
       <c r="C271" t="n">
-        <v>1.161026000976591</v>
+        <v>-1.075454999999977</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>210.8592224121093</v>
+        <v>163.575378</v>
       </c>
       <c r="B272" t="n">
-        <v>212.5957946777344</v>
+        <v>165.213196</v>
       </c>
       <c r="C272" t="n">
-        <v>-1.736572265625085</v>
+        <v>-1.63781800000001</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>215.0071258544922</v>
+        <v>171.25148</v>
       </c>
       <c r="B273" t="n">
-        <v>210.8592224121093</v>
+        <v>163.575378</v>
       </c>
       <c r="C273" t="n">
-        <v>4.147903442382869</v>
+        <v>7.676101999999986</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>212.6453857421875</v>
+        <v>171.182404</v>
       </c>
       <c r="B274" t="n">
-        <v>215.0071258544922</v>
+        <v>171.25148</v>
       </c>
       <c r="C274" t="n">
-        <v>-2.361740112304688</v>
+        <v>-0.06907599999999547</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>208.0707702636719</v>
+        <v>169.47551</v>
       </c>
       <c r="B275" t="n">
-        <v>212.6453857421875</v>
+        <v>171.182404</v>
       </c>
       <c r="C275" t="n">
-        <v>-4.574615478515625</v>
+        <v>-1.706893999999977</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>205.8975982666016</v>
+        <v>171.241623</v>
       </c>
       <c r="B276" t="n">
-        <v>208.0707702636719</v>
+        <v>169.47551</v>
       </c>
       <c r="C276" t="n">
-        <v>-2.173171997070256</v>
+        <v>1.76611299999999</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>206.5426177978516</v>
+        <v>171.429077</v>
       </c>
       <c r="B277" t="n">
-        <v>205.8975982666016</v>
+        <v>171.241623</v>
       </c>
       <c r="C277" t="n">
-        <v>0.6450195312499716</v>
+        <v>0.1874540000000025</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>207.4654846191407</v>
+        <v>170.500336</v>
       </c>
       <c r="B278" t="n">
-        <v>206.5426177978516</v>
+        <v>171.429077</v>
       </c>
       <c r="C278" t="n">
-        <v>0.9228668212890625</v>
+        <v>-0.9287410000000023</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>211.6133728027344</v>
+        <v>170.006332</v>
       </c>
       <c r="B279" t="n">
-        <v>207.4654846191407</v>
+        <v>170.500336</v>
       </c>
       <c r="C279" t="n">
-        <v>4.14788818359375</v>
+        <v>-0.4940040000000181</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>212.4568634033203</v>
+        <v>170.006332</v>
       </c>
       <c r="B280" t="n">
-        <v>211.6133728027344</v>
+        <v>170.006332</v>
       </c>
       <c r="C280" t="n">
-        <v>0.8434906005859091</v>
+        <v>0</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>209.0035552978516</v>
+        <v>170.618896</v>
       </c>
       <c r="B281" t="n">
-        <v>212.4568634033203</v>
+        <v>170.006332</v>
       </c>
       <c r="C281" t="n">
-        <v>-3.453308105468722</v>
+        <v>0.6125640000000203</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>215.0865020751953</v>
+        <v>172.950607</v>
       </c>
       <c r="B282" t="n">
-        <v>209.0035552978516</v>
+        <v>170.618896</v>
       </c>
       <c r="C282" t="n">
-        <v>6.082946777343722</v>
+        <v>2.331710999999984</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>218.5794982910156</v>
+        <v>173.05928</v>
       </c>
       <c r="B283" t="n">
-        <v>215.0865020751953</v>
+        <v>172.950607</v>
       </c>
       <c r="C283" t="n">
-        <v>3.492996215820284</v>
+        <v>0.1086730000000102</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>219.8496856689453</v>
+        <v>172.110809</v>
       </c>
       <c r="B284" t="n">
-        <v>218.5794982910156</v>
+        <v>173.05928</v>
       </c>
       <c r="C284" t="n">
-        <v>1.270187377929716</v>
+        <v>-0.9484710000000121</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>224.6029205322266</v>
+        <v>169.502457</v>
       </c>
       <c r="B285" t="n">
-        <v>219.8496856689453</v>
+        <v>172.110809</v>
       </c>
       <c r="C285" t="n">
-        <v>4.75323486328125</v>
+        <v>-2.608351999999996</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>226.0715789794922</v>
+        <v>169.779099</v>
       </c>
       <c r="B286" t="n">
-        <v>224.6029205322266</v>
+        <v>169.502457</v>
       </c>
       <c r="C286" t="n">
-        <v>1.468658447265625</v>
+        <v>0.2766420000000096</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>226.9249572753907</v>
+        <v>170.915314</v>
       </c>
       <c r="B287" t="n">
-        <v>226.0715789794922</v>
+        <v>169.779099</v>
       </c>
       <c r="C287" t="n">
-        <v>0.8533782958984659</v>
+        <v>1.136214999999993</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>231.1919555664062</v>
+        <v>173.326035</v>
       </c>
       <c r="B288" t="n">
-        <v>226.9249572753907</v>
+        <v>170.915314</v>
       </c>
       <c r="C288" t="n">
-        <v>4.266998291015597</v>
+        <v>2.410720999999995</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>225.823486328125</v>
+        <v>175.17363</v>
       </c>
       <c r="B289" t="n">
-        <v>231.1919555664062</v>
+        <v>173.326035</v>
       </c>
       <c r="C289" t="n">
-        <v>-5.36846923828125</v>
+        <v>1.847595000000013</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>228.7706909179688</v>
+        <v>175.124191</v>
       </c>
       <c r="B290" t="n">
-        <v>225.823486328125</v>
+        <v>175.17363</v>
       </c>
       <c r="C290" t="n">
-        <v>2.94720458984375</v>
+        <v>-0.04943900000000667</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>232.60107421875</v>
+        <v>177.930145</v>
       </c>
       <c r="B291" t="n">
-        <v>228.7706909179688</v>
+        <v>175.124191</v>
       </c>
       <c r="C291" t="n">
-        <v>3.83038330078125</v>
+        <v>2.805954000000014</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>233.0178527832031</v>
+        <v>178.779831</v>
       </c>
       <c r="B292" t="n">
-        <v>232.60107421875</v>
+        <v>177.930145</v>
       </c>
       <c r="C292" t="n">
-        <v>0.416778564453125</v>
+        <v>0.8496859999999913</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>227.1234130859375</v>
+        <v>177.426254</v>
       </c>
       <c r="B293" t="n">
-        <v>233.0178527832031</v>
+        <v>178.779831</v>
       </c>
       <c r="C293" t="n">
-        <v>-5.894439697265625</v>
+        <v>-1.353577000000001</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>222.4595031738281</v>
+        <v>177.060699</v>
       </c>
       <c r="B294" t="n">
-        <v>227.1234130859375</v>
+        <v>177.426254</v>
       </c>
       <c r="C294" t="n">
-        <v>-4.663909912109432</v>
+        <v>-0.3655550000000005</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>222.5885009765625</v>
+        <v>175.687378</v>
       </c>
       <c r="B295" t="n">
-        <v>222.4595031738281</v>
+        <v>177.060699</v>
       </c>
       <c r="C295" t="n">
-        <v>0.1289978027344603</v>
+        <v>-1.373321000000004</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>222.2411956787109</v>
+        <v>178.404388</v>
       </c>
       <c r="B296" t="n">
-        <v>222.5885009765625</v>
+        <v>175.687378</v>
       </c>
       <c r="C296" t="n">
-        <v>-0.3473052978516193</v>
+        <v>2.717010000000016</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>223.2831268310547</v>
+        <v>178.789734</v>
       </c>
       <c r="B297" t="n">
-        <v>222.2411956787109</v>
+        <v>178.404388</v>
       </c>
       <c r="C297" t="n">
-        <v>1.04193115234375</v>
+        <v>0.3853459999999984</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>216.8627624511719</v>
+        <v>181.58577</v>
       </c>
       <c r="B298" t="n">
-        <v>223.2831268310547</v>
+        <v>178.789734</v>
       </c>
       <c r="C298" t="n">
-        <v>-6.420364379882784</v>
+        <v>2.796035999999987</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>215.8208465576172</v>
+        <v>181.111511</v>
       </c>
       <c r="B299" t="n">
-        <v>216.8627624511719</v>
+        <v>181.58577</v>
       </c>
       <c r="C299" t="n">
-        <v>-1.041915893554688</v>
+        <v>-0.4742589999999893</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>216.2872467041016</v>
+        <v>181.743851</v>
       </c>
       <c r="B300" t="n">
-        <v>215.8208465576172</v>
+        <v>181.111511</v>
       </c>
       <c r="C300" t="n">
-        <v>0.4664001464844034</v>
+        <v>0.6323399999999992</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>216.5650939941407</v>
+        <v>183.77916</v>
       </c>
       <c r="B301" t="n">
-        <v>216.2872467041016</v>
+        <v>181.743851</v>
       </c>
       <c r="C301" t="n">
-        <v>0.2778472900390909</v>
+        <v>2.035308999999984</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>217.1208190917969</v>
+        <v>182.702209</v>
       </c>
       <c r="B302" t="n">
-        <v>216.5650939941407</v>
+        <v>183.77916</v>
       </c>
       <c r="C302" t="n">
-        <v>0.5557250976561932</v>
+        <v>-1.07695099999998</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>220.3756256103516</v>
+        <v>182.791168</v>
       </c>
       <c r="B303" t="n">
-        <v>217.1208190917969</v>
+        <v>182.702209</v>
       </c>
       <c r="C303" t="n">
-        <v>3.254806518554716</v>
+        <v>0.08895899999998846</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>216.6841430664062</v>
+        <v>181.753723</v>
       </c>
       <c r="B304" t="n">
-        <v>220.3756256103516</v>
+        <v>182.791168</v>
       </c>
       <c r="C304" t="n">
-        <v>-3.691482543945341</v>
+        <v>-1.037444999999991</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>218.1726379394531</v>
+        <v>184.757263</v>
       </c>
       <c r="B305" t="n">
-        <v>216.6841430664062</v>
+        <v>181.753723</v>
       </c>
       <c r="C305" t="n">
-        <v>1.488494873046875</v>
+        <v>3.003539999999987</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>207.6639099121093</v>
+        <v>184.441116</v>
       </c>
       <c r="B306" t="n">
-        <v>218.1726379394531</v>
+        <v>184.757263</v>
       </c>
       <c r="C306" t="n">
-        <v>-10.50872802734381</v>
+        <v>-0.3161470000000008</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>205.6395874023437</v>
+        <v>183.048004</v>
       </c>
       <c r="B307" t="n">
-        <v>207.6639099121093</v>
+        <v>184.441116</v>
       </c>
       <c r="C307" t="n">
-        <v>-2.024322509765625</v>
+        <v>-1.393112000000002</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>208.209701538086</v>
+        <v>185.804581</v>
       </c>
       <c r="B308" t="n">
-        <v>205.6395874023437</v>
+        <v>183.048004</v>
       </c>
       <c r="C308" t="n">
-        <v>2.57011413574233</v>
+        <v>2.756577000000021</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>211.6729431152344</v>
+        <v>186.980286</v>
       </c>
       <c r="B309" t="n">
-        <v>208.209701538086</v>
+        <v>185.804581</v>
       </c>
       <c r="C309" t="n">
-        <v>3.463241577148381</v>
+        <v>1.175704999999994</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>214.5804443359375</v>
+        <v>187.316208</v>
       </c>
       <c r="B310" t="n">
-        <v>211.6729431152344</v>
+        <v>186.980286</v>
       </c>
       <c r="C310" t="n">
-        <v>2.907501220703097</v>
+        <v>0.3359219999999823</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>216.1103820800781</v>
+        <v>191.643692</v>
       </c>
       <c r="B311" t="n">
-        <v>214.5804443359375</v>
+        <v>187.316208</v>
       </c>
       <c r="C311" t="n">
-        <v>1.529937744140568</v>
+        <v>4.327483999999998</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>219.8260040283203</v>
+        <v>190.151779</v>
       </c>
       <c r="B312" t="n">
-        <v>216.1103820800781</v>
+        <v>191.643692</v>
       </c>
       <c r="C312" t="n">
-        <v>3.715621948242244</v>
+        <v>-1.491912999999983</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>220.2730407714844</v>
+        <v>189.035355</v>
       </c>
       <c r="B313" t="n">
-        <v>219.8260040283203</v>
+        <v>190.151779</v>
       </c>
       <c r="C313" t="n">
-        <v>0.4470367431640909</v>
+        <v>-1.116423999999995</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>223.2534637451172</v>
+        <v>189.509583</v>
       </c>
       <c r="B314" t="n">
-        <v>220.2730407714844</v>
+        <v>189.035355</v>
       </c>
       <c r="C314" t="n">
-        <v>2.980422973632784</v>
+        <v>0.4742279999999823</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>224.5747833251953</v>
+        <v>188.393127</v>
       </c>
       <c r="B315" t="n">
-        <v>223.2534637451172</v>
+        <v>189.509583</v>
       </c>
       <c r="C315" t="n">
-        <v>1.321319580078125</v>
+        <v>-1.116455999999999</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>224.4158325195312</v>
+        <v>186.347946</v>
       </c>
       <c r="B316" t="n">
-        <v>224.5747833251953</v>
+        <v>188.393127</v>
       </c>
       <c r="C316" t="n">
-        <v>-0.1589508056640625</v>
+        <v>-2.045180999999985</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>225.0317840576172</v>
+        <v>185.82431</v>
       </c>
       <c r="B317" t="n">
-        <v>224.4158325195312</v>
+        <v>186.347946</v>
       </c>
       <c r="C317" t="n">
-        <v>0.6159515380859375</v>
+        <v>-0.5236360000000104</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>224.9225006103516</v>
+        <v>187.494064</v>
       </c>
       <c r="B318" t="n">
-        <v>225.0317840576172</v>
+        <v>185.82431</v>
       </c>
       <c r="C318" t="n">
-        <v>-0.1092834472655966</v>
+        <v>1.669754000000012</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>223.0647125244141</v>
+        <v>188.254822</v>
       </c>
       <c r="B319" t="n">
-        <v>224.9225006103516</v>
+        <v>187.494064</v>
       </c>
       <c r="C319" t="n">
-        <v>-1.8577880859375</v>
+        <v>0.7607579999999814</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>225.359619140625</v>
+        <v>188.40303</v>
       </c>
       <c r="B320" t="n">
-        <v>223.0647125244141</v>
+        <v>188.254822</v>
       </c>
       <c r="C320" t="n">
-        <v>2.294906616210881</v>
+        <v>0.148208000000011</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>225.6974182128907</v>
+        <v>191.663452</v>
       </c>
       <c r="B321" t="n">
-        <v>225.359619140625</v>
+        <v>188.40303</v>
       </c>
       <c r="C321" t="n">
-        <v>0.3377990722657103</v>
+        <v>3.260422000000005</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>226.5418853759766</v>
+        <v>191.40654</v>
       </c>
       <c r="B322" t="n">
-        <v>225.6974182128907</v>
+        <v>191.663452</v>
       </c>
       <c r="C322" t="n">
-        <v>0.8444671630859091</v>
+        <v>-0.2569119999999998</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>225.0119323730469</v>
+        <v>192.760147</v>
       </c>
       <c r="B323" t="n">
-        <v>226.5418853759766</v>
+        <v>191.40654</v>
       </c>
       <c r="C323" t="n">
-        <v>-1.529953002929716</v>
+        <v>1.353606999999982</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>228.2903900146484</v>
+        <v>190.813766</v>
       </c>
       <c r="B324" t="n">
-        <v>225.0119323730469</v>
+        <v>192.760147</v>
       </c>
       <c r="C324" t="n">
-        <v>3.278457641601562</v>
+        <v>-1.946381000000002</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>227.5055541992188</v>
+        <v>189.638031</v>
       </c>
       <c r="B325" t="n">
-        <v>228.2903900146484</v>
+        <v>190.813766</v>
       </c>
       <c r="C325" t="n">
-        <v>-0.7848358154296875</v>
+        <v>-1.175734999999975</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>221.3162078857422</v>
+        <v>190.438293</v>
       </c>
       <c r="B326" t="n">
-        <v>227.5055541992188</v>
+        <v>189.638031</v>
       </c>
       <c r="C326" t="n">
-        <v>-6.189346313476562</v>
+        <v>0.8002619999999752</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>219.4087371826172</v>
+        <v>191.297882</v>
       </c>
       <c r="B327" t="n">
-        <v>221.3162078857422</v>
+        <v>190.438293</v>
       </c>
       <c r="C327" t="n">
-        <v>-1.907470703124972</v>
+        <v>0.8595889999999997</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>220.9287567138672</v>
+        <v>192.167297</v>
       </c>
       <c r="B328" t="n">
-        <v>219.4087371826172</v>
+        <v>191.297882</v>
       </c>
       <c r="C328" t="n">
-        <v>1.520019531249972</v>
+        <v>0.8694150000000036</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>219.378921508789</v>
+        <v>190.902695</v>
       </c>
       <c r="B329" t="n">
-        <v>220.9287567138672</v>
+        <v>192.167297</v>
       </c>
       <c r="C329" t="n">
-        <v>-1.549835205078153</v>
+        <v>-1.264601999999996</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>219.4683532714844</v>
+        <v>193.481384</v>
       </c>
       <c r="B330" t="n">
-        <v>219.378921508789</v>
+        <v>190.902695</v>
       </c>
       <c r="C330" t="n">
-        <v>0.08943176269536934</v>
+        <v>2.578688999999997</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>218.6735382080078</v>
+        <v>194.093933</v>
       </c>
       <c r="B331" t="n">
-        <v>219.4683532714844</v>
+        <v>193.481384</v>
       </c>
       <c r="C331" t="n">
-        <v>-0.7948150634765625</v>
+        <v>0.6125490000000013</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>221.2069244384766</v>
+        <v>193.264023</v>
       </c>
       <c r="B332" t="n">
-        <v>218.6735382080078</v>
+        <v>194.093933</v>
       </c>
       <c r="C332" t="n">
-        <v>2.533386230468722</v>
+        <v>-0.8299099999999839</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>221.3162078857422</v>
+        <v>190.270355</v>
       </c>
       <c r="B333" t="n">
-        <v>221.2069244384766</v>
+        <v>193.264023</v>
       </c>
       <c r="C333" t="n">
-        <v>0.109283447265625</v>
+        <v>-2.993668000000014</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>221.0479583740234</v>
+        <v>188.877274</v>
       </c>
       <c r="B334" t="n">
-        <v>221.3162078857422</v>
+        <v>190.270355</v>
       </c>
       <c r="C334" t="n">
-        <v>-0.26824951171875</v>
+        <v>-1.393080999999995</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>214.9082946777344</v>
+        <v>179.807373</v>
       </c>
       <c r="B335" t="n">
-        <v>221.0479583740234</v>
+        <v>188.877274</v>
       </c>
       <c r="C335" t="n">
-        <v>-6.139663696289034</v>
+        <v>-9.069900999999987</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>215.3752136230469</v>
+        <v>176.705048</v>
       </c>
       <c r="B336" t="n">
-        <v>214.9082946777344</v>
+        <v>179.807373</v>
       </c>
       <c r="C336" t="n">
-        <v>0.4669189453125</v>
+        <v>-3.102325000000008</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>219.2497711181641</v>
+        <v>177.643646</v>
       </c>
       <c r="B337" t="n">
-        <v>215.3752136230469</v>
+        <v>176.705048</v>
       </c>
       <c r="C337" t="n">
-        <v>3.874557495117216</v>
+        <v>0.9385979999999847</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>227.3764038085937</v>
+        <v>176.052948</v>
       </c>
       <c r="B338" t="n">
-        <v>219.2497711181641</v>
+        <v>177.643646</v>
       </c>
       <c r="C338" t="n">
-        <v>8.126632690429574</v>
+        <v>-1.590698000000003</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>226.7107391357422</v>
+        <v>175.835571</v>
       </c>
       <c r="B339" t="n">
-        <v>227.3764038085937</v>
+        <v>176.052948</v>
       </c>
       <c r="C339" t="n">
-        <v>-0.6656646728515057</v>
+        <v>-0.217376999999999</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>224.9920501708984</v>
+        <v>175.894958</v>
       </c>
       <c r="B340" t="n">
-        <v>226.7107391357422</v>
+        <v>175.835571</v>
       </c>
       <c r="C340" t="n">
-        <v>-1.71868896484375</v>
+        <v>0.05938700000001518</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>225.8861694335937</v>
+        <v>177.547134</v>
       </c>
       <c r="B341" t="n">
-        <v>224.9920501708984</v>
+        <v>175.894958</v>
       </c>
       <c r="C341" t="n">
-        <v>0.8941192626952557</v>
+        <v>1.652175999999997</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>224.8927001953125</v>
+        <v>175.558563</v>
       </c>
       <c r="B342" t="n">
-        <v>225.8861694335937</v>
+        <v>177.547134</v>
       </c>
       <c r="C342" t="n">
-        <v>-0.9934692382811932</v>
+        <v>-1.988571000000007</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>226.0351867675781</v>
+        <v>174.687943</v>
       </c>
       <c r="B343" t="n">
-        <v>224.8927001953125</v>
+        <v>175.558563</v>
       </c>
       <c r="C343" t="n">
-        <v>1.142486572265568</v>
+        <v>-0.8706200000000024</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>226.3034057617188</v>
+        <v>172.145325</v>
       </c>
       <c r="B344" t="n">
-        <v>226.0351867675781</v>
+        <v>174.687943</v>
       </c>
       <c r="C344" t="n">
-        <v>0.2682189941406818</v>
+        <v>-2.542617999999976</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>231.4794158935547</v>
+        <v>172.630112</v>
       </c>
       <c r="B345" t="n">
-        <v>226.3034057617188</v>
+        <v>172.145325</v>
       </c>
       <c r="C345" t="n">
-        <v>5.176010131835938</v>
+        <v>0.484786999999983</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>224.7337341308593</v>
+        <v>173.965714</v>
       </c>
       <c r="B346" t="n">
-        <v>231.4794158935547</v>
+        <v>172.630112</v>
       </c>
       <c r="C346" t="n">
-        <v>-6.745681762695369</v>
+        <v>1.335601999999994</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>225.3000030517578</v>
+        <v>175.340897</v>
       </c>
       <c r="B347" t="n">
-        <v>224.7337341308593</v>
+        <v>173.965714</v>
       </c>
       <c r="C347" t="n">
-        <v>0.5662689208984943</v>
+        <v>1.375183000000021</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>224.1972503662109</v>
+        <v>179.189453</v>
       </c>
       <c r="B348" t="n">
-        <v>225.3000030517578</v>
+        <v>175.340897</v>
       </c>
       <c r="C348" t="n">
-        <v>-1.102752685546903</v>
+        <v>3.848555999999974</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>225.3199157714844</v>
+        <v>174.499985</v>
       </c>
       <c r="B349" t="n">
-        <v>224.1972503662109</v>
+        <v>179.189453</v>
       </c>
       <c r="C349" t="n">
-        <v>1.122665405273494</v>
+        <v>-4.689467999999977</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>220.2432708740234</v>
+        <v>176.706207</v>
       </c>
       <c r="B350" t="n">
-        <v>225.3199157714844</v>
+        <v>174.499985</v>
       </c>
       <c r="C350" t="n">
-        <v>-5.076644897460966</v>
+        <v>2.206221999999997</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>224.296615600586</v>
+        <v>178.269363</v>
       </c>
       <c r="B351" t="n">
-        <v>220.2432708740234</v>
+        <v>176.706207</v>
       </c>
       <c r="C351" t="n">
-        <v>4.053344726562528</v>
+        <v>1.563155999999992</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>228.042007446289</v>
+        <v>182.15744</v>
       </c>
       <c r="B352" t="n">
-        <v>224.296615600586</v>
+        <v>178.269363</v>
       </c>
       <c r="C352" t="n">
-        <v>3.745391845703068</v>
+        <v>3.88807700000001</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>227.5452575683593</v>
+        <v>185.649841</v>
       </c>
       <c r="B353" t="n">
-        <v>228.042007446289</v>
+        <v>182.15744</v>
       </c>
       <c r="C353" t="n">
-        <v>-0.4967498779297443</v>
+        <v>3.492401000000001</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>226.0650024414062</v>
+        <v>185.867477</v>
       </c>
       <c r="B354" t="n">
-        <v>227.5452575683593</v>
+        <v>185.649841</v>
       </c>
       <c r="C354" t="n">
-        <v>-1.48025512695304</v>
+        <v>0.2176359999999988</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>229.790542602539</v>
+        <v>187.440552</v>
       </c>
       <c r="B355" t="n">
-        <v>226.0650024414062</v>
+        <v>185.867477</v>
       </c>
       <c r="C355" t="n">
-        <v>3.725540161132784</v>
+        <v>1.573074999999989</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>232.3238830566407</v>
+        <v>187.677994</v>
       </c>
       <c r="B356" t="n">
-        <v>229.790542602539</v>
+        <v>187.440552</v>
       </c>
       <c r="C356" t="n">
-        <v>2.533340454101648</v>
+        <v>0.2374420000000157</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>230.2673950195312</v>
+        <v>180.960358</v>
       </c>
       <c r="B357" t="n">
-        <v>232.3238830566407</v>
+        <v>187.677994</v>
       </c>
       <c r="C357" t="n">
-        <v>-2.056488037109432</v>
+        <v>-6.717635999999999</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>230.6349792480469</v>
+        <v>175.667374</v>
       </c>
       <c r="B358" t="n">
-        <v>230.2673950195312</v>
+        <v>180.960358</v>
       </c>
       <c r="C358" t="n">
-        <v>0.3675842285156534</v>
+        <v>-5.292984000000018</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>233.4663848876953</v>
+        <v>176.280762</v>
       </c>
       <c r="B359" t="n">
-        <v>230.6349792480469</v>
+        <v>175.667374</v>
       </c>
       <c r="C359" t="n">
-        <v>2.831405639648409</v>
+        <v>0.6133880000000147</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>234.9367370605469</v>
+        <v>177.448212</v>
       </c>
       <c r="B360" t="n">
-        <v>233.4663848876953</v>
+        <v>176.280762</v>
       </c>
       <c r="C360" t="n">
-        <v>1.470352172851562</v>
+        <v>1.167450000000002</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>234.3207855224609</v>
+        <v>174.420822</v>
       </c>
       <c r="B361" t="n">
-        <v>234.9367370605469</v>
+        <v>177.448212</v>
       </c>
       <c r="C361" t="n">
-        <v>-0.6159515380859943</v>
+        <v>-3.027390000000025</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>229.2540435791016</v>
+        <v>172.353104</v>
       </c>
       <c r="B362" t="n">
-        <v>234.3207855224609</v>
+        <v>174.420822</v>
       </c>
       <c r="C362" t="n">
-        <v>-5.06674194335929</v>
+        <v>-2.067717999999985</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>229.0652923583984</v>
+        <v>173.86676</v>
       </c>
       <c r="B363" t="n">
-        <v>229.2540435791016</v>
+        <v>172.353104</v>
       </c>
       <c r="C363" t="n">
-        <v>-0.1887512207031534</v>
+        <v>1.513655999999997</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>229.8998107910156</v>
+        <v>173.144577</v>
       </c>
       <c r="B364" t="n">
-        <v>229.0652923583984</v>
+        <v>173.86676</v>
       </c>
       <c r="C364" t="n">
-        <v>0.8345184326171591</v>
+        <v>-0.7221830000000011</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>231.8768157958984</v>
+        <v>176.073029</v>
       </c>
       <c r="B365" t="n">
-        <v>229.8998107910156</v>
+        <v>173.144577</v>
       </c>
       <c r="C365" t="n">
-        <v>1.977005004882841</v>
+        <v>2.928451999999993</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>232.1450653076172</v>
+        <v>177.161316</v>
       </c>
       <c r="B366" t="n">
-        <v>231.8768157958984</v>
+        <v>176.073029</v>
       </c>
       <c r="C366" t="n">
-        <v>0.26824951171875</v>
+        <v>1.088287000000008</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>228.598373413086</v>
+        <v>173.619461</v>
       </c>
       <c r="B367" t="n">
-        <v>232.1450653076172</v>
+        <v>177.161316</v>
       </c>
       <c r="C367" t="n">
-        <v>-3.546691894531193</v>
+        <v>-3.541854999999998</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>224.4356994628907</v>
+        <v>172.07608</v>
       </c>
       <c r="B368" t="n">
-        <v>228.598373413086</v>
+        <v>173.619461</v>
       </c>
       <c r="C368" t="n">
-        <v>-4.162673950195341</v>
+        <v>-1.543381000000011</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>221.4552917480469</v>
+        <v>172.926895</v>
       </c>
       <c r="B369" t="n">
-        <v>224.4356994628907</v>
+        <v>172.07608</v>
       </c>
       <c r="C369" t="n">
-        <v>-2.980407714843778</v>
+        <v>0.8508150000000114</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>220.5611572265625</v>
+        <v>174.203171</v>
       </c>
       <c r="B370" t="n">
-        <v>221.4552917480469</v>
+        <v>172.926895</v>
       </c>
       <c r="C370" t="n">
-        <v>-0.894134521484375</v>
+        <v>1.276275999999996</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>221.9917449951172</v>
+        <v>170.12709</v>
       </c>
       <c r="B371" t="n">
-        <v>220.5611572265625</v>
+        <v>174.203171</v>
       </c>
       <c r="C371" t="n">
-        <v>1.430587768554688</v>
+        <v>-4.076080999999988</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>221.2665100097656</v>
+        <v>168.613388</v>
       </c>
       <c r="B372" t="n">
-        <v>221.9917449951172</v>
+        <v>170.12709</v>
       </c>
       <c r="C372" t="n">
-        <v>-0.7252349853515909</v>
+        <v>-1.513702000000023</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>225.9954528808593</v>
+        <v>168.870621</v>
       </c>
       <c r="B373" t="n">
-        <v>221.2665100097656</v>
+        <v>168.613388</v>
       </c>
       <c r="C373" t="n">
-        <v>4.72894287109375</v>
+        <v>0.2572330000000136</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>225.7269287109375</v>
+        <v>169.385056</v>
       </c>
       <c r="B374" t="n">
-        <v>225.9954528808593</v>
+        <v>168.870621</v>
       </c>
       <c r="C374" t="n">
-        <v>-0.2685241699218466</v>
+        <v>0.5144349999999918</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>223.0117492675781</v>
+        <v>171.89801</v>
       </c>
       <c r="B375" t="n">
-        <v>225.7269287109375</v>
+        <v>169.385056</v>
       </c>
       <c r="C375" t="n">
-        <v>-2.715179443359432</v>
+        <v>2.512954000000008</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>223.0117492675781</v>
+        <v>170.562393</v>
       </c>
       <c r="B376" t="n">
-        <v>223.0117492675781</v>
+        <v>171.89801</v>
       </c>
       <c r="C376" t="n">
-        <v>0</v>
+        <v>-1.335617000000013</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>223.8969268798828</v>
+        <v>171.808945</v>
       </c>
       <c r="B377" t="n">
-        <v>223.0117492675781</v>
+        <v>170.562393</v>
       </c>
       <c r="C377" t="n">
-        <v>0.8851776123047443</v>
+        <v>1.246552000000008</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>226.9800872802734</v>
+        <v>173.045639</v>
       </c>
       <c r="B378" t="n">
-        <v>223.8969268798828</v>
+        <v>171.808945</v>
       </c>
       <c r="C378" t="n">
-        <v>3.083160400390625</v>
+        <v>1.236694</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>223.7775573730469</v>
+        <v>175.598129</v>
       </c>
       <c r="B379" t="n">
-        <v>226.9800872802734</v>
+        <v>173.045639</v>
       </c>
       <c r="C379" t="n">
-        <v>-3.202529907226562</v>
+        <v>2.552490000000006</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>226.7811737060547</v>
+        <v>177.082138</v>
       </c>
       <c r="B380" t="n">
-        <v>223.7775573730469</v>
+        <v>175.598129</v>
       </c>
       <c r="C380" t="n">
-        <v>3.003616333007812</v>
+        <v>1.484008999999986</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>227.0397491455078</v>
+        <v>176.488556</v>
       </c>
       <c r="B381" t="n">
-        <v>226.7811737060547</v>
+        <v>177.082138</v>
       </c>
       <c r="C381" t="n">
-        <v>0.2585754394531534</v>
+        <v>-0.5935819999999978</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>227.7558288574219</v>
+        <v>177.88353</v>
       </c>
       <c r="B382" t="n">
-        <v>227.0397491455078</v>
+        <v>176.488556</v>
       </c>
       <c r="C382" t="n">
-        <v>0.7160797119140341</v>
+        <v>1.394974000000019</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>227.2784576416016</v>
+        <v>178.783829</v>
       </c>
       <c r="B383" t="n">
-        <v>227.7558288574219</v>
+        <v>177.88353</v>
       </c>
       <c r="C383" t="n">
-        <v>-0.4773712158202557</v>
+        <v>0.9002989999999897</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>228.62109375</v>
+        <v>176.943649</v>
       </c>
       <c r="B384" t="n">
-        <v>227.2784576416016</v>
+        <v>178.783829</v>
       </c>
       <c r="C384" t="n">
-        <v>1.342636108398381</v>
+        <v>-1.840180000000004</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>231.6047973632812</v>
+        <v>176.815002</v>
       </c>
       <c r="B385" t="n">
-        <v>228.62109375</v>
+        <v>176.943649</v>
       </c>
       <c r="C385" t="n">
-        <v>2.98370361328125</v>
+        <v>-0.1286470000000008</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>233.7829132080078</v>
+        <v>175.261749</v>
       </c>
       <c r="B386" t="n">
-        <v>231.6047973632812</v>
+        <v>176.815002</v>
       </c>
       <c r="C386" t="n">
-        <v>2.178115844726562</v>
+        <v>-1.553252999999984</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>233.6536254882812</v>
+        <v>173.965714</v>
       </c>
       <c r="B387" t="n">
-        <v>233.7829132080078</v>
+        <v>175.261749</v>
       </c>
       <c r="C387" t="n">
-        <v>-0.1292877197265625</v>
+        <v>-1.296035000000018</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>236.0405883789062</v>
+        <v>173.589767</v>
       </c>
       <c r="B388" t="n">
-        <v>233.6536254882812</v>
+        <v>173.965714</v>
       </c>
       <c r="C388" t="n">
-        <v>2.386962890625</v>
+        <v>-0.3759469999999965</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>238.2882843017578</v>
+        <v>171.037262</v>
       </c>
       <c r="B389" t="n">
-        <v>236.0405883789062</v>
+        <v>173.589767</v>
       </c>
       <c r="C389" t="n">
-        <v>2.247695922851562</v>
+        <v>-2.552504999999996</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>241.3316802978516</v>
+        <v>171.156006</v>
       </c>
       <c r="B390" t="n">
-        <v>238.2882843017578</v>
+        <v>171.037262</v>
       </c>
       <c r="C390" t="n">
-        <v>3.043395996093778</v>
+        <v>0.1187439999999924</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>241.6897125244141</v>
+        <v>171.591309</v>
       </c>
       <c r="B391" t="n">
-        <v>241.3316802978516</v>
+        <v>171.156006</v>
       </c>
       <c r="C391" t="n">
-        <v>0.3580322265625</v>
+        <v>0.4353030000000047</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>241.7195434570312</v>
+        <v>169.27626</v>
       </c>
       <c r="B392" t="n">
-        <v>241.6897125244141</v>
+        <v>171.591309</v>
       </c>
       <c r="C392" t="n">
-        <v>0.02983093261715908</v>
+        <v>-2.315048999999988</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>241.5206451416016</v>
+        <v>165.111115</v>
       </c>
       <c r="B393" t="n">
-        <v>241.7195434570312</v>
+        <v>169.27626</v>
       </c>
       <c r="C393" t="n">
-        <v>-0.1988983154296591</v>
+        <v>-4.165144999999995</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>245.409408569336</v>
+        <v>166.426926</v>
       </c>
       <c r="B394" t="n">
-        <v>241.5206451416016</v>
+        <v>165.111115</v>
       </c>
       <c r="C394" t="n">
-        <v>3.888763427734403</v>
+        <v>1.315810999999997</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>246.4238739013672</v>
+        <v>168.474854</v>
       </c>
       <c r="B395" t="n">
-        <v>245.409408569336</v>
+        <v>166.426926</v>
       </c>
       <c r="C395" t="n">
-        <v>1.014465332031193</v>
+        <v>2.047927999999985</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>245.1508178710937</v>
+        <v>168.949753</v>
       </c>
       <c r="B396" t="n">
-        <v>246.4238739013672</v>
+        <v>168.474854</v>
       </c>
       <c r="C396" t="n">
-        <v>-1.273056030273466</v>
+        <v>0.4748989999999935</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>246.6128387451172</v>
+        <v>172.115662</v>
       </c>
       <c r="B397" t="n">
-        <v>245.1508178710937</v>
+        <v>168.949753</v>
       </c>
       <c r="C397" t="n">
-        <v>1.462020874023494</v>
+        <v>3.165908999999999</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>246.7819061279297</v>
+        <v>175.677292</v>
       </c>
       <c r="B398" t="n">
-        <v>246.6128387451172</v>
+        <v>172.115662</v>
       </c>
       <c r="C398" t="n">
-        <v>0.1690673828124716</v>
+        <v>3.561630000000008</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>249.6760711669922</v>
+        <v>174.76709</v>
       </c>
       <c r="B399" t="n">
-        <v>246.7819061279297</v>
+        <v>175.677292</v>
       </c>
       <c r="C399" t="n">
-        <v>2.8941650390625</v>
+        <v>-0.9102019999999982</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>252.1028289794922</v>
+        <v>177.319595</v>
       </c>
       <c r="B400" t="n">
-        <v>249.6760711669922</v>
+        <v>174.76709</v>
       </c>
       <c r="C400" t="n">
-        <v>2.4267578125</v>
+        <v>2.552504999999996</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>246.7023315429688</v>
+        <v>179.881989</v>
       </c>
       <c r="B401" t="n">
-        <v>252.1028289794922</v>
+        <v>177.319595</v>
       </c>
       <c r="C401" t="n">
-        <v>-5.400497436523438</v>
+        <v>2.562394000000012</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>248.4328765869141</v>
+        <v>180.940598</v>
       </c>
       <c r="B402" t="n">
-        <v>246.7023315429688</v>
+        <v>179.881989</v>
       </c>
       <c r="C402" t="n">
-        <v>1.730545043945341</v>
+        <v>1.05860899999999</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>253.1073760986328</v>
+        <v>180.465698</v>
       </c>
       <c r="B403" t="n">
-        <v>248.4328765869141</v>
+        <v>180.940598</v>
       </c>
       <c r="C403" t="n">
-        <v>4.674499511718722</v>
+        <v>-0.474899999999991</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>253.8831176757812</v>
+        <v>184.656143</v>
       </c>
       <c r="B404" t="n">
-        <v>253.1073760986328</v>
+        <v>180.465698</v>
       </c>
       <c r="C404" t="n">
-        <v>0.7757415771484375</v>
+        <v>4.190444999999983</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>256.7971801757812</v>
+        <v>183.071091</v>
       </c>
       <c r="B405" t="n">
-        <v>253.8831176757812</v>
+        <v>184.656143</v>
       </c>
       <c r="C405" t="n">
-        <v>2.9140625</v>
+        <v>-1.58505199999999</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
-        <v>257.6127014160156</v>
+        <v>185.686401</v>
       </c>
       <c r="B406" t="n">
-        <v>256.7971801757812</v>
+        <v>183.071091</v>
       </c>
       <c r="C406" t="n">
-        <v>0.815521240234375</v>
+        <v>2.615309999999994</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>254.2013854980468</v>
+        <v>186.251068</v>
       </c>
       <c r="B407" t="n">
-        <v>257.6127014160156</v>
+        <v>185.686401</v>
       </c>
       <c r="C407" t="n">
-        <v>-3.411315917968778</v>
+        <v>0.5646670000000142</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
-        <v>250.8298034667969</v>
+        <v>187.93515</v>
       </c>
       <c r="B408" t="n">
-        <v>254.2013854980468</v>
+        <v>186.251068</v>
       </c>
       <c r="C408" t="n">
-        <v>-3.371582031249972</v>
+        <v>1.684081999999989</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
-        <v>249.0594635009766</v>
+        <v>187.915344</v>
       </c>
       <c r="B409" t="n">
-        <v>250.8298034667969</v>
+        <v>187.93515</v>
       </c>
       <c r="C409" t="n">
-        <v>-1.770339965820312</v>
+        <v>-0.01980599999998844</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
-        <v>242.5251770019531</v>
+        <v>189.65889</v>
       </c>
       <c r="B410" t="n">
-        <v>249.0594635009766</v>
+        <v>187.915344</v>
       </c>
       <c r="C410" t="n">
-        <v>-6.534286499023438</v>
+        <v>1.743546000000009</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
-        <v>242.037826538086</v>
+        <v>188.856445</v>
       </c>
       <c r="B411" t="n">
-        <v>242.5251770019531</v>
+        <v>189.65889</v>
       </c>
       <c r="C411" t="n">
-        <v>-0.4873504638671307</v>
+        <v>-0.8024450000000058</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
-        <v>243.6689300537109</v>
+        <v>189.520187</v>
       </c>
       <c r="B412" t="n">
-        <v>242.037826538086</v>
+        <v>188.856445</v>
       </c>
       <c r="C412" t="n">
-        <v>1.631103515624943</v>
+        <v>0.663741999999985</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
-        <v>240.8940887451172</v>
+        <v>188.192719</v>
       </c>
       <c r="B413" t="n">
-        <v>243.6689300537109</v>
+        <v>189.520187</v>
       </c>
       <c r="C413" t="n">
-        <v>-2.774841308593778</v>
+        <v>-1.327467999999982</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
-        <v>241.3814086914063</v>
+        <v>188.014389</v>
       </c>
       <c r="B414" t="n">
-        <v>240.8940887451172</v>
+        <v>188.192719</v>
       </c>
       <c r="C414" t="n">
-        <v>0.4873199462891193</v>
+        <v>-0.1783300000000168</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
-        <v>235.5632019042968</v>
+        <v>188.618698</v>
       </c>
       <c r="B415" t="n">
-        <v>241.3814086914063</v>
+        <v>188.014389</v>
       </c>
       <c r="C415" t="n">
-        <v>-5.818206787109432</v>
+        <v>0.6043090000000007</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
-        <v>233.126480102539</v>
+        <v>187.598343</v>
       </c>
       <c r="B416" t="n">
-        <v>235.5632019042968</v>
+        <v>188.618698</v>
       </c>
       <c r="C416" t="n">
-        <v>-2.436721801757812</v>
+        <v>-1.020354999999995</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
-        <v>232.0125579833984</v>
+        <v>188.172913</v>
       </c>
       <c r="B417" t="n">
-        <v>233.126480102539</v>
+        <v>187.598343</v>
       </c>
       <c r="C417" t="n">
-        <v>-1.113922119140597</v>
+        <v>0.5745699999999943</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
-        <v>236.57763671875</v>
+        <v>189.450836</v>
       </c>
       <c r="B418" t="n">
-        <v>232.0125579833984</v>
+        <v>188.172913</v>
       </c>
       <c r="C418" t="n">
-        <v>4.565078735351562</v>
+        <v>1.277923000000015</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
-        <v>227.0198516845703</v>
+        <v>187.657761</v>
       </c>
       <c r="B419" t="n">
-        <v>236.57763671875</v>
+        <v>189.450836</v>
       </c>
       <c r="C419" t="n">
-        <v>-9.557785034179688</v>
+        <v>-1.793075000000016</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
-        <v>228.7305145263672</v>
+        <v>191.610443</v>
       </c>
       <c r="B420" t="n">
-        <v>227.0198516845703</v>
+        <v>187.657761</v>
       </c>
       <c r="C420" t="n">
-        <v>1.710662841796875</v>
+        <v>3.95268200000001</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
-        <v>221.4303894042969</v>
+        <v>190.520721</v>
       </c>
       <c r="B421" t="n">
-        <v>228.7305145263672</v>
+        <v>191.610443</v>
       </c>
       <c r="C421" t="n">
-        <v>-7.300125122070312</v>
+        <v>-1.089721999999995</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
-        <v>222.6139221191407</v>
+        <v>192.452484</v>
       </c>
       <c r="B422" t="n">
-        <v>221.4303894042969</v>
+        <v>190.520721</v>
       </c>
       <c r="C422" t="n">
-        <v>1.183532714843778</v>
+        <v>1.931762999999989</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>222.4448547363281</v>
+        <v>193.879028</v>
       </c>
       <c r="B423" t="n">
-        <v>222.6139221191407</v>
+        <v>192.452484</v>
       </c>
       <c r="C423" t="n">
-        <v>-0.1690673828125853</v>
+        <v>1.426544000000007</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
-        <v>221.5696411132812</v>
+        <v>191.372681</v>
       </c>
       <c r="B424" t="n">
-        <v>222.4448547363281</v>
+        <v>193.879028</v>
       </c>
       <c r="C424" t="n">
-        <v>-0.8752136230468182</v>
+        <v>-2.506347000000005</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
-        <v>228.6111602783203</v>
+        <v>192.888382</v>
       </c>
       <c r="B425" t="n">
-        <v>221.5696411132812</v>
+        <v>191.372681</v>
       </c>
       <c r="C425" t="n">
-        <v>7.041519165039062</v>
+        <v>1.515701000000007</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
-        <v>236.9655456542969</v>
+        <v>196.107986</v>
       </c>
       <c r="B426" t="n">
-        <v>228.6111602783203</v>
+        <v>192.888382</v>
       </c>
       <c r="C426" t="n">
-        <v>8.354385375976562</v>
+        <v>3.219604000000004</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
-        <v>238.0595550537109</v>
+        <v>196.256577</v>
       </c>
       <c r="B427" t="n">
-        <v>236.9655456542969</v>
+        <v>196.107986</v>
       </c>
       <c r="C427" t="n">
-        <v>1.094009399414034</v>
+        <v>0.1485909999999819</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
-        <v>236.2991485595703</v>
+        <v>195.721619</v>
       </c>
       <c r="B428" t="n">
-        <v>238.0595550537109</v>
+        <v>196.256577</v>
       </c>
       <c r="C428" t="n">
-        <v>-1.760406494140597</v>
+        <v>-0.5349579999999889</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
-        <v>234.7178039550781</v>
+        <v>194.057343</v>
       </c>
       <c r="B429" t="n">
-        <v>236.2991485595703</v>
+        <v>195.721619</v>
       </c>
       <c r="C429" t="n">
-        <v>-1.581344604492244</v>
+        <v>-1.664276000000001</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
-        <v>226.771224975586</v>
+        <v>195.097519</v>
       </c>
       <c r="B430" t="n">
-        <v>234.7178039550781</v>
+        <v>194.057343</v>
       </c>
       <c r="C430" t="n">
-        <v>-7.946578979492074</v>
+        <v>1.040176000000002</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
-        <v>231.5352020263672</v>
+        <v>193.007263</v>
       </c>
       <c r="B431" t="n">
-        <v>226.771224975586</v>
+        <v>195.097519</v>
       </c>
       <c r="C431" t="n">
-        <v>4.763977050781193</v>
+        <v>-2.090256000000011</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
-        <v>231.2070007324218</v>
+        <v>192.858658</v>
       </c>
       <c r="B432" t="n">
-        <v>231.5352020263672</v>
+        <v>193.007263</v>
       </c>
       <c r="C432" t="n">
-        <v>-0.3282012939453409</v>
+        <v>-0.1486050000000034</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
-        <v>231.9529266357422</v>
+        <v>191.788742</v>
       </c>
       <c r="B433" t="n">
-        <v>231.2070007324218</v>
+        <v>192.858658</v>
       </c>
       <c r="C433" t="n">
-        <v>0.7459259033203409</v>
+        <v>-1.069915999999978</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
-        <v>226.3932800292969</v>
+        <v>191.243912</v>
       </c>
       <c r="B434" t="n">
-        <v>231.9529266357422</v>
+        <v>191.788742</v>
       </c>
       <c r="C434" t="n">
-        <v>-5.559646606445312</v>
+        <v>-0.5448300000000188</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
-        <v>226.6620941162109</v>
+        <v>191.342987</v>
       </c>
       <c r="B435" t="n">
-        <v>226.3932800292969</v>
+        <v>191.243912</v>
       </c>
       <c r="C435" t="n">
-        <v>0.2688140869140341</v>
+        <v>0.09907499999999914</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
-        <v>231.6105346679688</v>
+        <v>191.768951</v>
       </c>
       <c r="B436" t="n">
-        <v>226.6620941162109</v>
+        <v>191.342987</v>
       </c>
       <c r="C436" t="n">
-        <v>4.948440551757841</v>
+        <v>0.4259639999999933</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
-        <v>235.8420867919922</v>
+        <v>190.72876</v>
       </c>
       <c r="B437" t="n">
-        <v>231.6105346679688</v>
+        <v>191.768951</v>
       </c>
       <c r="C437" t="n">
-        <v>4.231552124023438</v>
+        <v>-1.040190999999993</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
-        <v>240.4818725585937</v>
+        <v>183.903244</v>
       </c>
       <c r="B438" t="n">
-        <v>235.8420867919922</v>
+        <v>190.72876</v>
       </c>
       <c r="C438" t="n">
-        <v>4.639785766601506</v>
+        <v>-6.825515999999993</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
-        <v>243.5385589599609</v>
+        <v>182.526245</v>
       </c>
       <c r="B439" t="n">
-        <v>240.4818725585937</v>
+        <v>183.903244</v>
       </c>
       <c r="C439" t="n">
-        <v>3.056686401367244</v>
+        <v>-1.376999000000012</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
-        <v>243.4091186523437</v>
+        <v>180.20813</v>
       </c>
       <c r="B440" t="n">
-        <v>243.5385589599609</v>
+        <v>182.526245</v>
       </c>
       <c r="C440" t="n">
-        <v>-0.1294403076172443</v>
+        <v>-2.318114999999977</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
-        <v>243.807373046875</v>
+        <v>179.48494</v>
       </c>
       <c r="B441" t="n">
-        <v>243.4091186523437</v>
+        <v>180.20813</v>
       </c>
       <c r="C441" t="n">
-        <v>0.3982543945313068</v>
+        <v>-0.7231900000000167</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
-        <v>244.763198852539</v>
+        <v>183.82399</v>
       </c>
       <c r="B442" t="n">
-        <v>243.807373046875</v>
+        <v>179.48494</v>
       </c>
       <c r="C442" t="n">
-        <v>0.9558258056640341</v>
+        <v>4.339050000000015</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
-        <v>244.4844207763672</v>
+        <v>183.407913</v>
       </c>
       <c r="B443" t="n">
-        <v>244.763198852539</v>
+        <v>183.82399</v>
       </c>
       <c r="C443" t="n">
-        <v>-0.2787780761718466</v>
+        <v>-0.4160770000000014</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>246.0277099609375</v>
+        <v>184.44809</v>
       </c>
       <c r="B444" t="n">
-        <v>244.4844207763672</v>
+        <v>183.407913</v>
       </c>
       <c r="C444" t="n">
-        <v>1.543289184570312</v>
+        <v>1.040177</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>245.9679718017578</v>
+        <v>183.853683</v>
       </c>
       <c r="B445" t="n">
-        <v>246.0277099609375</v>
+        <v>184.44809</v>
       </c>
       <c r="C445" t="n">
-        <v>-0.0597381591796875</v>
+        <v>-0.5944070000000181</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
-        <v>239.3169555664062</v>
+        <v>184.180618</v>
       </c>
       <c r="B446" t="n">
-        <v>245.9679718017578</v>
+        <v>183.853683</v>
       </c>
       <c r="C446" t="n">
-        <v>-6.651016235351562</v>
+        <v>0.3269350000000202</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>236.2702331542969</v>
+        <v>181.912018</v>
       </c>
       <c r="B447" t="n">
-        <v>239.3169555664062</v>
+        <v>184.180618</v>
       </c>
       <c r="C447" t="n">
-        <v>-3.046722412109375</v>
+        <v>-2.268600000000021</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>240.79052734375</v>
+        <v>180.970901</v>
       </c>
       <c r="B448" t="n">
-        <v>236.2702331542969</v>
+        <v>181.912018</v>
       </c>
       <c r="C448" t="n">
-        <v>4.520294189453125</v>
+        <v>-0.9411169999999913</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
-        <v>236.9970703125</v>
+        <v>186.86528</v>
       </c>
       <c r="B449" t="n">
-        <v>240.79052734375</v>
+        <v>180.970901</v>
       </c>
       <c r="C449" t="n">
-        <v>-3.79345703125</v>
+        <v>5.894379000000015</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>234.9061737060547</v>
+        <v>189.767838</v>
       </c>
       <c r="B450" t="n">
-        <v>236.9970703125</v>
+        <v>186.86528</v>
       </c>
       <c r="C450" t="n">
-        <v>-2.090896606445312</v>
+        <v>2.902557999999999</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
-        <v>234.7169952392578</v>
+        <v>192.07605</v>
       </c>
       <c r="B451" t="n">
-        <v>234.9061737060547</v>
+        <v>189.767838</v>
       </c>
       <c r="C451" t="n">
-        <v>-0.1891784667969034</v>
+        <v>2.308211999999997</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
-        <v>234.3087768554688</v>
+        <v>193.353973</v>
       </c>
       <c r="B452" t="n">
-        <v>234.7169952392578</v>
+        <v>192.07605</v>
       </c>
       <c r="C452" t="n">
-        <v>-0.4082183837890057</v>
+        <v>1.277922999999987</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
-        <v>238.0325622558593</v>
+        <v>192.680344</v>
       </c>
       <c r="B453" t="n">
-        <v>234.3087768554688</v>
+        <v>193.353973</v>
       </c>
       <c r="C453" t="n">
-        <v>3.72378540039054</v>
+        <v>-0.6736290000000054</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
-        <v>226.4928436279297</v>
+        <v>192.353409</v>
       </c>
       <c r="B454" t="n">
-        <v>238.0325622558593</v>
+        <v>192.680344</v>
       </c>
       <c r="C454" t="n">
-        <v>-11.53971862792963</v>
+        <v>-0.3269349999999918</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
-        <v>219.8816528320312</v>
+        <v>190.619781</v>
       </c>
       <c r="B455" t="n">
-        <v>226.4928436279297</v>
+        <v>192.353409</v>
       </c>
       <c r="C455" t="n">
-        <v>-6.611190795898438</v>
+        <v>-1.73362800000001</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
-        <v>216.0384216308593</v>
+        <v>189.936234</v>
       </c>
       <c r="B456" t="n">
-        <v>219.8816528320312</v>
+        <v>190.619781</v>
       </c>
       <c r="C456" t="n">
-        <v>-3.843231201171932</v>
+        <v>-0.6835469999999759</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
-        <v>208.7700958251953</v>
+        <v>186.280746</v>
       </c>
       <c r="B457" t="n">
-        <v>216.0384216308593</v>
+        <v>189.936234</v>
       </c>
       <c r="C457" t="n">
-        <v>-7.268325805664006</v>
+        <v>-3.65548800000002</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
-        <v>212.5635528564453</v>
+        <v>182.67482</v>
       </c>
       <c r="B458" t="n">
-        <v>208.7700958251953</v>
+        <v>186.280746</v>
       </c>
       <c r="C458" t="n">
-        <v>3.79345703125</v>
+        <v>-3.605925999999982</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
-        <v>213.0713653564453</v>
+        <v>185.111816</v>
       </c>
       <c r="B459" t="n">
-        <v>212.5635528564453</v>
+        <v>182.67482</v>
       </c>
       <c r="C459" t="n">
-        <v>0.5078125</v>
+        <v>2.436995999999994</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
-        <v>211.7670440673828</v>
+        <v>184.111252</v>
       </c>
       <c r="B460" t="n">
-        <v>213.0713653564453</v>
+        <v>185.111816</v>
       </c>
       <c r="C460" t="n">
-        <v>-1.3043212890625</v>
+        <v>-1.000563999999997</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
-        <v>214.3059692382812</v>
+        <v>185.924149</v>
       </c>
       <c r="B461" t="n">
-        <v>211.7670440673828</v>
+        <v>184.111252</v>
       </c>
       <c r="C461" t="n">
-        <v>2.538925170898438</v>
+        <v>1.812896999999992</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
-        <v>213.1709136962891</v>
+        <v>187.528992</v>
       </c>
       <c r="B462" t="n">
-        <v>214.3059692382812</v>
+        <v>185.924149</v>
       </c>
       <c r="C462" t="n">
-        <v>-1.135055541992188</v>
+        <v>1.604842999999988</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
-        <v>217.3228149414062</v>
+        <v>187.63797</v>
       </c>
       <c r="B463" t="n">
-        <v>213.1709136962891</v>
+        <v>187.528992</v>
       </c>
       <c r="C463" t="n">
-        <v>4.151901245117188</v>
+        <v>0.1089780000000076</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
-        <v>219.7721557617188</v>
+        <v>186.558167</v>
       </c>
       <c r="B464" t="n">
-        <v>217.3228149414062</v>
+        <v>187.63797</v>
       </c>
       <c r="C464" t="n">
-        <v>2.4493408203125</v>
+        <v>-1.079802999999998</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
-        <v>222.779052734375</v>
+        <v>187.321945</v>
       </c>
       <c r="B465" t="n">
-        <v>219.7721557617188</v>
+        <v>186.558167</v>
       </c>
       <c r="C465" t="n">
-        <v>3.00689697265625</v>
+        <v>0.7637780000000021</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
-        <v>220.5686645507812</v>
+        <v>185.635666</v>
       </c>
       <c r="B466" t="n">
-        <v>222.779052734375</v>
+        <v>187.321945</v>
       </c>
       <c r="C466" t="n">
-        <v>-2.21038818359375</v>
+        <v>-1.686279000000013</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
-        <v>222.8786010742188</v>
+        <v>183.542755</v>
       </c>
       <c r="B467" t="n">
-        <v>220.5686645507812</v>
+        <v>185.635666</v>
       </c>
       <c r="C467" t="n">
-        <v>2.3099365234375</v>
+        <v>-2.092910999999987</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
-        <v>216.9544067382812</v>
+        <v>182.659943</v>
       </c>
       <c r="B468" t="n">
-        <v>222.8786010742188</v>
+        <v>183.542755</v>
       </c>
       <c r="C468" t="n">
-        <v>-5.9241943359375</v>
+        <v>-0.8828120000000013</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
-        <v>221.1660614013672</v>
+        <v>182.372299</v>
       </c>
       <c r="B469" t="n">
-        <v>216.9544067382812</v>
+        <v>182.659943</v>
       </c>
       <c r="C469" t="n">
-        <v>4.211654663085938</v>
+        <v>-0.2876440000000002</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
-        <v>222.2214660644531</v>
+        <v>180.834839</v>
       </c>
       <c r="B470" t="n">
-        <v>221.1660614013672</v>
+        <v>182.372299</v>
       </c>
       <c r="C470" t="n">
-        <v>1.055404663085938</v>
+        <v>-1.53746000000001</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
-        <v>222.9184265136719</v>
+        <v>180.090912</v>
       </c>
       <c r="B471" t="n">
-        <v>222.2214660644531</v>
+        <v>180.834839</v>
       </c>
       <c r="C471" t="n">
-        <v>0.69696044921875</v>
+        <v>-0.7439269999999851</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
-        <v>202.3082580566407</v>
+        <v>180.844772</v>
       </c>
       <c r="B472" t="n">
-        <v>222.9184265136719</v>
+        <v>180.090912</v>
       </c>
       <c r="C472" t="n">
-        <v>-20.61016845703122</v>
+        <v>0.7538600000000031</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
-        <v>187.5625305175781</v>
+        <v>182.878174</v>
       </c>
       <c r="B473" t="n">
-        <v>202.3082580566407</v>
+        <v>180.844772</v>
       </c>
       <c r="C473" t="n">
-        <v>-14.74572753906259</v>
+        <v>2.033401999999995</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
-        <v>180.6725616455078</v>
+        <v>181.043152</v>
       </c>
       <c r="B474" t="n">
-        <v>187.5625305175781</v>
+        <v>182.878174</v>
       </c>
       <c r="C474" t="n">
-        <v>-6.889968872070256</v>
+        <v>-1.835022000000009</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
-        <v>171.6717987060547</v>
+        <v>179.694153</v>
       </c>
       <c r="B475" t="n">
-        <v>180.6725616455078</v>
+        <v>181.043152</v>
       </c>
       <c r="C475" t="n">
-        <v>-9.000762939453125</v>
+        <v>-1.348998999999992</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
-        <v>197.9870910644531</v>
+        <v>181.152252</v>
       </c>
       <c r="B476" t="n">
-        <v>171.6717987060547</v>
+        <v>179.694153</v>
       </c>
       <c r="C476" t="n">
-        <v>26.31529235839844</v>
+        <v>1.458099000000004</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
-        <v>189.5936584472656</v>
+        <v>179.952042</v>
       </c>
       <c r="B477" t="n">
-        <v>197.9870910644531</v>
+        <v>181.152252</v>
       </c>
       <c r="C477" t="n">
-        <v>-8.393432617187528</v>
+        <v>-1.200209999999998</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
-        <v>197.2901306152344</v>
+        <v>179.287476</v>
       </c>
       <c r="B478" t="n">
-        <v>189.5936584472656</v>
+        <v>179.952042</v>
       </c>
       <c r="C478" t="n">
-        <v>7.696472167968807</v>
+        <v>-0.6645660000000078</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
-        <v>201.6411590576172</v>
+        <v>178.206299</v>
       </c>
       <c r="B479" t="n">
-        <v>197.2901306152344</v>
+        <v>179.287476</v>
       </c>
       <c r="C479" t="n">
-        <v>4.351028442382756</v>
+        <v>-1.081176999999997</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
-        <v>201.2628173828125</v>
+        <v>173.683167</v>
       </c>
       <c r="B480" t="n">
-        <v>201.6411590576172</v>
+        <v>178.206299</v>
       </c>
       <c r="C480" t="n">
-        <v>-0.3783416748046591</v>
+        <v>-4.523132000000004</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
-        <v>193.4269561767578</v>
+        <v>168.743469</v>
       </c>
       <c r="B481" t="n">
-        <v>201.2628173828125</v>
+        <v>173.683167</v>
       </c>
       <c r="C481" t="n">
-        <v>-7.835861206054688</v>
+        <v>-4.939697999999993</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
-        <v>196.1251983642578</v>
+        <v>167.751556</v>
       </c>
       <c r="B482" t="n">
-        <v>193.4269561767578</v>
+        <v>168.743469</v>
       </c>
       <c r="C482" t="n">
-        <v>2.6982421875</v>
+        <v>-0.9919130000000109</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
-        <v>192.3217620849609</v>
+        <v>167.632538</v>
       </c>
       <c r="B483" t="n">
-        <v>196.1251983642578</v>
+        <v>167.751556</v>
       </c>
       <c r="C483" t="n">
-        <v>-3.803436279296903</v>
+        <v>-0.1190179999999827</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
-        <v>198.8732452392578</v>
+        <v>169.348557</v>
       </c>
       <c r="B484" t="n">
-        <v>192.3217620849609</v>
+        <v>167.632538</v>
       </c>
       <c r="C484" t="n">
-        <v>6.551483154296932</v>
+        <v>1.716018999999989</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
-        <v>203.712142944336</v>
+        <v>171.352203</v>
       </c>
       <c r="B485" t="n">
-        <v>198.8732452392578</v>
+        <v>169.348557</v>
       </c>
       <c r="C485" t="n">
-        <v>4.838897705078153</v>
+        <v>2.003646000000003</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
-        <v>207.4657745361328</v>
+        <v>171.828293</v>
       </c>
       <c r="B486" t="n">
-        <v>203.712142944336</v>
+        <v>171.352203</v>
       </c>
       <c r="C486" t="n">
-        <v>3.753631591796818</v>
+        <v>0.4760899999999992</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
-        <v>208.371810913086</v>
+        <v>169.7453</v>
       </c>
       <c r="B487" t="n">
-        <v>207.4657745361328</v>
+        <v>171.828293</v>
       </c>
       <c r="C487" t="n">
-        <v>0.9060363769531818</v>
+        <v>-2.082993000000016</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
-        <v>209.2281188964844</v>
+        <v>171.600159</v>
       </c>
       <c r="B488" t="n">
-        <v>208.371810913086</v>
+        <v>169.7453</v>
       </c>
       <c r="C488" t="n">
-        <v>0.8563079833984091</v>
+        <v>1.854859000000005</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
-        <v>210.29345703125</v>
+        <v>171.223267</v>
       </c>
       <c r="B489" t="n">
-        <v>209.2281188964844</v>
+        <v>171.600159</v>
       </c>
       <c r="C489" t="n">
-        <v>1.065338134765597</v>
+        <v>-0.376891999999998</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
-        <v>211.5778503417969</v>
+        <v>172.314346</v>
       </c>
       <c r="B490" t="n">
-        <v>210.29345703125</v>
+        <v>171.223267</v>
       </c>
       <c r="C490" t="n">
-        <v>1.284393310546875</v>
+        <v>1.091079000000008</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
-        <v>212.3943023681641</v>
+        <v>174.655243</v>
       </c>
       <c r="B491" t="n">
-        <v>211.5778503417969</v>
+        <v>172.314346</v>
       </c>
       <c r="C491" t="n">
-        <v>0.8164520263672159</v>
+        <v>2.340897000000012</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
-        <v>204.4588928222656</v>
+        <v>177.224304</v>
       </c>
       <c r="B492" t="n">
-        <v>212.3943023681641</v>
+        <v>174.655243</v>
       </c>
       <c r="C492" t="n">
-        <v>-7.935409545898494</v>
+        <v>2.569060999999977</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
-        <v>198.0269165039062</v>
+        <v>169.983353</v>
       </c>
       <c r="B493" t="n">
-        <v>204.4588928222656</v>
+        <v>177.224304</v>
       </c>
       <c r="C493" t="n">
-        <v>-6.431976318359347</v>
+        <v>-7.240950999999995</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
-        <v>197.6485748291016</v>
+        <v>170.886002</v>
       </c>
       <c r="B494" t="n">
-        <v>198.0269165039062</v>
+        <v>169.983353</v>
       </c>
       <c r="C494" t="n">
-        <v>-0.3783416748046591</v>
+        <v>0.9026489999999967</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
-        <v>195.3983764648437</v>
+        <v>169.46756</v>
       </c>
       <c r="B495" t="n">
-        <v>197.6485748291016</v>
+        <v>170.886002</v>
       </c>
       <c r="C495" t="n">
-        <v>-2.250198364257898</v>
+        <v>-1.418441999999999</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
-        <v>196.6329956054688</v>
+        <v>168.336807</v>
       </c>
       <c r="B496" t="n">
-        <v>195.3983764648437</v>
+        <v>169.46756</v>
       </c>
       <c r="C496" t="n">
-        <v>1.234619140625057</v>
+        <v>-1.130752999999999</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
-        <v>197.668472290039</v>
+        <v>171.907654</v>
       </c>
       <c r="B497" t="n">
-        <v>196.6329956054688</v>
+        <v>168.336807</v>
       </c>
       <c r="C497" t="n">
-        <v>1.035476684570284</v>
+        <v>3.570847000000015</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
-        <v>210.1504821777344</v>
+        <v>170.092453</v>
       </c>
       <c r="B498" t="n">
-        <v>197.668472290039</v>
+        <v>171.907654</v>
       </c>
       <c r="C498" t="n">
-        <v>12.48200988769537</v>
+        <v>-1.815201000000002</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
-        <v>212.2839965820312</v>
+        <v>168.654205</v>
       </c>
       <c r="B499" t="n">
-        <v>210.1504821777344</v>
+        <v>170.092453</v>
       </c>
       <c r="C499" t="n">
-        <v>2.133514404296847</v>
+        <v>-1.438248000000016</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
-        <v>211.6858367919922</v>
+        <v>167.473831</v>
       </c>
       <c r="B500" t="n">
-        <v>212.2839965820312</v>
+        <v>168.654205</v>
       </c>
       <c r="C500" t="n">
-        <v>-0.5981597900390625</v>
+        <v>-1.180374</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="n">
-        <v>210.8085021972656</v>
+        <v>168.277283</v>
       </c>
       <c r="B501" t="n">
-        <v>211.6858367919922</v>
+        <v>167.473831</v>
       </c>
       <c r="C501" t="n">
-        <v>-0.8773345947265909</v>
+        <v>0.8034520000000214</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="n">
-        <v>210.6190643310547</v>
+        <v>167.453995</v>
       </c>
       <c r="B502" t="n">
-        <v>210.8085021972656</v>
+        <v>168.277283</v>
       </c>
       <c r="C502" t="n">
-        <v>-0.1894378662109091</v>
+        <v>-0.8232880000000193</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="n">
-        <v>208.1465911865234</v>
+        <v>168.20784</v>
       </c>
       <c r="B503" t="n">
-        <v>210.6190643310547</v>
+        <v>167.453995</v>
       </c>
       <c r="C503" t="n">
-        <v>-2.47247314453125</v>
+        <v>0.7538450000000125</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="n">
-        <v>206.232421875</v>
+        <v>167.087021</v>
       </c>
       <c r="B504" t="n">
-        <v>208.1465911865234</v>
+        <v>168.20784</v>
       </c>
       <c r="C504" t="n">
-        <v>-1.914169311523438</v>
+        <v>-1.120819000000012</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="n">
-        <v>201.4768981933593</v>
+        <v>168.297119</v>
       </c>
       <c r="B505" t="n">
-        <v>206.232421875</v>
+        <v>167.087021</v>
       </c>
       <c r="C505" t="n">
-        <v>-4.755523681640682</v>
+        <v>1.210098000000016</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="n">
-        <v>200.7490997314453</v>
+        <v>166.422409</v>
       </c>
       <c r="B506" t="n">
-        <v>201.4768981933593</v>
+        <v>168.297119</v>
       </c>
       <c r="C506" t="n">
-        <v>-0.7277984619140057</v>
+        <v>-1.874710000000022</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="n">
-        <v>194.6775817871093</v>
+        <v>173.623657</v>
       </c>
       <c r="B507" t="n">
-        <v>200.7490997314453</v>
+        <v>166.422409</v>
       </c>
       <c r="C507" t="n">
-        <v>-6.071517944335994</v>
+        <v>7.201248000000021</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="n">
-        <v>199.6026000976562</v>
+        <v>175.121429</v>
       </c>
       <c r="B508" t="n">
-        <v>194.6775817871093</v>
+        <v>173.623657</v>
       </c>
       <c r="C508" t="n">
-        <v>4.925018310546932</v>
+        <v>1.497771999999998</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="n">
-        <v>199.8119659423828</v>
+        <v>171.292694</v>
       </c>
       <c r="B509" t="n">
-        <v>199.6026000976562</v>
+        <v>175.121429</v>
       </c>
       <c r="C509" t="n">
-        <v>0.2093658447265625</v>
+        <v>-3.828734999999995</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="n">
-        <v>199.3433837890625</v>
+        <v>168.009476</v>
       </c>
       <c r="B510" t="n">
-        <v>199.8119659423828</v>
+        <v>171.292694</v>
       </c>
       <c r="C510" t="n">
-        <v>-0.4685821533203125</v>
+        <v>-3.283218000000005</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="n">
-        <v>200.2406616210937</v>
+        <v>166.640625</v>
       </c>
       <c r="B511" t="n">
-        <v>199.3433837890625</v>
+        <v>168.009476</v>
       </c>
       <c r="C511" t="n">
-        <v>0.8972778320311932</v>
+        <v>-1.368851000000006</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="n">
-        <v>201.0880737304688</v>
+        <v>165.6884</v>
       </c>
       <c r="B512" t="n">
-        <v>200.2406616210937</v>
+        <v>166.640625</v>
       </c>
       <c r="C512" t="n">
-        <v>0.8474121093750568</v>
+        <v>-0.9522249999999985</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="n">
-        <v>202.6533203125</v>
+        <v>163.664917</v>
       </c>
       <c r="B513" t="n">
-        <v>201.0880737304688</v>
+        <v>165.6884</v>
       </c>
       <c r="C513" t="n">
-        <v>1.565246582031222</v>
+        <v>-2.023482999999999</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="n">
-        <v>202.2046661376953</v>
+        <v>164.498093</v>
       </c>
       <c r="B514" t="n">
-        <v>202.6533203125</v>
+        <v>163.664917</v>
       </c>
       <c r="C514" t="n">
-        <v>-0.4486541748046591</v>
+        <v>0.8331760000000088</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="n">
-        <v>200.0213165283203</v>
+        <v>165.54953</v>
       </c>
       <c r="B515" t="n">
-        <v>202.2046661376953</v>
+        <v>164.498093</v>
       </c>
       <c r="C515" t="n">
-        <v>-2.183349609375</v>
+        <v>1.051436999999993</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="n">
-        <v>203.3013305664062</v>
+        <v>167.65239</v>
       </c>
       <c r="B516" t="n">
-        <v>200.0213165283203</v>
+        <v>165.54953</v>
       </c>
       <c r="C516" t="n">
-        <v>3.280014038085938</v>
+        <v>2.102859999999993</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="n">
-        <v>200.8388214111328</v>
+        <v>168.51535</v>
       </c>
       <c r="B517" t="n">
-        <v>203.3013305664062</v>
+        <v>167.65239</v>
       </c>
       <c r="C517" t="n">
-        <v>-2.462509155273438</v>
+        <v>0.8629600000000153</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="n">
-        <v>202.0551300048828</v>
+        <v>167.930115</v>
       </c>
       <c r="B518" t="n">
-        <v>200.8388214111328</v>
+        <v>168.51535</v>
       </c>
       <c r="C518" t="n">
-        <v>1.21630859375</v>
+        <v>-0.5852350000000115</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="n">
-        <v>198.1769256591797</v>
+        <v>172.096115</v>
       </c>
       <c r="B519" t="n">
-        <v>202.0551300048828</v>
+        <v>167.930115</v>
       </c>
       <c r="C519" t="n">
-        <v>-3.878204345703125</v>
+        <v>4.165999999999997</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="n">
-        <v>198.5956573486328</v>
+        <v>168.951782</v>
       </c>
       <c r="B520" t="n">
-        <v>198.1769256591797</v>
+        <v>172.096115</v>
       </c>
       <c r="C520" t="n">
-        <v>0.4187316894531534</v>
+        <v>-3.144332999999989</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="n">
-        <v>195.85400390625</v>
+        <v>167.930115</v>
       </c>
       <c r="B521" t="n">
-        <v>198.5956573486328</v>
+        <v>168.951782</v>
       </c>
       <c r="C521" t="n">
-        <v>-2.741653442382841</v>
+        <v>-1.021667000000008</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="n">
-        <v>197.8180236816407</v>
+        <v>171.629929</v>
       </c>
       <c r="B522" t="n">
-        <v>195.85400390625</v>
+        <v>167.930115</v>
       </c>
       <c r="C522" t="n">
-        <v>1.964019775390653</v>
+        <v>3.699814000000003</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="n">
-        <v>195.0464477539062</v>
+        <v>181.896179</v>
       </c>
       <c r="B523" t="n">
-        <v>197.8180236816407</v>
+        <v>171.629929</v>
       </c>
       <c r="C523" t="n">
-        <v>-2.771575927734403</v>
+        <v>10.26624999999999</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="n">
-        <v>195.9836120605468</v>
+        <v>180.2397</v>
       </c>
       <c r="B524" t="n">
-        <v>195.0464477539062</v>
+        <v>181.896179</v>
       </c>
       <c r="C524" t="n">
-        <v>0.9371643066405966</v>
+        <v>-1.65647899999999</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="n">
-        <v>200.3901977539062</v>
+        <v>180.924118</v>
       </c>
       <c r="B525" t="n">
-        <v>195.9836120605468</v>
+        <v>180.2397</v>
       </c>
       <c r="C525" t="n">
-        <v>4.406585693359375</v>
+        <v>0.6844179999999938</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="n">
-        <v>200.888671875</v>
+        <v>181.261368</v>
       </c>
       <c r="B526" t="n">
-        <v>200.3901977539062</v>
+        <v>180.924118</v>
       </c>
       <c r="C526" t="n">
-        <v>0.4984741210937784</v>
+        <v>0.3372500000000116</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="n">
-        <v>199.6923217773437</v>
+        <v>183.076553</v>
       </c>
       <c r="B527" t="n">
-        <v>200.888671875</v>
+        <v>181.261368</v>
       </c>
       <c r="C527" t="n">
-        <v>-1.196350097656307</v>
+        <v>1.815184999999985</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="n">
-        <v>200.948486328125</v>
+        <v>181.815125</v>
       </c>
       <c r="B528" t="n">
-        <v>199.6923217773437</v>
+        <v>183.076553</v>
       </c>
       <c r="C528" t="n">
-        <v>1.256164550781307</v>
+        <v>-1.261427999999995</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="n">
-        <v>200.3901977539062</v>
+        <v>185.023331</v>
       </c>
       <c r="B529" t="n">
-        <v>200.948486328125</v>
+        <v>181.815125</v>
       </c>
       <c r="C529" t="n">
-        <v>-0.5582885742187784</v>
+        <v>3.208206000000018</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="n">
-        <v>200.469970703125</v>
+        <v>186.165573</v>
       </c>
       <c r="B530" t="n">
-        <v>200.3901977539062</v>
+        <v>185.023331</v>
       </c>
       <c r="C530" t="n">
-        <v>0.07977294921875</v>
+        <v>1.142241999999982</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="n">
-        <v>204.5475463867188</v>
+        <v>188.440125</v>
       </c>
       <c r="B531" t="n">
-        <v>200.469970703125</v>
+        <v>186.165573</v>
       </c>
       <c r="C531" t="n">
-        <v>4.077575683593778</v>
+        <v>2.274552</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="n">
-        <v>207.1895141601562</v>
+        <v>188.559311</v>
       </c>
       <c r="B532" t="n">
-        <v>204.5475463867188</v>
+        <v>188.440125</v>
       </c>
       <c r="C532" t="n">
-        <v>2.6419677734375</v>
+        <v>0.1191860000000133</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="n">
-        <v>211.7954864501953</v>
+        <v>188.589127</v>
       </c>
       <c r="B533" t="n">
-        <v>207.1895141601562</v>
+        <v>188.559311</v>
       </c>
       <c r="C533" t="n">
-        <v>4.605972290039062</v>
+        <v>0.02981599999998252</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="n">
-        <v>212.9021148681641</v>
+        <v>189.751205</v>
       </c>
       <c r="B534" t="n">
-        <v>211.7954864501953</v>
+        <v>188.589127</v>
       </c>
       <c r="C534" t="n">
-        <v>1.106628417968778</v>
+        <v>1.162078000000008</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="n">
-        <v>209.3130340576172</v>
+        <v>191.052383</v>
       </c>
       <c r="B535" t="n">
-        <v>212.9021148681641</v>
+        <v>189.751205</v>
       </c>
       <c r="C535" t="n">
-        <v>-3.589080810546903</v>
+        <v>1.301177999999993</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="n">
-        <v>209.3728637695312</v>
+        <v>189.612167</v>
       </c>
       <c r="B536" t="n">
-        <v>209.3130340576172</v>
+        <v>191.052383</v>
       </c>
       <c r="C536" t="n">
-        <v>0.0598297119140625</v>
+        <v>-1.440215999999992</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="n">
-        <v>210.4994354248047</v>
+        <v>185.619293</v>
       </c>
       <c r="B537" t="n">
-        <v>209.3728637695312</v>
+        <v>189.612167</v>
       </c>
       <c r="C537" t="n">
-        <v>1.126571655273438</v>
+        <v>-3.992874</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="n">
-        <v>211.7655944824219</v>
+        <v>188.698364</v>
       </c>
       <c r="B538" t="n">
-        <v>210.4994354248047</v>
+        <v>185.619293</v>
       </c>
       <c r="C538" t="n">
-        <v>1.266159057617188</v>
+        <v>3.079070999999999</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="n">
-        <v>210.5193634033203</v>
+        <v>188.708298</v>
       </c>
       <c r="B539" t="n">
-        <v>211.7655944824219</v>
+        <v>188.698364</v>
       </c>
       <c r="C539" t="n">
-        <v>-1.246231079101534</v>
+        <v>0.00993400000001543</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="n">
-        <v>207.9870758056641</v>
+        <v>189.006287</v>
       </c>
       <c r="B540" t="n">
-        <v>210.5193634033203</v>
+        <v>188.708298</v>
       </c>
       <c r="C540" t="n">
-        <v>-2.53228759765625</v>
+        <v>0.2979889999999727</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="n">
-        <v>208.475601196289</v>
+        <v>189.999527</v>
       </c>
       <c r="B541" t="n">
-        <v>207.9870758056641</v>
+        <v>189.006287</v>
       </c>
       <c r="C541" t="n">
-        <v>0.4885253906249432</v>
+        <v>0.9932400000000143</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="n">
-        <v>209.5223999023437</v>
+        <v>190.953064</v>
       </c>
       <c r="B542" t="n">
-        <v>208.475601196289</v>
+        <v>189.999527</v>
       </c>
       <c r="C542" t="n">
-        <v>1.046798706054631</v>
+        <v>0.9535370000000114</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="n">
-        <v>209.382827758789</v>
+        <v>192.721054</v>
       </c>
       <c r="B543" t="n">
-        <v>209.5223999023437</v>
+        <v>190.953064</v>
       </c>
       <c r="C543" t="n">
-        <v>-0.1395721435546307</v>
+        <v>1.767989999999998</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="n">
-        <v>210.539306640625</v>
+        <v>193.03891</v>
       </c>
       <c r="B544" t="n">
-        <v>209.382827758789</v>
+        <v>192.721054</v>
       </c>
       <c r="C544" t="n">
-        <v>1.156478881835994</v>
+        <v>0.3178559999999777</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="n">
-        <v>211.8353729248047</v>
+        <v>194.548645</v>
       </c>
       <c r="B545" t="n">
-        <v>210.539306640625</v>
+        <v>193.03891</v>
       </c>
       <c r="C545" t="n">
-        <v>1.296066284179659</v>
+        <v>1.509735000000006</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="n">
-        <v>213.749526977539</v>
+        <v>193.168015</v>
       </c>
       <c r="B546" t="n">
-        <v>211.8353729248047</v>
+        <v>194.548645</v>
       </c>
       <c r="C546" t="n">
-        <v>1.914154052734347</v>
+        <v>-1.380629999999996</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="n">
-        <v>213.5003051757812</v>
+        <v>195.561752</v>
       </c>
       <c r="B547" t="n">
-        <v>213.749526977539</v>
+        <v>193.168015</v>
       </c>
       <c r="C547" t="n">
-        <v>-0.2492218017577841</v>
+        <v>2.393737000000016</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="n">
-        <v>213.1114807128907</v>
+        <v>191.817184</v>
       </c>
       <c r="B548" t="n">
-        <v>213.5003051757812</v>
+        <v>195.561752</v>
       </c>
       <c r="C548" t="n">
-        <v>-0.3888244628905966</v>
+        <v>-3.744568000000015</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="n">
-        <v>213.2311248779297</v>
+        <v>205.752533</v>
       </c>
       <c r="B549" t="n">
-        <v>213.1114807128907</v>
+        <v>191.817184</v>
       </c>
       <c r="C549" t="n">
-        <v>0.1196441650390341</v>
+        <v>13.935349</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="n">
-        <v>213.400619506836</v>
+        <v>211.632614</v>
       </c>
       <c r="B550" t="n">
-        <v>213.2311248779297</v>
+        <v>205.752533</v>
       </c>
       <c r="C550" t="n">
-        <v>0.1694946289063068</v>
+        <v>5.88008099999999</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="n">
-        <v>210.6290435791016</v>
+        <v>212.794739</v>
       </c>
       <c r="B551" t="n">
-        <v>213.400619506836</v>
+        <v>211.632614</v>
       </c>
       <c r="C551" t="n">
-        <v>-2.771575927734403</v>
+        <v>1.162125000000003</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="n">
-        <v>208.415771484375</v>
+        <v>211.056519</v>
       </c>
       <c r="B552" t="n">
-        <v>210.6290435791016</v>
+        <v>212.794739</v>
       </c>
       <c r="C552" t="n">
-        <v>-2.213272094726591</v>
+        <v>-1.738219999999984</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="n">
-        <v>206.9402770996093</v>
+        <v>215.208313</v>
       </c>
       <c r="B553" t="n">
-        <v>208.415771484375</v>
+        <v>211.056519</v>
       </c>
       <c r="C553" t="n">
-        <v>-1.47549438476571</v>
+        <v>4.151793999999995</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="n">
-        <v>201.7660064697266</v>
+        <v>212.84436</v>
       </c>
       <c r="B554" t="n">
-        <v>206.9402770996093</v>
+        <v>215.208313</v>
       </c>
       <c r="C554" t="n">
-        <v>-5.174270629882727</v>
+        <v>-2.363953000000009</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="n">
-        <v>202.7330780029297</v>
+        <v>208.265457</v>
       </c>
       <c r="B555" t="n">
-        <v>201.7660064697266</v>
+        <v>212.84436</v>
       </c>
       <c r="C555" t="n">
-        <v>0.967071533203125</v>
+        <v>-4.578902999999997</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="n">
-        <v>202.3043670654297</v>
+        <v>206.090271</v>
       </c>
       <c r="B556" t="n">
-        <v>202.7330780029297</v>
+        <v>208.265457</v>
       </c>
       <c r="C556" t="n">
-        <v>-0.4287109375</v>
+        <v>-2.175185999999997</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="n">
-        <v>212.60302734375</v>
+        <v>206.73587</v>
       </c>
       <c r="B557" t="n">
-        <v>202.3043670654297</v>
+        <v>206.090271</v>
       </c>
       <c r="C557" t="n">
-        <v>10.29866027832031</v>
+        <v>0.6455990000000043</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="n">
-        <v>219.3624572753907</v>
+        <v>207.659592</v>
       </c>
       <c r="B558" t="n">
-        <v>212.60302734375</v>
+        <v>206.73587</v>
       </c>
       <c r="C558" t="n">
-        <v>6.759429931640653</v>
+        <v>0.9237219999999979</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="n">
-        <v>228.6541748046875</v>
+        <v>211.811371</v>
       </c>
       <c r="B559" t="n">
-        <v>219.3624572753907</v>
+        <v>207.659592</v>
       </c>
       <c r="C559" t="n">
-        <v>9.291717529296847</v>
+        <v>4.151779000000005</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="n">
-        <v>226.747802734375</v>
+        <v>212.655685</v>
       </c>
       <c r="B560" t="n">
-        <v>228.6541748046875</v>
+        <v>211.811371</v>
       </c>
       <c r="C560" t="n">
-        <v>-1.9063720703125</v>
+        <v>0.8443139999999971</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="n">
-        <v>229.2131042480469</v>
+        <v>209.199127</v>
       </c>
       <c r="B561" t="n">
-        <v>226.747802734375</v>
+        <v>212.655685</v>
       </c>
       <c r="C561" t="n">
-        <v>2.465301513671875</v>
+        <v>-3.456558000000001</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="n">
-        <v>232.8861236572266</v>
+        <v>215.287781</v>
       </c>
       <c r="B562" t="n">
-        <v>229.2131042480469</v>
+        <v>209.199127</v>
       </c>
       <c r="C562" t="n">
-        <v>3.673019409179688</v>
+        <v>6.088653999999991</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="n">
-        <v>232.337158203125</v>
+        <v>218.784027</v>
       </c>
       <c r="B563" t="n">
-        <v>232.8861236572266</v>
+        <v>215.287781</v>
       </c>
       <c r="C563" t="n">
-        <v>-0.5489654541015625</v>
+        <v>3.496246000000014</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="n">
-        <v>231.1494140625</v>
+        <v>220.055405</v>
       </c>
       <c r="B564" t="n">
-        <v>232.337158203125</v>
+        <v>218.784027</v>
       </c>
       <c r="C564" t="n">
-        <v>-1.187744140625</v>
+        <v>1.271377999999999</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="n">
-        <v>230.4507598876953</v>
+        <v>224.81308</v>
       </c>
       <c r="B565" t="n">
-        <v>231.1494140625</v>
+        <v>220.055405</v>
       </c>
       <c r="C565" t="n">
-        <v>-0.6986541748046591</v>
+        <v>4.757675000000006</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="n">
-        <v>230.1213836669922</v>
+        <v>226.283112</v>
       </c>
       <c r="B566" t="n">
-        <v>230.4507598876953</v>
+        <v>224.81308</v>
       </c>
       <c r="C566" t="n">
-        <v>-0.3293762207031534</v>
+        <v>1.470031999999975</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="n">
-        <v>225.5800323486328</v>
+        <v>227.137283</v>
       </c>
       <c r="B567" t="n">
-        <v>230.1213836669922</v>
+        <v>226.283112</v>
       </c>
       <c r="C567" t="n">
-        <v>-4.541351318359375</v>
+        <v>0.854171000000008</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="n">
-        <v>224.4721527099609</v>
+        <v>231.408279</v>
       </c>
       <c r="B568" t="n">
-        <v>225.5800323486328</v>
+        <v>227.137283</v>
       </c>
       <c r="C568" t="n">
-        <v>-1.107879638671932</v>
+        <v>4.270995999999997</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="n">
-        <v>227.3267059326172</v>
+        <v>226.03479</v>
       </c>
       <c r="B569" t="n">
-        <v>224.4721527099609</v>
+        <v>231.408279</v>
       </c>
       <c r="C569" t="n">
-        <v>2.854553222656307</v>
+        <v>-5.373489000000006</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="n">
-        <v>226.7278442382812</v>
+        <v>228.984756</v>
       </c>
       <c r="B570" t="n">
-        <v>227.3267059326172</v>
+        <v>226.03479</v>
       </c>
       <c r="C570" t="n">
-        <v>-0.5988616943359375</v>
+        <v>2.949966000000018</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="n">
-        <v>228.873764038086</v>
+        <v>232.81871</v>
       </c>
       <c r="B571" t="n">
-        <v>226.7278442382812</v>
+        <v>228.984756</v>
       </c>
       <c r="C571" t="n">
-        <v>2.145919799804744</v>
+        <v>3.833954000000006</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="n">
-        <v>230.0515289306641</v>
+        <v>233.235886</v>
       </c>
       <c r="B572" t="n">
-        <v>228.873764038086</v>
+        <v>232.81871</v>
       </c>
       <c r="C572" t="n">
-        <v>1.177764892578097</v>
+        <v>0.4171759999999836</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="n">
-        <v>232.1175842285156</v>
+        <v>227.335953</v>
       </c>
       <c r="B573" t="n">
-        <v>230.0515289306641</v>
+        <v>233.235886</v>
       </c>
       <c r="C573" t="n">
-        <v>2.066055297851506</v>
+        <v>-5.899933000000004</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="n">
-        <v>231.6983795166016</v>
+        <v>222.667648</v>
       </c>
       <c r="B574" t="n">
-        <v>232.1175842285156</v>
+        <v>227.335953</v>
       </c>
       <c r="C574" t="n">
-        <v>-0.4192047119140057</v>
+        <v>-4.668304999999975</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="n">
-        <v>229.2829895019531</v>
+        <v>222.796783</v>
       </c>
       <c r="B575" t="n">
-        <v>231.6983795166016</v>
+        <v>222.667648</v>
       </c>
       <c r="C575" t="n">
-        <v>-2.415390014648466</v>
+        <v>0.1291349999999909</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="n">
-        <v>238.016342163086</v>
+        <v>222.449158</v>
       </c>
       <c r="B576" t="n">
-        <v>229.2829895019531</v>
+        <v>222.796783</v>
       </c>
       <c r="C576" t="n">
-        <v>8.733352661132869</v>
+        <v>-0.3476249999999936</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="n">
-        <v>239.3238372802734</v>
+        <v>223.492035</v>
       </c>
       <c r="B577" t="n">
-        <v>238.016342163086</v>
+        <v>222.449158</v>
       </c>
       <c r="C577" t="n">
-        <v>1.307495117187443</v>
+        <v>1.042876999999976</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="n">
-        <v>239.2340087890625</v>
+        <v>217.065674</v>
       </c>
       <c r="B578" t="n">
-        <v>239.3238372802734</v>
+        <v>223.492035</v>
       </c>
       <c r="C578" t="n">
-        <v>-0.08982849121096592</v>
+        <v>-6.426360999999986</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="n">
-        <v>237.4274597167969</v>
+        <v>216.022797</v>
       </c>
       <c r="B579" t="n">
-        <v>239.2340087890625</v>
+        <v>217.065674</v>
       </c>
       <c r="C579" t="n">
-        <v>-1.806549072265597</v>
+        <v>-1.042877000000004</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="n">
-        <v>233.9041748046875</v>
+        <v>216.489624</v>
       </c>
       <c r="B580" t="n">
-        <v>237.4274597167969</v>
+        <v>216.022797</v>
       </c>
       <c r="C580" t="n">
-        <v>-3.523284912109347</v>
+        <v>0.466826999999995</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="n">
-        <v>226.3585510253907</v>
+        <v>216.767731</v>
       </c>
       <c r="B581" t="n">
-        <v>233.9041748046875</v>
+        <v>216.489624</v>
       </c>
       <c r="C581" t="n">
-        <v>-7.545623779296875</v>
+        <v>0.2781070000000057</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="n">
-        <v>229.5923919677734</v>
+        <v>217.323959</v>
       </c>
       <c r="B582" t="n">
-        <v>226.3585510253907</v>
+        <v>216.767731</v>
       </c>
       <c r="C582" t="n">
-        <v>3.233840942382784</v>
+        <v>0.5562280000000044</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="n">
-        <v>233.6247100830078</v>
+        <v>220.581818</v>
       </c>
       <c r="B583" t="n">
-        <v>229.5923919677734</v>
+        <v>217.323959</v>
       </c>
       <c r="C583" t="n">
-        <v>4.032318115234375</v>
+        <v>3.257858999999996</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="n">
-        <v>236.2496948242188</v>
+        <v>216.886917</v>
       </c>
       <c r="B584" t="n">
-        <v>233.6247100830078</v>
+        <v>220.581818</v>
       </c>
       <c r="C584" t="n">
-        <v>2.624984741210938</v>
+        <v>-3.694900999999987</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="n">
-        <v>237.6969451904297</v>
+        <v>218.376801</v>
       </c>
       <c r="B585" t="n">
-        <v>236.2496948242188</v>
+        <v>216.886917</v>
       </c>
       <c r="C585" t="n">
-        <v>1.447250366210938</v>
+        <v>1.489883999999989</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="n">
-        <v>238.5353546142578</v>
+        <v>207.858246</v>
       </c>
       <c r="B586" t="n">
-        <v>237.6969451904297</v>
+        <v>218.376801</v>
       </c>
       <c r="C586" t="n">
-        <v>0.838409423828125</v>
+        <v>-10.51855499999999</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="n">
-        <v>237.4274597167969</v>
+        <v>205.832001</v>
       </c>
       <c r="B587" t="n">
-        <v>238.5353546142578</v>
+        <v>207.858246</v>
       </c>
       <c r="C587" t="n">
-        <v>-1.107894897460938</v>
+        <v>-2.026245000000017</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="n">
-        <v>245.032958984375</v>
+        <v>208.40451</v>
       </c>
       <c r="B588" t="n">
-        <v>237.4274597167969</v>
+        <v>205.832001</v>
       </c>
       <c r="C588" t="n">
-        <v>7.605499267578125</v>
+        <v>2.572508999999997</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="n">
-        <v>255.5928192138672</v>
+        <v>211.870987</v>
       </c>
       <c r="B589" t="n">
-        <v>245.032958984375</v>
+        <v>208.40451</v>
       </c>
       <c r="C589" t="n">
-        <v>10.55986022949219</v>
+        <v>3.466477000000026</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="n">
-        <v>253.9459686279297</v>
+        <v>214.781219</v>
       </c>
       <c r="B590" t="n">
-        <v>255.5928192138672</v>
+        <v>211.870987</v>
       </c>
       <c r="C590" t="n">
-        <v>-1.6468505859375</v>
+        <v>2.910231999999979</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="n">
-        <v>251.8300018310547</v>
+        <v>216.312607</v>
       </c>
       <c r="B591" t="n">
-        <v>253.9459686279297</v>
+        <v>214.781219</v>
       </c>
       <c r="C591" t="n">
-        <v>-2.115966796875</v>
+        <v>1.531388000000021</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="n">
-        <v>256.3813171386719</v>
+        <v>220.031693</v>
       </c>
       <c r="B592" t="n">
-        <v>251.8300018310547</v>
+        <v>216.312607</v>
       </c>
       <c r="C592" t="n">
-        <v>4.551315307617188</v>
+        <v>3.719085999999976</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="n">
-        <v>254.9740142822266</v>
+        <v>220.479156</v>
       </c>
       <c r="B593" t="n">
-        <v>256.3813171386719</v>
+        <v>220.031693</v>
       </c>
       <c r="C593" t="n">
-        <v>-1.407302856445312</v>
+        <v>0.4474629999999991</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="n">
-        <v>253.9459686279297</v>
+        <v>223.462357</v>
       </c>
       <c r="B594" t="n">
-        <v>254.9740142822266</v>
+        <v>220.479156</v>
       </c>
       <c r="C594" t="n">
-        <v>-1.028045654296875</v>
+        <v>2.983201000000008</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="n">
-        <v>254.1455993652344</v>
+        <v>224.784927</v>
       </c>
       <c r="B595" t="n">
-        <v>253.9459686279297</v>
+        <v>223.462357</v>
       </c>
       <c r="C595" t="n">
-        <v>0.1996307373047159</v>
+        <v>1.322570000000013</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="n">
-        <v>254.9640350341797</v>
+        <v>224.625824</v>
       </c>
       <c r="B596" t="n">
-        <v>254.1455993652344</v>
+        <v>224.784927</v>
       </c>
       <c r="C596" t="n">
-        <v>0.8184356689452557</v>
+        <v>-0.159103000000016</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="n">
-        <v>256.6408386230469</v>
+        <v>225.24234</v>
       </c>
       <c r="B597" t="n">
-        <v>254.9640350341797</v>
+        <v>224.625824</v>
       </c>
       <c r="C597" t="n">
-        <v>1.676803588867216</v>
+        <v>0.6165160000000185</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="n">
-        <v>257.5291442871094</v>
+        <v>225.132965</v>
       </c>
       <c r="B598" t="n">
-        <v>256.6408386230469</v>
+        <v>225.24234</v>
       </c>
       <c r="C598" t="n">
-        <v>0.8883056640625</v>
+        <v>-0.109375</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="n">
-        <v>256.20166015625</v>
+        <v>223.273438</v>
       </c>
       <c r="B599" t="n">
-        <v>257.5291442871094</v>
+        <v>225.132965</v>
       </c>
       <c r="C599" t="n">
-        <v>-1.327484130859375</v>
+        <v>-1.859527000000014</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="n">
-        <v>255.9920959472656</v>
+        <v>225.570496</v>
       </c>
       <c r="B600" t="n">
-        <v>256.20166015625</v>
+        <v>223.273438</v>
       </c>
       <c r="C600" t="n">
-        <v>-0.209564208984375</v>
+        <v>2.297057999999993</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="n">
-        <v>257.569091796875</v>
+        <v>225.9086</v>
       </c>
       <c r="B601" t="n">
-        <v>255.9920959472656</v>
+        <v>225.570496</v>
       </c>
       <c r="C601" t="n">
-        <v>1.576995849609375</v>
+        <v>0.3381040000000155</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="n">
-        <v>253.5567016601562</v>
+        <v>226.753845</v>
       </c>
       <c r="B602" t="n">
-        <v>257.569091796875</v>
+        <v>225.9086</v>
       </c>
       <c r="C602" t="n">
-        <v>-4.01239013671875</v>
+        <v>0.8452450000000056</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="n">
-        <v>244.8034057617188</v>
+        <v>225.222473</v>
       </c>
       <c r="B603" t="n">
-        <v>253.5567016601562</v>
+        <v>226.753845</v>
       </c>
       <c r="C603" t="n">
-        <v>-8.7532958984375</v>
+        <v>-1.531372000000005</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="n">
-        <v>247.1888580322266</v>
+        <v>228.503998</v>
       </c>
       <c r="B604" t="n">
-        <v>244.8034057617188</v>
+        <v>225.222473</v>
       </c>
       <c r="C604" t="n">
-        <v>2.385452270507812</v>
+        <v>3.281524999999988</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="n">
-        <v>247.2986450195312</v>
+        <v>227.718414</v>
       </c>
       <c r="B605" t="n">
-        <v>247.1888580322266</v>
+        <v>228.503998</v>
       </c>
       <c r="C605" t="n">
-        <v>0.1097869873046591</v>
+        <v>-0.7855840000000001</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="n">
-        <v>248.8656616210937</v>
+        <v>221.523285</v>
       </c>
       <c r="B606" t="n">
-        <v>247.2986450195312</v>
+        <v>227.718414</v>
       </c>
       <c r="C606" t="n">
-        <v>1.567016601562472</v>
+        <v>-6.195129000000009</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="n">
-        <v>246.9792633056641</v>
+        <v>219.614044</v>
       </c>
       <c r="B607" t="n">
-        <v>248.8656616210937</v>
+        <v>221.523285</v>
       </c>
       <c r="C607" t="n">
-        <v>-1.886398315429602</v>
+        <v>-1.90924099999998</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="n">
-        <v>251.8100280761719</v>
+        <v>221.135483</v>
       </c>
       <c r="B608" t="n">
-        <v>246.9792633056641</v>
+        <v>219.614044</v>
       </c>
       <c r="C608" t="n">
-        <v>4.830764770507784</v>
+        <v>1.521438999999987</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="n">
-        <v>261.7411193847656</v>
+        <v>219.584198</v>
       </c>
       <c r="B609" t="n">
-        <v>251.8100280761719</v>
+        <v>221.135483</v>
       </c>
       <c r="C609" t="n">
-        <v>9.93109130859375</v>
+        <v>-1.551285000000007</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="n">
-        <v>262.2700805664062</v>
+        <v>219.673706</v>
       </c>
       <c r="B610" t="n">
-        <v>261.7411193847656</v>
+        <v>219.584198</v>
       </c>
       <c r="C610" t="n">
-        <v>0.528961181640625</v>
+        <v>0.08950800000002346</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="n">
-        <v>257.9583435058594</v>
+        <v>218.878159</v>
       </c>
       <c r="B611" t="n">
-        <v>262.2700805664062</v>
+        <v>219.673706</v>
       </c>
       <c r="C611" t="n">
-        <v>-4.311737060546875</v>
+        <v>-0.7955469999999991</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="n">
-        <v>259.0861511230469</v>
+        <v>221.413895</v>
       </c>
       <c r="B612" t="n">
-        <v>257.9583435058594</v>
+        <v>218.878159</v>
       </c>
       <c r="C612" t="n">
-        <v>1.1278076171875</v>
+        <v>2.535735999999986</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="n">
-        <v>262.3200378417969</v>
+        <v>221.523285</v>
       </c>
       <c r="B613" t="n">
-        <v>259.0861511230469</v>
+        <v>221.413895</v>
       </c>
       <c r="C613" t="n">
-        <v>3.23388671875</v>
+        <v>0.1093899999999906</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="n">
-        <v>268.2986145019531</v>
+        <v>221.254791</v>
       </c>
       <c r="B614" t="n">
-        <v>262.3200378417969</v>
+        <v>221.523285</v>
       </c>
       <c r="C614" t="n">
-        <v>5.97857666015625</v>
+        <v>-0.2684939999999756</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="n">
-        <v>268.4882507324219</v>
+        <v>215.109375</v>
       </c>
       <c r="B615" t="n">
-        <v>268.2986145019531</v>
+        <v>221.254791</v>
       </c>
       <c r="C615" t="n">
-        <v>0.18963623046875</v>
+        <v>-6.145416000000012</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="n">
-        <v>269.1869201660156</v>
+        <v>215.576752</v>
       </c>
       <c r="B616" t="n">
-        <v>268.4882507324219</v>
+        <v>215.109375</v>
       </c>
       <c r="C616" t="n">
-        <v>0.69866943359375</v>
+        <v>0.467376999999999</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="n">
-        <v>270.8836669921875</v>
+        <v>219.454926</v>
       </c>
       <c r="B617" t="n">
-        <v>269.1869201660156</v>
+        <v>215.576752</v>
       </c>
       <c r="C617" t="n">
-        <v>1.696746826171875</v>
+        <v>3.878174000000001</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="n">
-        <v>269.8556518554688</v>
+        <v>227.589157</v>
       </c>
       <c r="B618" t="n">
-        <v>270.8836669921875</v>
+        <v>219.454926</v>
       </c>
       <c r="C618" t="n">
-        <v>-1.02801513671875</v>
+        <v>8.134231</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="n">
-        <v>268.5381469726562</v>
+        <v>226.922897</v>
       </c>
       <c r="B619" t="n">
-        <v>269.8556518554688</v>
+        <v>227.589157</v>
       </c>
       <c r="C619" t="n">
-        <v>-1.3175048828125</v>
+        <v>-0.6662599999999941</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="n">
-        <v>269.5262756347656</v>
+        <v>225.202576</v>
       </c>
       <c r="B620" t="n">
-        <v>268.5381469726562</v>
+        <v>226.922897</v>
       </c>
       <c r="C620" t="n">
-        <v>0.988128662109375</v>
+        <v>-1.720321000000013</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="n">
-        <v>269.6260986328125</v>
+        <v>226.097534</v>
       </c>
       <c r="B621" t="n">
-        <v>269.5262756347656</v>
+        <v>225.202576</v>
       </c>
       <c r="C621" t="n">
-        <v>0.099822998046875</v>
+        <v>0.8949580000000026</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="n">
-        <v>269.2567749023437</v>
+        <v>225.103119</v>
       </c>
       <c r="B622" t="n">
-        <v>269.6260986328125</v>
+        <v>226.097534</v>
       </c>
       <c r="C622" t="n">
-        <v>-0.3693237304688068</v>
+        <v>-0.9944150000000036</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="n">
-        <v>267.9592590332031</v>
+        <v>226.246689</v>
       </c>
       <c r="B623" t="n">
-        <v>269.2567749023437</v>
+        <v>225.103119</v>
       </c>
       <c r="C623" t="n">
-        <v>-1.297515869140568</v>
+        <v>1.143570000000011</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="n">
-        <v>269.1781311035156</v>
+        <v>226.515167</v>
       </c>
       <c r="B624" t="n">
-        <v>267.9592590332031</v>
+        <v>226.246689</v>
       </c>
       <c r="C624" t="n">
-        <v>1.2188720703125</v>
+        <v>0.2684779999999876</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="n">
-        <v>274.99267578125</v>
+        <v>231.696014</v>
       </c>
       <c r="B625" t="n">
-        <v>269.1781311035156</v>
+        <v>226.515167</v>
       </c>
       <c r="C625" t="n">
-        <v>5.814544677734375</v>
+        <v>5.180847</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="n">
-        <v>273.21435546875</v>
+        <v>224.944031</v>
       </c>
       <c r="B626" t="n">
-        <v>274.99267578125</v>
+        <v>231.696014</v>
       </c>
       <c r="C626" t="n">
-        <v>-1.7783203125</v>
+        <v>-6.751982999999996</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="n">
-        <v>272.6948547363281</v>
+        <v>225.510834</v>
       </c>
       <c r="B627" t="n">
-        <v>273.21435546875</v>
+        <v>224.944031</v>
       </c>
       <c r="C627" t="n">
-        <v>-0.519500732421875</v>
+        <v>0.5668029999999931</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="n">
-        <v>272.1553344726562</v>
+        <v>224.407028</v>
       </c>
       <c r="B628" t="n">
-        <v>272.6948547363281</v>
+        <v>225.510834</v>
       </c>
       <c r="C628" t="n">
-        <v>-0.539520263671875</v>
+        <v>-1.103805999999992</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="n">
-        <v>267.2099609375</v>
+        <v>225.530746</v>
       </c>
       <c r="B629" t="n">
-        <v>272.1553344726562</v>
+        <v>224.407028</v>
       </c>
       <c r="C629" t="n">
-        <v>-4.94537353515625</v>
+        <v>1.123717999999997</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="n">
-        <v>267.1900024414062</v>
+        <v>220.449341</v>
       </c>
       <c r="B630" t="n">
-        <v>267.2099609375</v>
+        <v>225.530746</v>
       </c>
       <c r="C630" t="n">
-        <v>-0.01995849609375</v>
+        <v>-5.08140499999999</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="n">
-        <v>268.3089294433594</v>
+        <v>224.5065</v>
       </c>
       <c r="B631" t="n">
-        <v>267.1900024414062</v>
+        <v>220.449341</v>
       </c>
       <c r="C631" t="n">
-        <v>1.118927001953125</v>
+        <v>4.057158999999984</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="n">
-        <v>266.0010986328125</v>
+        <v>228.255386</v>
       </c>
       <c r="B632" t="n">
-        <v>268.3089294433594</v>
+        <v>224.5065</v>
       </c>
       <c r="C632" t="n">
-        <v>-2.307830810546875</v>
+        <v>3.748885999999999</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="n">
-        <v>271.2361755371094</v>
+        <v>227.758179</v>
       </c>
       <c r="B633" t="n">
-        <v>266.0010986328125</v>
+        <v>228.255386</v>
       </c>
       <c r="C633" t="n">
-        <v>5.235076904296875</v>
+        <v>-0.4972069999999746</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="n">
-        <v>275.6620788574219</v>
+        <v>226.27652</v>
       </c>
       <c r="B634" t="n">
-        <v>271.2361755371094</v>
+        <v>227.758179</v>
       </c>
       <c r="C634" t="n">
-        <v>4.4259033203125</v>
+        <v>-1.481659000000008</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="n">
-        <v>276.7110900878906</v>
+        <v>230.005554</v>
       </c>
       <c r="B635" t="n">
-        <v>275.6620788574219</v>
+        <v>226.27652</v>
       </c>
       <c r="C635" t="n">
-        <v>1.04901123046875</v>
+        <v>3.729033999999984</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="n">
-        <v>277.29052734375</v>
+        <v>232.541275</v>
       </c>
       <c r="B636" t="n">
-        <v>276.7110900878906</v>
+        <v>230.005554</v>
       </c>
       <c r="C636" t="n">
-        <v>0.579437255859375</v>
+        <v>2.535721000000024</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="n">
-        <v>278.5893249511719</v>
+        <v>230.482864</v>
       </c>
       <c r="B637" t="n">
-        <v>277.29052734375</v>
+        <v>232.541275</v>
       </c>
       <c r="C637" t="n">
-        <v>1.298797607421875</v>
+        <v>-2.058411000000007</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="n">
-        <v>282.8353576660156</v>
+        <v>230.850784</v>
       </c>
       <c r="B638" t="n">
-        <v>278.5893249511719</v>
+        <v>230.482864</v>
       </c>
       <c r="C638" t="n">
-        <v>4.24603271484375</v>
+        <v>0.367919999999998</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="n">
-        <v>285.9224548339844</v>
+        <v>233.68486</v>
       </c>
       <c r="B639" t="n">
-        <v>282.8353576660156</v>
+        <v>230.850784</v>
       </c>
       <c r="C639" t="n">
-        <v>3.08709716796875</v>
+        <v>2.834075999999982</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="n">
-        <v>283.8843688964844</v>
+        <v>235.156555</v>
       </c>
       <c r="B640" t="n">
-        <v>285.9224548339844</v>
+        <v>233.68486</v>
       </c>
       <c r="C640" t="n">
-        <v>-2.0380859375</v>
+        <v>1.471695000000011</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="n">
-        <v>280.4375915527344</v>
+        <v>234.540039</v>
       </c>
       <c r="B641" t="n">
-        <v>283.8843688964844</v>
+        <v>235.156555</v>
       </c>
       <c r="C641" t="n">
-        <v>-3.44677734375</v>
+        <v>-0.6165159999999901</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="n">
-        <v>278.5193786621094</v>
+        <v>229.468567</v>
       </c>
       <c r="B642" t="n">
-        <v>280.4375915527344</v>
+        <v>234.540039</v>
       </c>
       <c r="C642" t="n">
-        <v>-1.918212890625</v>
+        <v>-5.071472</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="n">
-        <v>277.6302185058594</v>
+        <v>229.279633</v>
       </c>
       <c r="B643" t="n">
-        <v>278.5193786621094</v>
+        <v>229.468567</v>
       </c>
       <c r="C643" t="n">
-        <v>-0.88916015625</v>
+        <v>-0.1889340000000175</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="n">
-        <v>276.9208679199219</v>
+        <v>230.114929</v>
       </c>
       <c r="B644" t="n">
-        <v>277.6302185058594</v>
+        <v>229.279633</v>
       </c>
       <c r="C644" t="n">
-        <v>-0.7093505859375</v>
+        <v>0.8352959999999996</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="n">
-        <v>278.5193786621094</v>
+        <v>232.093781</v>
       </c>
       <c r="B645" t="n">
-        <v>276.9208679199219</v>
+        <v>230.114929</v>
       </c>
       <c r="C645" t="n">
-        <v>1.5985107421875</v>
+        <v>1.978852000000018</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="n">
-        <v>277.7700805664062</v>
+        <v>232.362289</v>
       </c>
       <c r="B646" t="n">
-        <v>278.5193786621094</v>
+        <v>232.093781</v>
       </c>
       <c r="C646" t="n">
-        <v>-0.749298095703125</v>
+        <v>0.2685079999999971</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="n">
-        <v>278.0198669433594</v>
+        <v>228.812271</v>
       </c>
       <c r="B647" t="n">
-        <v>277.7700805664062</v>
+        <v>232.362289</v>
       </c>
       <c r="C647" t="n">
-        <v>0.249786376953125</v>
+        <v>-3.550017999999994</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="n">
-        <v>273.8537292480469</v>
+        <v>224.645706</v>
       </c>
       <c r="B648" t="n">
-        <v>278.0198669433594</v>
+        <v>228.812271</v>
       </c>
       <c r="C648" t="n">
-        <v>-4.1661376953125</v>
+        <v>-4.16656500000002</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="n">
-        <v>274.353271484375</v>
+        <v>221.662491</v>
       </c>
       <c r="B649" t="n">
-        <v>273.8537292480469</v>
+        <v>224.645706</v>
       </c>
       <c r="C649" t="n">
-        <v>0.499542236328125</v>
+        <v>-2.983215000000001</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="n">
-        <v>271.5858764648437</v>
+        <v>220.767517</v>
       </c>
       <c r="B650" t="n">
-        <v>274.353271484375</v>
+        <v>221.662491</v>
       </c>
       <c r="C650" t="n">
-        <v>-2.767395019531307</v>
+        <v>-0.8949739999999906</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="n">
-        <v>271.935546875</v>
+        <v>222.199478</v>
       </c>
       <c r="B651" t="n">
-        <v>271.5858764648437</v>
+        <v>220.767517</v>
       </c>
       <c r="C651" t="n">
-        <v>0.3496704101563068</v>
+        <v>1.431961000000001</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="n">
-        <v>273.4141845703125</v>
+        <v>221.473541</v>
       </c>
       <c r="B652" t="n">
-        <v>271.935546875</v>
+        <v>222.199478</v>
       </c>
       <c r="C652" t="n">
-        <v>1.4786376953125</v>
+        <v>-0.7259369999999876</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="n">
-        <v>270.7166748046875</v>
+        <v>226.206909</v>
       </c>
       <c r="B653" t="n">
-        <v>273.4141845703125</v>
+        <v>221.473541</v>
       </c>
       <c r="C653" t="n">
-        <v>-2.697509765625</v>
+        <v>4.733367999999984</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="n">
-        <v>272.1053771972656</v>
+        <v>225.938141</v>
       </c>
       <c r="B654" t="n">
-        <v>270.7166748046875</v>
+        <v>226.206909</v>
       </c>
       <c r="C654" t="n">
-        <v>1.388702392578125</v>
+        <v>-0.2687679999999943</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="n">
-        <v>273.5540161132812</v>
+        <v>223.220428</v>
       </c>
       <c r="B655" t="n">
-        <v>272.1053771972656</v>
+        <v>225.938141</v>
       </c>
       <c r="C655" t="n">
-        <v>1.448638916015625</v>
+        <v>-2.717713000000003</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="n">
-        <v>273.1444091796875</v>
+        <v>223.220428</v>
       </c>
       <c r="B656" t="n">
-        <v>273.5540161132812</v>
+        <v>223.220428</v>
       </c>
       <c r="C656" t="n">
-        <v>-0.40960693359375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="n">
-        <v>273.5040893554688</v>
+        <v>224.10643</v>
       </c>
       <c r="B657" t="n">
-        <v>273.1444091796875</v>
+        <v>223.220428</v>
       </c>
       <c r="C657" t="n">
-        <v>0.35968017578125</v>
+        <v>0.8860019999999906</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="n">
-        <v>272.82470703125</v>
+        <v>227.192474</v>
       </c>
       <c r="B658" t="n">
-        <v>273.5040893554688</v>
+        <v>224.10643</v>
       </c>
       <c r="C658" t="n">
-        <v>-0.67938232421875</v>
+        <v>3.086044000000015</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="n">
-        <v>271.6058349609375</v>
+        <v>223.986954</v>
       </c>
       <c r="B659" t="n">
-        <v>272.82470703125</v>
+        <v>227.192474</v>
       </c>
       <c r="C659" t="n">
-        <v>-1.2188720703125</v>
+        <v>-3.205520000000007</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="n">
-        <v>270.7566528320312</v>
+        <v>226.993378</v>
       </c>
       <c r="B660" t="n">
-        <v>271.6058349609375</v>
+        <v>223.986954</v>
       </c>
       <c r="C660" t="n">
-        <v>-0.84918212890625</v>
+        <v>3.00642400000001</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="n">
-        <v>267.0101623535156</v>
+        <v>227.252197</v>
       </c>
       <c r="B661" t="n">
-        <v>270.7566528320312</v>
+        <v>226.993378</v>
       </c>
       <c r="C661" t="n">
-        <v>-3.746490478515625</v>
+        <v>0.2588189999999884</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="n">
-        <v>262.1147155761719</v>
+        <v>227.968948</v>
       </c>
       <c r="B662" t="n">
-        <v>267.0101623535156</v>
+        <v>227.252197</v>
       </c>
       <c r="C662" t="n">
-        <v>-4.89544677734375</v>
+        <v>0.7167510000000163</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="n">
-        <v>260.0866088867188</v>
+        <v>227.491119</v>
       </c>
       <c r="B663" t="n">
-        <v>262.1147155761719</v>
+        <v>227.968948</v>
       </c>
       <c r="C663" t="n">
-        <v>-2.028106689453125</v>
-      </c>
-    </row>
-    <row r="664">
-      <c r="A664" t="n">
-        <v>258.7978515625</v>
-      </c>
-      <c r="B664" t="n">
-        <v>260.0866088867188</v>
-      </c>
-      <c r="C664" t="n">
-        <v>-1.28875732421875</v>
-      </c>
-    </row>
-    <row r="665">
-      <c r="A665" t="n">
-        <v>259.1275329589844</v>
-      </c>
-      <c r="B665" t="n">
-        <v>258.7978515625</v>
-      </c>
-      <c r="C665" t="n">
-        <v>0.329681396484375</v>
-      </c>
-    </row>
-    <row r="666">
-      <c r="A666" t="n">
-        <v>260.0067138671875</v>
-      </c>
-      <c r="B666" t="n">
-        <v>259.1275329589844</v>
-      </c>
-      <c r="C666" t="n">
-        <v>0.879180908203125</v>
-      </c>
-    </row>
-    <row r="667">
-      <c r="A667" t="n">
-        <v>260.8059387207031</v>
-      </c>
-      <c r="B667" t="n">
-        <v>260.0067138671875</v>
-      </c>
-      <c r="C667" t="n">
-        <v>0.799224853515625</v>
-      </c>
-    </row>
-    <row r="668">
-      <c r="A668" t="n">
-        <v>259.7169799804688</v>
-      </c>
-      <c r="B668" t="n">
-        <v>260.8059387207031</v>
-      </c>
-      <c r="C668" t="n">
-        <v>-1.088958740234375</v>
-      </c>
-    </row>
-    <row r="669">
-      <c r="A669" t="n">
-        <v>257.9685974121094</v>
-      </c>
-      <c r="B669" t="n">
-        <v>259.7169799804688</v>
-      </c>
-      <c r="C669" t="n">
-        <v>-1.748382568359375</v>
-      </c>
-    </row>
-    <row r="670">
-      <c r="A670" t="n">
-        <v>255.2911224365235</v>
-      </c>
-      <c r="B670" t="n">
-        <v>257.9685974121094</v>
-      </c>
-      <c r="C670" t="n">
-        <v>-2.677474975585909</v>
-      </c>
-    </row>
-    <row r="671">
-      <c r="A671" t="n">
-        <v>246.4693756103516</v>
-      </c>
-      <c r="B671" t="n">
-        <v>255.2911224365235</v>
-      </c>
-      <c r="C671" t="n">
-        <v>-8.821746826171875</v>
-      </c>
-    </row>
-    <row r="672">
-      <c r="A672" t="n">
-        <v>247.4184875488281</v>
-      </c>
-      <c r="B672" t="n">
-        <v>246.4693756103516</v>
-      </c>
-      <c r="C672" t="n">
-        <v>0.9491119384764772</v>
-      </c>
-    </row>
-    <row r="673">
-      <c r="A673" t="n">
-        <v>248.1178436279297</v>
-      </c>
-      <c r="B673" t="n">
-        <v>247.4184875488281</v>
-      </c>
-      <c r="C673" t="n">
-        <v>0.6993560791016193</v>
-      </c>
-    </row>
-    <row r="674">
-      <c r="A674" t="n">
-        <v>247.808120727539</v>
-      </c>
-      <c r="B674" t="n">
-        <v>248.1178436279297</v>
-      </c>
-      <c r="C674" t="n">
-        <v>-0.3097229003906534</v>
-      </c>
-    </row>
-    <row r="675">
-      <c r="A675" t="n">
-        <v>255.1712341308593</v>
-      </c>
-      <c r="B675" t="n">
-        <v>247.808120727539</v>
-      </c>
-      <c r="C675" t="n">
-        <v>7.363113403320284</v>
-      </c>
-    </row>
-    <row r="676">
-      <c r="A676" t="n">
-        <v>258.0285339355469</v>
-      </c>
-      <c r="B676" t="n">
-        <v>255.1712341308593</v>
-      </c>
-      <c r="C676" t="n">
-        <v>2.857299804687557</v>
-      </c>
-    </row>
-    <row r="677">
-      <c r="A677" t="n">
-        <v>256.2002868652344</v>
-      </c>
-      <c r="B677" t="n">
-        <v>258.0285339355469</v>
-      </c>
-      <c r="C677" t="n">
-        <v>-1.8282470703125</v>
-      </c>
-    </row>
-    <row r="678">
-      <c r="A678" t="n">
-        <v>258.0385437011719</v>
-      </c>
-      <c r="B678" t="n">
-        <v>256.2002868652344</v>
-      </c>
-      <c r="C678" t="n">
-        <v>1.8382568359375</v>
-      </c>
-    </row>
-    <row r="679">
-      <c r="A679" t="n">
-        <v>259.2374267578125</v>
-      </c>
-      <c r="B679" t="n">
-        <v>258.0385437011719</v>
-      </c>
-      <c r="C679" t="n">
-        <v>1.198883056640625</v>
-      </c>
-    </row>
-    <row r="680">
-      <c r="A680" t="n">
-        <v>269.7575988769531</v>
-      </c>
-      <c r="B680" t="n">
-        <v>259.2374267578125</v>
-      </c>
-      <c r="C680" t="n">
-        <v>10.52017211914062</v>
-      </c>
-    </row>
-    <row r="681">
-      <c r="A681" t="n">
-        <v>269.2280883789062</v>
-      </c>
-      <c r="B681" t="n">
-        <v>269.7575988769531</v>
-      </c>
-      <c r="C681" t="n">
-        <v>-0.529510498046875</v>
-      </c>
-    </row>
-    <row r="682">
-      <c r="A682" t="n">
-        <v>276.2315063476562</v>
-      </c>
-      <c r="B682" t="n">
-        <v>269.2280883789062</v>
-      </c>
-      <c r="C682" t="n">
-        <v>7.00341796875</v>
-      </c>
-    </row>
-    <row r="683">
-      <c r="A683" t="n">
-        <v>275.6520690917969</v>
-      </c>
-      <c r="B683" t="n">
-        <v>276.2315063476562</v>
-      </c>
-      <c r="C683" t="n">
-        <v>-0.579437255859375</v>
-      </c>
-    </row>
-    <row r="684">
-      <c r="A684" t="n">
-        <v>277.8599853515625</v>
-      </c>
-      <c r="B684" t="n">
-        <v>275.6520690917969</v>
-      </c>
-      <c r="C684" t="n">
-        <v>2.207916259765625</v>
-      </c>
-    </row>
-    <row r="685">
-      <c r="A685" t="n">
-        <v>274.6199951171875</v>
-      </c>
-      <c r="B685" t="n">
-        <v>277.8599853515625</v>
-      </c>
-      <c r="C685" t="n">
-        <v>-3.239990234375</v>
-      </c>
-    </row>
-    <row r="686">
-      <c r="A686" t="n">
-        <v>273.6799926757812</v>
-      </c>
-      <c r="B686" t="n">
-        <v>274.6199951171875</v>
-      </c>
-      <c r="C686" t="n">
-        <v>-0.94000244140625</v>
-      </c>
-    </row>
-    <row r="687">
-      <c r="A687" t="n">
-        <v>275.5</v>
-      </c>
-      <c r="B687" t="n">
-        <v>273.6799926757812</v>
-      </c>
-      <c r="C687" t="n">
-        <v>1.82000732421875</v>
-      </c>
-    </row>
-    <row r="688">
-      <c r="A688" t="n">
-        <v>261.7300109863281</v>
-      </c>
-      <c r="B688" t="n">
-        <v>275.5</v>
-      </c>
-      <c r="C688" t="n">
-        <v>-13.76998901367188</v>
-      </c>
-    </row>
-    <row r="689">
-      <c r="A689" t="n">
-        <v>255.7799987792969</v>
-      </c>
-      <c r="B689" t="n">
-        <v>261.7300109863281</v>
-      </c>
-      <c r="C689" t="n">
-        <v>-5.95001220703125</v>
+        <v>-0.477829000000014</v>
       </c>
     </row>
   </sheetData>
